--- a/LISTADO PARA CONVENIO.xlsx
+++ b/LISTADO PARA CONVENIO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JRomero01\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaqu\Desktop\Generador-de-archivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F131C98-1462-4855-984E-EAF1D075C2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621EF3C3-5E27-4C59-B8B3-C8FF695EE3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16043" uniqueCount="3660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15761" uniqueCount="3660">
   <si>
     <t>Unidad Negocios</t>
   </si>
@@ -11688,7 +11688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AN535"/>
+  <dimension ref="A1:AN538"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" hidden="1" customWidth="1"/>
@@ -11851,7 +11851,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -11971,7 +11971,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>2344</v>
       </c>
       <c r="P3" t="str">
-        <f t="shared" ref="P3:P66" si="0">_xlfn.CONCAT(Q3," ",R3," ",S3)</f>
+        <f t="shared" ref="P3:P6" si="0">_xlfn.CONCAT(Q3," ",R3," ",S3)</f>
         <v>RAQUEL JANETH FERNANDEZ AMEZQUITA</v>
       </c>
       <c r="Q3" t="s">
@@ -12091,7 +12091,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -12211,7 +12211,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -12331,7 +12331,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -12451,7 +12451,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -12494,10 +12494,6 @@
       <c r="O7" t="s">
         <v>2858</v>
       </c>
-      <c r="P7" t="str">
-        <f t="shared" si="0"/>
-        <v>BLANCA NEREIDA PEÑA AYALA</v>
-      </c>
       <c r="Q7" t="s">
         <v>2859</v>
       </c>
@@ -12571,7 +12567,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -12614,10 +12610,6 @@
       <c r="O8" t="s">
         <v>2865</v>
       </c>
-      <c r="P8" t="str">
-        <f t="shared" si="0"/>
-        <v>JOSE LUIS TOTO MOZO</v>
-      </c>
       <c r="Q8" t="s">
         <v>404</v>
       </c>
@@ -12691,7 +12683,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -12707,9 +12699,6 @@
       <c r="E9" t="s">
         <v>2854</v>
       </c>
-      <c r="F9" t="s">
-        <v>2855</v>
-      </c>
       <c r="G9" t="s">
         <v>2856</v>
       </c>
@@ -12734,10 +12723,6 @@
       <c r="O9" t="s">
         <v>2872</v>
       </c>
-      <c r="P9" t="str">
-        <f t="shared" si="0"/>
-        <v>DOMINGO FLORES MARTINEZ</v>
-      </c>
       <c r="Q9" t="s">
         <v>381</v>
       </c>
@@ -12811,7 +12796,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -12854,10 +12839,6 @@
       <c r="O10" t="s">
         <v>2877</v>
       </c>
-      <c r="P10" t="str">
-        <f t="shared" si="0"/>
-        <v>FERNANDO NICOLAS SOLANO MUÑOZ</v>
-      </c>
       <c r="Q10" t="s">
         <v>2878</v>
       </c>
@@ -12931,7 +12912,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -12974,10 +12955,6 @@
       <c r="O11" t="s">
         <v>2884</v>
       </c>
-      <c r="P11" t="str">
-        <f t="shared" si="0"/>
-        <v>JOSE LUIS DE LA ROSA ALEJANDRO</v>
-      </c>
       <c r="Q11" t="s">
         <v>404</v>
       </c>
@@ -13051,7 +13028,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -13094,10 +13071,6 @@
       <c r="O12" t="s">
         <v>2889</v>
       </c>
-      <c r="P12" t="str">
-        <f t="shared" si="0"/>
-        <v>BEATRIZ ADRIANA MOCTEZUMA CARDONA</v>
-      </c>
       <c r="Q12" t="s">
         <v>2890</v>
       </c>
@@ -13171,7 +13144,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -13214,10 +13187,6 @@
       <c r="O13" t="s">
         <v>2896</v>
       </c>
-      <c r="P13" t="str">
-        <f t="shared" si="0"/>
-        <v>SALVADOR ROSAS CASTILLO</v>
-      </c>
       <c r="Q13" t="s">
         <v>2897</v>
       </c>
@@ -13291,7 +13260,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -13334,10 +13303,6 @@
       <c r="O14" t="s">
         <v>2902</v>
       </c>
-      <c r="P14" t="str">
-        <f t="shared" si="0"/>
-        <v>CARLOS PINO GARCIA</v>
-      </c>
       <c r="Q14" t="s">
         <v>1108</v>
       </c>
@@ -13411,7 +13376,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -13454,10 +13419,6 @@
       <c r="O15" t="s">
         <v>2908</v>
       </c>
-      <c r="P15" t="str">
-        <f t="shared" si="0"/>
-        <v>GUADALUPE MAURICIO PLATA</v>
-      </c>
       <c r="Q15" t="s">
         <v>2909</v>
       </c>
@@ -13531,7 +13492,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -13574,10 +13535,6 @@
       <c r="O16" t="s">
         <v>2914</v>
       </c>
-      <c r="P16" t="str">
-        <f t="shared" si="0"/>
-        <v>JHONATAN CORONADO CONTRERAS</v>
-      </c>
       <c r="Q16" t="s">
         <v>2915</v>
       </c>
@@ -13648,7 +13605,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -13691,10 +13648,6 @@
       <c r="O17" t="s">
         <v>2919</v>
       </c>
-      <c r="P17" t="str">
-        <f t="shared" si="0"/>
-        <v>LAUREANO MORALES GONZALEZ</v>
-      </c>
       <c r="Q17" t="s">
         <v>2920</v>
       </c>
@@ -13768,7 +13721,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -13811,10 +13764,6 @@
       <c r="O18" t="s">
         <v>2925</v>
       </c>
-      <c r="P18" t="str">
-        <f t="shared" si="0"/>
-        <v>PLACIDO RAMON FLORENCIA</v>
-      </c>
       <c r="Q18" t="s">
         <v>2926</v>
       </c>
@@ -13888,7 +13837,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -13931,10 +13880,6 @@
       <c r="O19" t="s">
         <v>2933</v>
       </c>
-      <c r="P19" t="str">
-        <f t="shared" si="0"/>
-        <v>FELIPE DE JESUS MARTINEZ PAEZ</v>
-      </c>
       <c r="Q19" t="s">
         <v>2934</v>
       </c>
@@ -14008,7 +13953,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -14051,10 +13996,6 @@
       <c r="O20" t="s">
         <v>2940</v>
       </c>
-      <c r="P20" t="str">
-        <f t="shared" si="0"/>
-        <v>JOSE MANUEL LOPEZ HERNANDEZ</v>
-      </c>
       <c r="Q20" t="s">
         <v>972</v>
       </c>
@@ -14128,7 +14069,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -14171,10 +14112,6 @@
       <c r="O21" t="s">
         <v>2945</v>
       </c>
-      <c r="P21" t="str">
-        <f t="shared" si="0"/>
-        <v>JULIO CARBALLO ROMERO</v>
-      </c>
       <c r="Q21" t="s">
         <v>2946</v>
       </c>
@@ -14248,7 +14185,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -14291,10 +14228,6 @@
       <c r="O22" t="s">
         <v>2951</v>
       </c>
-      <c r="P22" t="str">
-        <f t="shared" si="0"/>
-        <v>PERLA ITZEL MENDEZ LOPEZ</v>
-      </c>
       <c r="Q22" t="s">
         <v>2952</v>
       </c>
@@ -14368,7 +14301,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -14411,10 +14344,6 @@
       <c r="O23" t="s">
         <v>2957</v>
       </c>
-      <c r="P23" t="str">
-        <f t="shared" si="0"/>
-        <v>AIDEE REBECA RIVERA RODRIGUEZ</v>
-      </c>
       <c r="Q23" t="s">
         <v>2958</v>
       </c>
@@ -14488,7 +14417,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -14531,10 +14460,6 @@
       <c r="O24" t="s">
         <v>2963</v>
       </c>
-      <c r="P24" t="str">
-        <f t="shared" si="0"/>
-        <v>YURIDIA PUCHETA RODRIGUEZ</v>
-      </c>
       <c r="Q24" t="s">
         <v>2964</v>
       </c>
@@ -14608,7 +14533,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -14651,10 +14576,6 @@
       <c r="O25" t="s">
         <v>2969</v>
       </c>
-      <c r="P25" t="str">
-        <f t="shared" si="0"/>
-        <v>DOMINIC DE JESUS AGUILAR HERNANDEZ</v>
-      </c>
       <c r="Q25" t="s">
         <v>2970</v>
       </c>
@@ -14728,7 +14649,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -14771,10 +14692,6 @@
       <c r="O26" t="s">
         <v>2975</v>
       </c>
-      <c r="P26" t="str">
-        <f t="shared" si="0"/>
-        <v>LESLY AMIZADAY URIBE MORALES</v>
-      </c>
       <c r="Q26" t="s">
         <v>2976</v>
       </c>
@@ -14848,7 +14765,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -14891,10 +14808,6 @@
       <c r="O27" t="s">
         <v>2387</v>
       </c>
-      <c r="P27" t="str">
-        <f t="shared" si="0"/>
-        <v>MARIO ALBERTO MARTINEZ SALAZAR</v>
-      </c>
       <c r="Q27" t="s">
         <v>2388</v>
       </c>
@@ -14965,7 +14878,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -15008,10 +14921,6 @@
       <c r="O28" t="s">
         <v>2392</v>
       </c>
-      <c r="P28" t="str">
-        <f t="shared" si="0"/>
-        <v>MARCELINO HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q28" t="s">
         <v>178</v>
       </c>
@@ -15082,7 +14991,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -15125,10 +15034,6 @@
       <c r="O29" t="s">
         <v>2396</v>
       </c>
-      <c r="P29" t="str">
-        <f t="shared" si="0"/>
-        <v>JULIO IVAN REYES MEJIA</v>
-      </c>
       <c r="Q29" t="s">
         <v>2397</v>
       </c>
@@ -15199,7 +15104,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -15242,10 +15147,6 @@
       <c r="O30" t="s">
         <v>2401</v>
       </c>
-      <c r="P30" t="str">
-        <f t="shared" si="0"/>
-        <v>EDGAR AXEL VALLEJO ENRIQUEZ</v>
-      </c>
       <c r="Q30" t="s">
         <v>2402</v>
       </c>
@@ -15319,7 +15220,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -15362,10 +15263,6 @@
       <c r="O31" t="s">
         <v>2409</v>
       </c>
-      <c r="P31" t="str">
-        <f t="shared" si="0"/>
-        <v>JESUS PUENTE PUENTE</v>
-      </c>
       <c r="Q31" t="s">
         <v>440</v>
       </c>
@@ -15439,7 +15336,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -15482,10 +15379,6 @@
       <c r="O32" t="s">
         <v>2415</v>
       </c>
-      <c r="P32" t="str">
-        <f t="shared" si="0"/>
-        <v>CESAR EDUARDO BALDERAS GARCIA</v>
-      </c>
       <c r="Q32" t="s">
         <v>2416</v>
       </c>
@@ -15559,7 +15452,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -15602,10 +15495,6 @@
       <c r="O33" t="s">
         <v>2422</v>
       </c>
-      <c r="P33" t="str">
-        <f t="shared" si="0"/>
-        <v>CESAR ARIEL PECH CHIM</v>
-      </c>
       <c r="Q33" t="s">
         <v>2423</v>
       </c>
@@ -15679,7 +15568,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -15722,10 +15611,6 @@
       <c r="O34" t="s">
         <v>2722</v>
       </c>
-      <c r="P34" t="str">
-        <f t="shared" si="0"/>
-        <v>MARCO ANTONIO VELAZQUEZ ALVAREZ</v>
-      </c>
       <c r="Q34" t="s">
         <v>864</v>
       </c>
@@ -15799,7 +15684,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -15815,9 +15700,6 @@
       <c r="E35" t="s">
         <v>2719</v>
       </c>
-      <c r="F35" t="s">
-        <v>2720</v>
-      </c>
       <c r="G35" t="s">
         <v>2721</v>
       </c>
@@ -15842,10 +15724,6 @@
       <c r="O35" t="s">
         <v>2727</v>
       </c>
-      <c r="P35" t="str">
-        <f t="shared" si="0"/>
-        <v>ESTRELLA YUDITH LLANO GUAJARDO</v>
-      </c>
       <c r="Q35" t="s">
         <v>2728</v>
       </c>
@@ -15919,7 +15797,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -15935,9 +15813,6 @@
       <c r="E36" t="s">
         <v>2719</v>
       </c>
-      <c r="F36" t="s">
-        <v>2720</v>
-      </c>
       <c r="G36" t="s">
         <v>2721</v>
       </c>
@@ -15962,10 +15837,6 @@
       <c r="O36" t="s">
         <v>2735</v>
       </c>
-      <c r="P36" t="str">
-        <f t="shared" si="0"/>
-        <v>RODRIGO VALENTIN ANTONIO</v>
-      </c>
       <c r="Q36" t="s">
         <v>252</v>
       </c>
@@ -16039,7 +15910,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -16055,9 +15926,6 @@
       <c r="E37" t="s">
         <v>2719</v>
       </c>
-      <c r="F37" t="s">
-        <v>2720</v>
-      </c>
       <c r="G37" t="s">
         <v>2721</v>
       </c>
@@ -16082,10 +15950,6 @@
       <c r="O37" t="s">
         <v>2741</v>
       </c>
-      <c r="P37" t="str">
-        <f t="shared" si="0"/>
-        <v>ERIKA SUGEY NIÑO CARDIEL</v>
-      </c>
       <c r="Q37" t="s">
         <v>2742</v>
       </c>
@@ -16159,7 +16023,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -16175,9 +16039,6 @@
       <c r="E38" t="s">
         <v>2719</v>
       </c>
-      <c r="F38" t="s">
-        <v>2720</v>
-      </c>
       <c r="G38" t="s">
         <v>2721</v>
       </c>
@@ -16202,10 +16063,6 @@
       <c r="O38" t="s">
         <v>2749</v>
       </c>
-      <c r="P38" t="str">
-        <f t="shared" si="0"/>
-        <v>YURITZA GUADALUPE CAMARA VILLARINO</v>
-      </c>
       <c r="Q38" t="s">
         <v>2750</v>
       </c>
@@ -16279,7 +16136,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -16295,9 +16152,6 @@
       <c r="E39" t="s">
         <v>2719</v>
       </c>
-      <c r="F39" t="s">
-        <v>2720</v>
-      </c>
       <c r="G39" t="s">
         <v>2721</v>
       </c>
@@ -16322,10 +16176,6 @@
       <c r="O39" t="s">
         <v>2756</v>
       </c>
-      <c r="P39" t="str">
-        <f t="shared" si="0"/>
-        <v>MARCELINO ALEJO DEL ANGEL</v>
-      </c>
       <c r="Q39" t="s">
         <v>178</v>
       </c>
@@ -16399,7 +16249,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -16415,9 +16265,6 @@
       <c r="E40" t="s">
         <v>2719</v>
       </c>
-      <c r="F40" t="s">
-        <v>2720</v>
-      </c>
       <c r="G40" t="s">
         <v>2721</v>
       </c>
@@ -16442,10 +16289,6 @@
       <c r="O40" t="s">
         <v>2762</v>
       </c>
-      <c r="P40" t="str">
-        <f t="shared" si="0"/>
-        <v>JOSE LUIS SOTO ROBLES</v>
-      </c>
       <c r="Q40" t="s">
         <v>404</v>
       </c>
@@ -16519,7 +16362,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -16535,9 +16378,6 @@
       <c r="E41" t="s">
         <v>2719</v>
       </c>
-      <c r="F41" t="s">
-        <v>2720</v>
-      </c>
       <c r="G41" t="s">
         <v>2721</v>
       </c>
@@ -16562,10 +16402,6 @@
       <c r="O41" t="s">
         <v>2767</v>
       </c>
-      <c r="P41" t="str">
-        <f t="shared" si="0"/>
-        <v>BENJAMIN PEREZ BENITEZ</v>
-      </c>
       <c r="Q41" t="s">
         <v>2768</v>
       </c>
@@ -16639,7 +16475,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="42" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -16655,9 +16491,6 @@
       <c r="E42" t="s">
         <v>2719</v>
       </c>
-      <c r="F42" t="s">
-        <v>2720</v>
-      </c>
       <c r="G42" t="s">
         <v>2721</v>
       </c>
@@ -16682,10 +16515,6 @@
       <c r="O42" t="s">
         <v>2774</v>
       </c>
-      <c r="P42" t="str">
-        <f t="shared" si="0"/>
-        <v>MARTINA ALCALA MARTINEZ</v>
-      </c>
       <c r="Q42" t="s">
         <v>2775</v>
       </c>
@@ -16759,7 +16588,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="43" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -16775,9 +16604,6 @@
       <c r="E43" t="s">
         <v>2719</v>
       </c>
-      <c r="F43" t="s">
-        <v>2720</v>
-      </c>
       <c r="G43" t="s">
         <v>2721</v>
       </c>
@@ -16802,10 +16628,6 @@
       <c r="O43" t="s">
         <v>2781</v>
       </c>
-      <c r="P43" t="str">
-        <f t="shared" si="0"/>
-        <v>MIGUEL HERNANDEZ VAZQUEZ</v>
-      </c>
       <c r="Q43" t="s">
         <v>1336</v>
       </c>
@@ -16879,7 +16701,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -16895,9 +16717,6 @@
       <c r="E44" t="s">
         <v>2719</v>
       </c>
-      <c r="F44" t="s">
-        <v>2720</v>
-      </c>
       <c r="G44" t="s">
         <v>2721</v>
       </c>
@@ -16922,10 +16741,6 @@
       <c r="O44" t="s">
         <v>2786</v>
       </c>
-      <c r="P44" t="str">
-        <f t="shared" si="0"/>
-        <v>FROY URIEL MARTINEZ MUÑOA</v>
-      </c>
       <c r="Q44" t="s">
         <v>2787</v>
       </c>
@@ -16999,7 +16814,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -17015,9 +16830,6 @@
       <c r="E45" t="s">
         <v>2719</v>
       </c>
-      <c r="F45" t="s">
-        <v>2720</v>
-      </c>
       <c r="G45" t="s">
         <v>2721</v>
       </c>
@@ -17042,10 +16854,6 @@
       <c r="O45" t="s">
         <v>2793</v>
       </c>
-      <c r="P45" t="str">
-        <f t="shared" si="0"/>
-        <v>JUAN JOSE ALVARADO SALAS</v>
-      </c>
       <c r="Q45" t="s">
         <v>2794</v>
       </c>
@@ -17119,7 +16927,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -17162,10 +16970,6 @@
       <c r="O46" t="s">
         <v>3170</v>
       </c>
-      <c r="P46" t="str">
-        <f t="shared" si="0"/>
-        <v>JOSE RAMON CANO REYES</v>
-      </c>
       <c r="Q46" t="s">
         <v>3171</v>
       </c>
@@ -17239,7 +17043,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="47" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -17282,10 +17086,6 @@
       <c r="O47" t="s">
         <v>3177</v>
       </c>
-      <c r="P47" t="str">
-        <f t="shared" si="0"/>
-        <v>ABDIEL ALCALDE MARTINEZ</v>
-      </c>
       <c r="Q47" t="s">
         <v>3178</v>
       </c>
@@ -17359,7 +17159,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="48" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -17402,10 +17202,6 @@
       <c r="O48" t="s">
         <v>3122</v>
       </c>
-      <c r="P48" t="str">
-        <f t="shared" si="0"/>
-        <v>MARTIN ANGEL ROSAS CASTILLO</v>
-      </c>
       <c r="Q48" t="s">
         <v>3123</v>
       </c>
@@ -17479,7 +17275,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="49" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -17495,9 +17291,6 @@
       <c r="E49" t="s">
         <v>3119</v>
       </c>
-      <c r="F49" t="s">
-        <v>3120</v>
-      </c>
       <c r="G49" t="s">
         <v>3121</v>
       </c>
@@ -17522,10 +17315,6 @@
       <c r="O49" t="s">
         <v>3128</v>
       </c>
-      <c r="P49" t="str">
-        <f t="shared" si="0"/>
-        <v>JUAN FRANCISCO NERIO SANCHEZ</v>
-      </c>
       <c r="Q49" t="s">
         <v>2573</v>
       </c>
@@ -17599,7 +17388,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="50" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -17615,9 +17404,6 @@
       <c r="E50" t="s">
         <v>3119</v>
       </c>
-      <c r="F50" t="s">
-        <v>3120</v>
-      </c>
       <c r="G50" t="s">
         <v>3121</v>
       </c>
@@ -17642,10 +17428,6 @@
       <c r="O50" t="s">
         <v>3135</v>
       </c>
-      <c r="P50" t="str">
-        <f t="shared" si="0"/>
-        <v>JAQUELINE ANAHI CARBAJAL GARCIA</v>
-      </c>
       <c r="Q50" t="s">
         <v>3136</v>
       </c>
@@ -17719,7 +17501,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="51" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -17735,9 +17517,6 @@
       <c r="E51" t="s">
         <v>3119</v>
       </c>
-      <c r="F51" t="s">
-        <v>3120</v>
-      </c>
       <c r="G51" t="s">
         <v>3121</v>
       </c>
@@ -17762,10 +17541,6 @@
       <c r="O51" t="s">
         <v>3142</v>
       </c>
-      <c r="P51" t="str">
-        <f t="shared" si="0"/>
-        <v>MARIA ANTONIA ARIAS LUNA</v>
-      </c>
       <c r="Q51" t="s">
         <v>3143</v>
       </c>
@@ -17839,7 +17614,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="52" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -17855,9 +17630,6 @@
       <c r="E52" t="s">
         <v>3119</v>
       </c>
-      <c r="F52" t="s">
-        <v>3120</v>
-      </c>
       <c r="G52" t="s">
         <v>3121</v>
       </c>
@@ -17882,10 +17654,6 @@
       <c r="O52" t="s">
         <v>3148</v>
       </c>
-      <c r="P52" t="str">
-        <f t="shared" si="0"/>
-        <v>MARIA ANIZETA PEREZ SOSA</v>
-      </c>
       <c r="Q52" t="s">
         <v>3149</v>
       </c>
@@ -17959,7 +17727,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="53" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -18002,10 +17770,6 @@
       <c r="O53" t="s">
         <v>2237</v>
       </c>
-      <c r="P53" t="str">
-        <f t="shared" si="0"/>
-        <v>RUTH IRASEMA SUSTAITA ZUÑIGA</v>
-      </c>
       <c r="Q53" t="s">
         <v>2238</v>
       </c>
@@ -18076,7 +17840,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="54" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -18092,9 +17856,6 @@
       <c r="E54" t="s">
         <v>2234</v>
       </c>
-      <c r="F54" t="s">
-        <v>2235</v>
-      </c>
       <c r="G54" t="s">
         <v>2236</v>
       </c>
@@ -18119,10 +17880,6 @@
       <c r="O54" t="s">
         <v>2242</v>
       </c>
-      <c r="P54" t="str">
-        <f t="shared" si="0"/>
-        <v>ESMERALDA GONZALEZ CORONEL</v>
-      </c>
       <c r="Q54" t="s">
         <v>522</v>
       </c>
@@ -18196,7 +17953,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="55" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -18212,9 +17969,6 @@
       <c r="E55" t="s">
         <v>2234</v>
       </c>
-      <c r="F55" t="s">
-        <v>2235</v>
-      </c>
       <c r="G55" t="s">
         <v>2236</v>
       </c>
@@ -18239,10 +17993,6 @@
       <c r="O55" t="s">
         <v>2249</v>
       </c>
-      <c r="P55" t="str">
-        <f t="shared" si="0"/>
-        <v>PEDRO DAMIAN PICON DIMAS</v>
-      </c>
       <c r="Q55" t="s">
         <v>2250</v>
       </c>
@@ -18316,7 +18066,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="56" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -18332,9 +18082,6 @@
       <c r="E56" t="s">
         <v>2234</v>
       </c>
-      <c r="F56" t="s">
-        <v>2235</v>
-      </c>
       <c r="G56" t="s">
         <v>2321</v>
       </c>
@@ -18359,10 +18106,6 @@
       <c r="O56" t="s">
         <v>2322</v>
       </c>
-      <c r="P56" t="str">
-        <f t="shared" si="0"/>
-        <v>JUAN MANUEL GOMEZ PEREZ</v>
-      </c>
       <c r="Q56" t="s">
         <v>2323</v>
       </c>
@@ -18436,7 +18179,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="57" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>39</v>
       </c>
@@ -18452,9 +18195,6 @@
       <c r="E57" t="s">
         <v>2234</v>
       </c>
-      <c r="F57" t="s">
-        <v>2235</v>
-      </c>
       <c r="G57" t="s">
         <v>2321</v>
       </c>
@@ -18479,10 +18219,6 @@
       <c r="O57" t="s">
         <v>2328</v>
       </c>
-      <c r="P57" t="str">
-        <f t="shared" si="0"/>
-        <v>MARIO ADAN GARCIA ANGELES</v>
-      </c>
       <c r="Q57" t="s">
         <v>2329</v>
       </c>
@@ -18556,7 +18292,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -18599,10 +18335,6 @@
       <c r="O58" t="s">
         <v>49</v>
       </c>
-      <c r="P58" t="str">
-        <f t="shared" si="0"/>
-        <v>MARIA TEODORA ROMUALDO GONZALEZ</v>
-      </c>
       <c r="Q58" t="s">
         <v>50</v>
       </c>
@@ -18673,7 +18405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>39</v>
       </c>
@@ -18689,9 +18421,6 @@
       <c r="E59" t="s">
         <v>43</v>
       </c>
-      <c r="F59" t="s">
-        <v>44</v>
-      </c>
       <c r="G59" t="s">
         <v>45</v>
       </c>
@@ -18716,10 +18445,6 @@
       <c r="O59" t="s">
         <v>67</v>
       </c>
-      <c r="P59" t="str">
-        <f t="shared" si="0"/>
-        <v>DANIEL MORALES OVILLA</v>
-      </c>
       <c r="Q59" t="s">
         <v>68</v>
       </c>
@@ -18793,7 +18518,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>39</v>
       </c>
@@ -18809,9 +18534,6 @@
       <c r="E60" t="s">
         <v>43</v>
       </c>
-      <c r="F60" t="s">
-        <v>44</v>
-      </c>
       <c r="G60" t="s">
         <v>45</v>
       </c>
@@ -18836,10 +18558,6 @@
       <c r="O60" t="s">
         <v>77</v>
       </c>
-      <c r="P60" t="str">
-        <f t="shared" si="0"/>
-        <v>NINFA CANDELARIA ANGUIANO CORDOVA</v>
-      </c>
       <c r="Q60" t="s">
         <v>78</v>
       </c>
@@ -18913,7 +18631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -18929,9 +18647,6 @@
       <c r="E61" t="s">
         <v>43</v>
       </c>
-      <c r="F61" t="s">
-        <v>44</v>
-      </c>
       <c r="G61" t="s">
         <v>45</v>
       </c>
@@ -18956,10 +18671,6 @@
       <c r="O61" t="s">
         <v>86</v>
       </c>
-      <c r="P61" t="str">
-        <f t="shared" si="0"/>
-        <v>BRISEIDA SANTIAGO DOMINGUEZ</v>
-      </c>
       <c r="Q61" t="s">
         <v>87</v>
       </c>
@@ -19033,7 +18744,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>39</v>
       </c>
@@ -19049,9 +18760,6 @@
       <c r="E62" t="s">
         <v>43</v>
       </c>
-      <c r="F62" t="s">
-        <v>44</v>
-      </c>
       <c r="G62" t="s">
         <v>45</v>
       </c>
@@ -19076,10 +18784,6 @@
       <c r="O62" t="s">
         <v>95</v>
       </c>
-      <c r="P62" t="str">
-        <f t="shared" si="0"/>
-        <v>DAVID ENRIQUEZ GUTIERREZ</v>
-      </c>
       <c r="Q62" t="s">
         <v>96</v>
       </c>
@@ -19153,7 +18857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -19196,10 +18900,6 @@
       <c r="O63" t="s">
         <v>3037</v>
       </c>
-      <c r="P63" t="str">
-        <f t="shared" si="0"/>
-        <v>ANGEL URIEL GONZALEZ DOMINGUEZ</v>
-      </c>
       <c r="Q63" t="s">
         <v>3038</v>
       </c>
@@ -19273,7 +18973,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="64" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -19289,9 +18989,6 @@
       <c r="E64" t="s">
         <v>3034</v>
       </c>
-      <c r="F64" t="s">
-        <v>3035</v>
-      </c>
       <c r="G64" t="s">
         <v>3036</v>
       </c>
@@ -19316,10 +19013,6 @@
       <c r="O64" t="s">
         <v>3043</v>
       </c>
-      <c r="P64" t="str">
-        <f t="shared" si="0"/>
-        <v>BALTAZAR BAUTISTA DEL ANGEL</v>
-      </c>
       <c r="Q64" t="s">
         <v>3044</v>
       </c>
@@ -19393,7 +19086,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -19409,9 +19102,6 @@
       <c r="E65" t="s">
         <v>3034</v>
       </c>
-      <c r="F65" t="s">
-        <v>3035</v>
-      </c>
       <c r="G65" t="s">
         <v>3036</v>
       </c>
@@ -19436,10 +19126,6 @@
       <c r="O65" t="s">
         <v>3049</v>
       </c>
-      <c r="P65" t="str">
-        <f t="shared" si="0"/>
-        <v>LUISA LETICIA CHAN CRUZ</v>
-      </c>
       <c r="Q65" t="s">
         <v>3050</v>
       </c>
@@ -19513,7 +19199,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -19529,9 +19215,6 @@
       <c r="E66" t="s">
         <v>3034</v>
       </c>
-      <c r="F66" t="s">
-        <v>3035</v>
-      </c>
       <c r="G66" t="s">
         <v>3036</v>
       </c>
@@ -19556,10 +19239,6 @@
       <c r="O66" t="s">
         <v>3056</v>
       </c>
-      <c r="P66" t="str">
-        <f t="shared" si="0"/>
-        <v>ELOIDA GARCIA HERNANDEZ</v>
-      </c>
       <c r="Q66" t="s">
         <v>3057</v>
       </c>
@@ -19630,7 +19309,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="67" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -19646,9 +19325,6 @@
       <c r="E67" t="s">
         <v>3034</v>
       </c>
-      <c r="F67" t="s">
-        <v>3035</v>
-      </c>
       <c r="G67" t="s">
         <v>3036</v>
       </c>
@@ -19673,10 +19349,6 @@
       <c r="O67" t="s">
         <v>3061</v>
       </c>
-      <c r="P67" t="str">
-        <f t="shared" ref="P67:P115" si="1">_xlfn.CONCAT(Q67," ",R67," ",S67)</f>
-        <v>ANGEL HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q67" t="s">
         <v>529</v>
       </c>
@@ -19750,7 +19422,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="68" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -19766,9 +19438,6 @@
       <c r="E68" t="s">
         <v>3034</v>
       </c>
-      <c r="F68" t="s">
-        <v>3035</v>
-      </c>
       <c r="G68" t="s">
         <v>3036</v>
       </c>
@@ -19793,10 +19462,6 @@
       <c r="O68" t="s">
         <v>3066</v>
       </c>
-      <c r="P68" t="str">
-        <f t="shared" si="1"/>
-        <v>GERARDO MARTINEZ ROCHA</v>
-      </c>
       <c r="Q68" t="s">
         <v>3067</v>
       </c>
@@ -19870,7 +19535,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="69" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>39</v>
       </c>
@@ -19886,9 +19551,6 @@
       <c r="E69" t="s">
         <v>3034</v>
       </c>
-      <c r="F69" t="s">
-        <v>3035</v>
-      </c>
       <c r="G69" t="s">
         <v>3036</v>
       </c>
@@ -19913,10 +19575,6 @@
       <c r="O69" t="s">
         <v>3073</v>
       </c>
-      <c r="P69" t="str">
-        <f t="shared" si="1"/>
-        <v>CRISTINA OVIEDO AGUILERA</v>
-      </c>
       <c r="Q69" t="s">
         <v>3074</v>
       </c>
@@ -19990,7 +19648,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="70" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -20006,9 +19664,6 @@
       <c r="E70" t="s">
         <v>3034</v>
       </c>
-      <c r="F70" t="s">
-        <v>3035</v>
-      </c>
       <c r="G70" t="s">
         <v>3036</v>
       </c>
@@ -20033,10 +19688,6 @@
       <c r="O70" t="s">
         <v>3080</v>
       </c>
-      <c r="P70" t="str">
-        <f t="shared" si="1"/>
-        <v>ERIC ALEJANDRO CORTAZAR DE LA CRUZ</v>
-      </c>
       <c r="Q70" t="s">
         <v>3081</v>
       </c>
@@ -20110,7 +19761,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="71" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>39</v>
       </c>
@@ -20126,9 +19777,6 @@
       <c r="E71" t="s">
         <v>3034</v>
       </c>
-      <c r="F71" t="s">
-        <v>3035</v>
-      </c>
       <c r="G71" t="s">
         <v>3036</v>
       </c>
@@ -20153,10 +19801,6 @@
       <c r="O71" t="s">
         <v>3087</v>
       </c>
-      <c r="P71" t="str">
-        <f t="shared" si="1"/>
-        <v>MARIA CONCEPCION LOPEZ LOPEZ</v>
-      </c>
       <c r="Q71" t="s">
         <v>3088</v>
       </c>
@@ -20230,7 +19874,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="72" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>39</v>
       </c>
@@ -20246,9 +19890,6 @@
       <c r="E72" t="s">
         <v>3034</v>
       </c>
-      <c r="F72" t="s">
-        <v>3035</v>
-      </c>
       <c r="G72" t="s">
         <v>3036</v>
       </c>
@@ -20273,10 +19914,6 @@
       <c r="O72" t="s">
         <v>3093</v>
       </c>
-      <c r="P72" t="str">
-        <f t="shared" si="1"/>
-        <v>JONATAN LEONEL MAITRET GONZALEZ</v>
-      </c>
       <c r="Q72" t="s">
         <v>3094</v>
       </c>
@@ -20350,7 +19987,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>39</v>
       </c>
@@ -20366,9 +20003,6 @@
       <c r="E73" t="s">
         <v>3034</v>
       </c>
-      <c r="F73" t="s">
-        <v>3035</v>
-      </c>
       <c r="G73" t="s">
         <v>3036</v>
       </c>
@@ -20393,10 +20027,6 @@
       <c r="O73" t="s">
         <v>3100</v>
       </c>
-      <c r="P73" t="str">
-        <f t="shared" si="1"/>
-        <v>ANDRICK PATRICIO RUBIO HERNANDEZ</v>
-      </c>
       <c r="Q73" t="s">
         <v>3101</v>
       </c>
@@ -20470,7 +20100,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="74" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>39</v>
       </c>
@@ -20513,10 +20143,6 @@
       <c r="O74" t="s">
         <v>2299</v>
       </c>
-      <c r="P74" t="str">
-        <f t="shared" si="1"/>
-        <v>EDIEL ALBERTO OXTE RIVERA</v>
-      </c>
       <c r="Q74" t="s">
         <v>2300</v>
       </c>
@@ -20590,7 +20216,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="75" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>39</v>
       </c>
@@ -20606,9 +20232,6 @@
       <c r="E75" t="s">
         <v>2296</v>
       </c>
-      <c r="F75" t="s">
-        <v>2297</v>
-      </c>
       <c r="G75" t="s">
         <v>2298</v>
       </c>
@@ -20633,10 +20256,6 @@
       <c r="O75" t="s">
         <v>2307</v>
       </c>
-      <c r="P75" t="str">
-        <f t="shared" si="1"/>
-        <v>REYNA GUADALUPE HERNANDEZ RAMIREZ</v>
-      </c>
       <c r="Q75" t="s">
         <v>2308</v>
       </c>
@@ -20710,7 +20329,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="76" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -20753,10 +20372,6 @@
       <c r="O76" t="s">
         <v>1181</v>
       </c>
-      <c r="P76" t="str">
-        <f t="shared" si="1"/>
-        <v>CARLOS MONTES VIDAL</v>
-      </c>
       <c r="Q76" t="s">
         <v>1108</v>
       </c>
@@ -20830,7 +20445,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="77" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>39</v>
       </c>
@@ -20846,9 +20461,6 @@
       <c r="E77" t="s">
         <v>1177</v>
       </c>
-      <c r="F77" t="s">
-        <v>1178</v>
-      </c>
       <c r="G77" t="s">
         <v>1179</v>
       </c>
@@ -20873,10 +20485,6 @@
       <c r="O77" t="s">
         <v>1189</v>
       </c>
-      <c r="P77" t="str">
-        <f t="shared" si="1"/>
-        <v>DEMETRIO ESTRADA ZAVALA</v>
-      </c>
       <c r="Q77" t="s">
         <v>1190</v>
       </c>
@@ -20950,7 +20558,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="78" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>39</v>
       </c>
@@ -20966,9 +20574,6 @@
       <c r="E78" t="s">
         <v>1177</v>
       </c>
-      <c r="F78" t="s">
-        <v>1178</v>
-      </c>
       <c r="G78" t="s">
         <v>1179</v>
       </c>
@@ -20993,10 +20598,6 @@
       <c r="O78" t="s">
         <v>1195</v>
       </c>
-      <c r="P78" t="str">
-        <f t="shared" si="1"/>
-        <v>NATALIA SILVESTRE MARTINEZ</v>
-      </c>
       <c r="Q78" t="s">
         <v>1196</v>
       </c>
@@ -21070,7 +20671,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="79" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>39</v>
       </c>
@@ -21086,9 +20687,6 @@
       <c r="E79" t="s">
         <v>1177</v>
       </c>
-      <c r="F79" t="s">
-        <v>1178</v>
-      </c>
       <c r="G79" t="s">
         <v>1179</v>
       </c>
@@ -21113,10 +20711,6 @@
       <c r="O79" t="s">
         <v>1202</v>
       </c>
-      <c r="P79" t="str">
-        <f t="shared" si="1"/>
-        <v>EVARISTO SANTOS VELASQUEZ</v>
-      </c>
       <c r="Q79" t="s">
         <v>1203</v>
       </c>
@@ -21190,7 +20784,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="80" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -21206,9 +20800,6 @@
       <c r="E80" t="s">
         <v>1177</v>
       </c>
-      <c r="F80" t="s">
-        <v>1178</v>
-      </c>
       <c r="G80" t="s">
         <v>1179</v>
       </c>
@@ -21233,10 +20824,6 @@
       <c r="O80" t="s">
         <v>1210</v>
       </c>
-      <c r="P80" t="str">
-        <f t="shared" si="1"/>
-        <v>ANGEL ACOSTA CORONA</v>
-      </c>
       <c r="Q80" t="s">
         <v>529</v>
       </c>
@@ -21310,7 +20897,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -21326,9 +20913,6 @@
       <c r="E81" t="s">
         <v>1177</v>
       </c>
-      <c r="F81" t="s">
-        <v>1178</v>
-      </c>
       <c r="G81" t="s">
         <v>1179</v>
       </c>
@@ -21353,10 +20937,6 @@
       <c r="O81" t="s">
         <v>1216</v>
       </c>
-      <c r="P81" t="str">
-        <f t="shared" si="1"/>
-        <v>NEFTALI TOSCA JIMENEZ</v>
-      </c>
       <c r="Q81" t="s">
         <v>1217</v>
       </c>
@@ -21430,7 +21010,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="82" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -21446,9 +21026,6 @@
       <c r="E82" t="s">
         <v>1177</v>
       </c>
-      <c r="F82" t="s">
-        <v>1178</v>
-      </c>
       <c r="G82" t="s">
         <v>1179</v>
       </c>
@@ -21473,10 +21050,6 @@
       <c r="O82" t="s">
         <v>1223</v>
       </c>
-      <c r="P82" t="str">
-        <f t="shared" si="1"/>
-        <v>GRISELDA CORONADO DIAZ</v>
-      </c>
       <c r="Q82" t="s">
         <v>1224</v>
       </c>
@@ -21550,7 +21123,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="83" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -21566,9 +21139,6 @@
       <c r="E83" t="s">
         <v>1177</v>
       </c>
-      <c r="F83" t="s">
-        <v>1178</v>
-      </c>
       <c r="G83" t="s">
         <v>1179</v>
       </c>
@@ -21593,10 +21163,6 @@
       <c r="O83" t="s">
         <v>1230</v>
       </c>
-      <c r="P83" t="str">
-        <f t="shared" si="1"/>
-        <v>ALEXANDER ALONSO RUIZ ALBORES</v>
-      </c>
       <c r="Q83" t="s">
         <v>1231</v>
       </c>
@@ -21670,7 +21236,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="84" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -21686,9 +21252,6 @@
       <c r="E84" t="s">
         <v>1177</v>
       </c>
-      <c r="F84" t="s">
-        <v>1178</v>
-      </c>
       <c r="G84" t="s">
         <v>1179</v>
       </c>
@@ -21713,10 +21276,6 @@
       <c r="O84" t="s">
         <v>1237</v>
       </c>
-      <c r="P84" t="str">
-        <f t="shared" si="1"/>
-        <v>MARIBEL HERNANDEZ MARTINEZ</v>
-      </c>
       <c r="Q84" t="s">
         <v>1238</v>
       </c>
@@ -21790,7 +21349,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -21806,9 +21365,6 @@
       <c r="E85" t="s">
         <v>1177</v>
       </c>
-      <c r="F85" t="s">
-        <v>1178</v>
-      </c>
       <c r="G85" t="s">
         <v>1179</v>
       </c>
@@ -21833,10 +21389,6 @@
       <c r="O85" t="s">
         <v>1243</v>
       </c>
-      <c r="P85" t="str">
-        <f t="shared" si="1"/>
-        <v>ANA KAREN RIVERA ESTRADA</v>
-      </c>
       <c r="Q85" t="s">
         <v>1244</v>
       </c>
@@ -21910,7 +21462,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="86" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -21926,9 +21478,6 @@
       <c r="E86" t="s">
         <v>1177</v>
       </c>
-      <c r="F86" t="s">
-        <v>1178</v>
-      </c>
       <c r="G86" t="s">
         <v>1179</v>
       </c>
@@ -21953,10 +21502,6 @@
       <c r="O86" t="s">
         <v>1249</v>
       </c>
-      <c r="P86" t="str">
-        <f t="shared" si="1"/>
-        <v>NORA HILDA TELLEZ LOPEZ</v>
-      </c>
       <c r="Q86" t="s">
         <v>1250</v>
       </c>
@@ -22030,7 +21575,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="87" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -22046,9 +21591,6 @@
       <c r="E87" t="s">
         <v>1177</v>
       </c>
-      <c r="F87" t="s">
-        <v>1178</v>
-      </c>
       <c r="G87" t="s">
         <v>1179</v>
       </c>
@@ -22073,10 +21615,6 @@
       <c r="O87" t="s">
         <v>1256</v>
       </c>
-      <c r="P87" t="str">
-        <f t="shared" si="1"/>
-        <v>MARIA TERESA ESPINOSA RODRIGUEZ</v>
-      </c>
       <c r="Q87" t="s">
         <v>1257</v>
       </c>
@@ -22150,7 +21688,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="88" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -22166,9 +21704,6 @@
       <c r="E88" t="s">
         <v>1177</v>
       </c>
-      <c r="F88" t="s">
-        <v>1178</v>
-      </c>
       <c r="G88" t="s">
         <v>1179</v>
       </c>
@@ -22193,10 +21728,6 @@
       <c r="O88" t="s">
         <v>1263</v>
       </c>
-      <c r="P88" t="str">
-        <f t="shared" si="1"/>
-        <v>ROMAN MURGA TOLEDO</v>
-      </c>
       <c r="Q88" t="s">
         <v>476</v>
       </c>
@@ -22267,7 +21798,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="89" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -22283,9 +21814,6 @@
       <c r="E89" t="s">
         <v>1177</v>
       </c>
-      <c r="F89" t="s">
-        <v>1178</v>
-      </c>
       <c r="G89" t="s">
         <v>1179</v>
       </c>
@@ -22310,10 +21838,6 @@
       <c r="O89" t="s">
         <v>1269</v>
       </c>
-      <c r="P89" t="str">
-        <f t="shared" si="1"/>
-        <v>IDALIA HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q89" t="s">
         <v>1270</v>
       </c>
@@ -22387,7 +21911,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="90" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -22403,9 +21927,6 @@
       <c r="E90" t="s">
         <v>1177</v>
       </c>
-      <c r="F90" t="s">
-        <v>1178</v>
-      </c>
       <c r="G90" t="s">
         <v>1179</v>
       </c>
@@ -22430,10 +21951,6 @@
       <c r="O90" t="s">
         <v>1275</v>
       </c>
-      <c r="P90" t="str">
-        <f t="shared" si="1"/>
-        <v>ROSA CRUZ MENDOZA</v>
-      </c>
       <c r="Q90" t="s">
         <v>1276</v>
       </c>
@@ -22507,7 +22024,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -22523,9 +22040,6 @@
       <c r="E91" t="s">
         <v>1177</v>
       </c>
-      <c r="F91" t="s">
-        <v>1178</v>
-      </c>
       <c r="G91" t="s">
         <v>1179</v>
       </c>
@@ -22550,10 +22064,6 @@
       <c r="O91" t="s">
         <v>1281</v>
       </c>
-      <c r="P91" t="str">
-        <f t="shared" si="1"/>
-        <v>MARIA DE JESUS OCEJO CORTES</v>
-      </c>
       <c r="Q91" t="s">
         <v>1282</v>
       </c>
@@ -22627,7 +22137,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="92" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -22643,9 +22153,6 @@
       <c r="E92" t="s">
         <v>1177</v>
       </c>
-      <c r="F92" t="s">
-        <v>1178</v>
-      </c>
       <c r="G92" t="s">
         <v>1179</v>
       </c>
@@ -22670,10 +22177,6 @@
       <c r="O92" t="s">
         <v>1288</v>
       </c>
-      <c r="P92" t="str">
-        <f t="shared" si="1"/>
-        <v>ALEJANDRO MENDOZA AGUILAR</v>
-      </c>
       <c r="Q92" t="s">
         <v>215</v>
       </c>
@@ -22747,7 +22250,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="93" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -22763,9 +22266,6 @@
       <c r="E93" t="s">
         <v>1177</v>
       </c>
-      <c r="F93" t="s">
-        <v>1178</v>
-      </c>
       <c r="G93" t="s">
         <v>1179</v>
       </c>
@@ -22790,10 +22290,6 @@
       <c r="O93" t="s">
         <v>1293</v>
       </c>
-      <c r="P93" t="str">
-        <f t="shared" si="1"/>
-        <v>JAQUELIN HERNANDEZ AMARO</v>
-      </c>
       <c r="Q93" t="s">
         <v>1294</v>
       </c>
@@ -22867,7 +22363,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="94" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>39</v>
       </c>
@@ -22883,9 +22379,6 @@
       <c r="E94" t="s">
         <v>1177</v>
       </c>
-      <c r="F94" t="s">
-        <v>1178</v>
-      </c>
       <c r="G94" t="s">
         <v>1179</v>
       </c>
@@ -22910,10 +22403,6 @@
       <c r="O94" t="s">
         <v>1300</v>
       </c>
-      <c r="P94" t="str">
-        <f t="shared" si="1"/>
-        <v>ROCIO VELA DE LA ROSA</v>
-      </c>
       <c r="Q94" t="s">
         <v>1301</v>
       </c>
@@ -22987,7 +22476,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="95" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>39</v>
       </c>
@@ -23003,9 +22492,6 @@
       <c r="E95" t="s">
         <v>1177</v>
       </c>
-      <c r="F95" t="s">
-        <v>1178</v>
-      </c>
       <c r="G95" t="s">
         <v>1179</v>
       </c>
@@ -23030,10 +22516,6 @@
       <c r="O95" t="s">
         <v>1308</v>
       </c>
-      <c r="P95" t="str">
-        <f t="shared" si="1"/>
-        <v>RAMIRO DE JESUS ZAPO PUCHETA</v>
-      </c>
       <c r="Q95" t="s">
         <v>1309</v>
       </c>
@@ -23107,7 +22589,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="96" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>39</v>
       </c>
@@ -23123,9 +22605,6 @@
       <c r="E96" t="s">
         <v>1177</v>
       </c>
-      <c r="F96" t="s">
-        <v>1178</v>
-      </c>
       <c r="G96" t="s">
         <v>1179</v>
       </c>
@@ -23150,10 +22629,6 @@
       <c r="O96" t="s">
         <v>1316</v>
       </c>
-      <c r="P96" t="str">
-        <f t="shared" si="1"/>
-        <v>CARMEN JIMENEZ CONTRERAS</v>
-      </c>
       <c r="Q96" t="s">
         <v>1317</v>
       </c>
@@ -23227,7 +22702,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="97" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>39</v>
       </c>
@@ -23243,9 +22718,6 @@
       <c r="E97" t="s">
         <v>1177</v>
       </c>
-      <c r="F97" t="s">
-        <v>1178</v>
-      </c>
       <c r="G97" t="s">
         <v>1179</v>
       </c>
@@ -23270,10 +22742,6 @@
       <c r="O97" t="s">
         <v>1323</v>
       </c>
-      <c r="P97" t="str">
-        <f t="shared" si="1"/>
-        <v>VELIA NELLY ZAMORA GOMEZ</v>
-      </c>
       <c r="Q97" t="s">
         <v>1324</v>
       </c>
@@ -23347,7 +22815,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="98" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>39</v>
       </c>
@@ -23363,9 +22831,6 @@
       <c r="E98" t="s">
         <v>1177</v>
       </c>
-      <c r="F98" t="s">
-        <v>1178</v>
-      </c>
       <c r="G98" t="s">
         <v>1179</v>
       </c>
@@ -23390,10 +22855,6 @@
       <c r="O98" t="s">
         <v>1329</v>
       </c>
-      <c r="P98" t="str">
-        <f t="shared" si="1"/>
-        <v>JOSE JAVIER LOPEZ RAMOS</v>
-      </c>
       <c r="Q98" t="s">
         <v>1330</v>
       </c>
@@ -23467,7 +22928,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="99" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>39</v>
       </c>
@@ -23483,9 +22944,6 @@
       <c r="E99" t="s">
         <v>1177</v>
       </c>
-      <c r="F99" t="s">
-        <v>1178</v>
-      </c>
       <c r="G99" t="s">
         <v>1179</v>
       </c>
@@ -23510,10 +22968,6 @@
       <c r="O99" t="s">
         <v>1335</v>
       </c>
-      <c r="P99" t="str">
-        <f t="shared" si="1"/>
-        <v>MIGUEL BAEZA VIDAL</v>
-      </c>
       <c r="Q99" t="s">
         <v>1336</v>
       </c>
@@ -23587,7 +23041,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="100" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>39</v>
       </c>
@@ -23603,9 +23057,6 @@
       <c r="E100" t="s">
         <v>1177</v>
       </c>
-      <c r="F100" t="s">
-        <v>1178</v>
-      </c>
       <c r="G100" t="s">
         <v>1179</v>
       </c>
@@ -23630,10 +23081,6 @@
       <c r="O100" t="s">
         <v>1342</v>
       </c>
-      <c r="P100" t="str">
-        <f t="shared" si="1"/>
-        <v>PEDRO CRUZ AGUILAR</v>
-      </c>
       <c r="Q100" t="s">
         <v>1343</v>
       </c>
@@ -23707,7 +23154,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="101" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>39</v>
       </c>
@@ -23723,9 +23170,6 @@
       <c r="E101" t="s">
         <v>1177</v>
       </c>
-      <c r="F101" t="s">
-        <v>1178</v>
-      </c>
       <c r="G101" t="s">
         <v>1179</v>
       </c>
@@ -23750,10 +23194,6 @@
       <c r="O101" t="s">
         <v>1348</v>
       </c>
-      <c r="P101" t="str">
-        <f t="shared" si="1"/>
-        <v>NATAN MACIAS FLORES</v>
-      </c>
       <c r="Q101" t="s">
         <v>1349</v>
       </c>
@@ -23827,7 +23267,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="102" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>39</v>
       </c>
@@ -23843,9 +23283,6 @@
       <c r="E102" t="s">
         <v>1177</v>
       </c>
-      <c r="F102" t="s">
-        <v>1178</v>
-      </c>
       <c r="G102" t="s">
         <v>1179</v>
       </c>
@@ -23870,10 +23307,6 @@
       <c r="O102" t="s">
         <v>1355</v>
       </c>
-      <c r="P102" t="str">
-        <f t="shared" si="1"/>
-        <v>YESICA GUADALUPE VALENCIA ACOSTA</v>
-      </c>
       <c r="Q102" t="s">
         <v>1356</v>
       </c>
@@ -23947,7 +23380,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="103" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>39</v>
       </c>
@@ -23963,9 +23396,6 @@
       <c r="E103" t="s">
         <v>1177</v>
       </c>
-      <c r="F103" t="s">
-        <v>1178</v>
-      </c>
       <c r="G103" t="s">
         <v>1179</v>
       </c>
@@ -23990,10 +23420,6 @@
       <c r="O103" t="s">
         <v>1361</v>
       </c>
-      <c r="P103" t="str">
-        <f t="shared" si="1"/>
-        <v>AZENETH ALEJANDRA SANCHEZ RODRIGUEZ</v>
-      </c>
       <c r="Q103" t="s">
         <v>1362</v>
       </c>
@@ -24067,7 +23493,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="104" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>39</v>
       </c>
@@ -24083,9 +23509,6 @@
       <c r="E104" t="s">
         <v>1177</v>
       </c>
-      <c r="F104" t="s">
-        <v>1178</v>
-      </c>
       <c r="G104" t="s">
         <v>1179</v>
       </c>
@@ -24110,10 +23533,6 @@
       <c r="O104" t="s">
         <v>1367</v>
       </c>
-      <c r="P104" t="str">
-        <f t="shared" si="1"/>
-        <v>SILVIA MORALES RODRIGUEZ</v>
-      </c>
       <c r="Q104" t="s">
         <v>1368</v>
       </c>
@@ -24187,7 +23606,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="105" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>39</v>
       </c>
@@ -24203,9 +23622,6 @@
       <c r="E105" t="s">
         <v>1177</v>
       </c>
-      <c r="F105" t="s">
-        <v>1178</v>
-      </c>
       <c r="G105" t="s">
         <v>1179</v>
       </c>
@@ -24230,10 +23646,6 @@
       <c r="O105" t="s">
         <v>1373</v>
       </c>
-      <c r="P105" t="str">
-        <f t="shared" si="1"/>
-        <v>TERESA DE JESUS SANTIZO TORRES</v>
-      </c>
       <c r="Q105" t="s">
         <v>1374</v>
       </c>
@@ -24304,7 +23716,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="106" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>39</v>
       </c>
@@ -24320,9 +23732,6 @@
       <c r="E106" t="s">
         <v>1177</v>
       </c>
-      <c r="F106" t="s">
-        <v>1178</v>
-      </c>
       <c r="G106" t="s">
         <v>1179</v>
       </c>
@@ -24347,10 +23756,6 @@
       <c r="O106" t="s">
         <v>1379</v>
       </c>
-      <c r="P106" t="str">
-        <f t="shared" si="1"/>
-        <v>EFREN CORONADO BECERRA</v>
-      </c>
       <c r="Q106" t="s">
         <v>1380</v>
       </c>
@@ -24421,7 +23826,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="107" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>39</v>
       </c>
@@ -24437,9 +23842,6 @@
       <c r="E107" t="s">
         <v>1177</v>
       </c>
-      <c r="F107" t="s">
-        <v>1178</v>
-      </c>
       <c r="G107" t="s">
         <v>1179</v>
       </c>
@@ -24464,10 +23866,6 @@
       <c r="O107" t="s">
         <v>1385</v>
       </c>
-      <c r="P107" t="str">
-        <f t="shared" si="1"/>
-        <v>JOSE ANTONIO MEJIA CORTES</v>
-      </c>
       <c r="Q107" t="s">
         <v>1386</v>
       </c>
@@ -24541,7 +23939,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="108" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>39</v>
       </c>
@@ -24557,9 +23955,6 @@
       <c r="E108" t="s">
         <v>1177</v>
       </c>
-      <c r="F108" t="s">
-        <v>1178</v>
-      </c>
       <c r="G108" t="s">
         <v>1179</v>
       </c>
@@ -24584,10 +23979,6 @@
       <c r="O108" t="s">
         <v>1392</v>
       </c>
-      <c r="P108" t="str">
-        <f t="shared" si="1"/>
-        <v>ALMA IDOLINA NUÑEZ CEBREROS</v>
-      </c>
       <c r="Q108" t="s">
         <v>1393</v>
       </c>
@@ -24661,7 +24052,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>39</v>
       </c>
@@ -24677,9 +24068,6 @@
       <c r="E109" t="s">
         <v>1177</v>
       </c>
-      <c r="F109" t="s">
-        <v>1178</v>
-      </c>
       <c r="G109" t="s">
         <v>1179</v>
       </c>
@@ -24704,10 +24092,6 @@
       <c r="O109" t="s">
         <v>1401</v>
       </c>
-      <c r="P109" t="str">
-        <f t="shared" si="1"/>
-        <v>MARIA DEL ROSARIO GARCIA MENDOZA</v>
-      </c>
       <c r="Q109" t="s">
         <v>528</v>
       </c>
@@ -24781,7 +24165,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="110" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>39</v>
       </c>
@@ -24797,9 +24181,6 @@
       <c r="E110" t="s">
         <v>1177</v>
       </c>
-      <c r="F110" t="s">
-        <v>1178</v>
-      </c>
       <c r="G110" t="s">
         <v>1179</v>
       </c>
@@ -24824,10 +24205,6 @@
       <c r="O110" t="s">
         <v>1406</v>
       </c>
-      <c r="P110" t="str">
-        <f t="shared" si="1"/>
-        <v>LUIS AGUSTIN LAGUNA</v>
-      </c>
       <c r="Q110" t="s">
         <v>1407</v>
       </c>
@@ -24901,7 +24278,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="111" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>39</v>
       </c>
@@ -24917,9 +24294,6 @@
       <c r="E111" t="s">
         <v>1177</v>
       </c>
-      <c r="F111" t="s">
-        <v>1178</v>
-      </c>
       <c r="G111" t="s">
         <v>1179</v>
       </c>
@@ -24944,10 +24318,6 @@
       <c r="O111" t="s">
         <v>1413</v>
       </c>
-      <c r="P111" t="str">
-        <f t="shared" si="1"/>
-        <v>BLANCA ESTELA GALLEGOS CASILDO</v>
-      </c>
       <c r="Q111" t="s">
         <v>1414</v>
       </c>
@@ -25021,7 +24391,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="112" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>39</v>
       </c>
@@ -25037,9 +24407,6 @@
       <c r="E112" t="s">
         <v>1177</v>
       </c>
-      <c r="F112" t="s">
-        <v>1178</v>
-      </c>
       <c r="G112" t="s">
         <v>1179</v>
       </c>
@@ -25064,10 +24431,6 @@
       <c r="O112" t="s">
         <v>1420</v>
       </c>
-      <c r="P112" t="str">
-        <f t="shared" si="1"/>
-        <v>LUCIO BENJAMIN OTARULA GARCIA</v>
-      </c>
       <c r="Q112" t="s">
         <v>1421</v>
       </c>
@@ -25141,7 +24504,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="113" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>39</v>
       </c>
@@ -25157,9 +24520,6 @@
       <c r="E113" t="s">
         <v>1177</v>
       </c>
-      <c r="F113" t="s">
-        <v>1178</v>
-      </c>
       <c r="G113" t="s">
         <v>1179</v>
       </c>
@@ -25184,10 +24544,6 @@
       <c r="O113" t="s">
         <v>1427</v>
       </c>
-      <c r="P113" t="str">
-        <f t="shared" si="1"/>
-        <v>FELIPE PATRICIO LUNA</v>
-      </c>
       <c r="Q113" t="s">
         <v>1428</v>
       </c>
@@ -25261,7 +24617,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="114" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>39</v>
       </c>
@@ -25277,9 +24633,6 @@
       <c r="E114" t="s">
         <v>1177</v>
       </c>
-      <c r="F114" t="s">
-        <v>1178</v>
-      </c>
       <c r="G114" t="s">
         <v>1179</v>
       </c>
@@ -25304,10 +24657,6 @@
       <c r="O114" t="s">
         <v>1433</v>
       </c>
-      <c r="P114" t="str">
-        <f t="shared" si="1"/>
-        <v>JOANA GABRIEL CRISTOBAL</v>
-      </c>
       <c r="Q114" t="s">
         <v>1434</v>
       </c>
@@ -25381,7 +24730,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="115" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>39</v>
       </c>
@@ -25397,9 +24746,6 @@
       <c r="E115" t="s">
         <v>1177</v>
       </c>
-      <c r="F115" t="s">
-        <v>1178</v>
-      </c>
       <c r="G115" t="s">
         <v>1179</v>
       </c>
@@ -25423,10 +24769,6 @@
       </c>
       <c r="O115" t="s">
         <v>1440</v>
-      </c>
-      <c r="P115" t="str">
-        <f t="shared" si="1"/>
-        <v>OSCAR HERNANDEZ GALAN</v>
       </c>
       <c r="Q115" t="s">
         <v>825</v>
@@ -30373,7 +29715,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="158" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>39</v>
       </c>
@@ -30389,9 +29731,6 @@
       <c r="E158" t="s">
         <v>1177</v>
       </c>
-      <c r="F158" t="s">
-        <v>1178</v>
-      </c>
       <c r="G158" t="s">
         <v>1179</v>
       </c>
@@ -30416,10 +29755,6 @@
       <c r="O158" t="s">
         <v>1446</v>
       </c>
-      <c r="P158" t="str">
-        <f t="shared" ref="P158:P221" si="2">_xlfn.CONCAT(Q158," ",R158," ",S158)</f>
-        <v>MARI CARMEN ANTONIO PEREZ</v>
-      </c>
       <c r="Q158" t="s">
         <v>1447</v>
       </c>
@@ -30493,7 +29828,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="159" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>39</v>
       </c>
@@ -30509,9 +29844,6 @@
       <c r="E159" t="s">
         <v>1177</v>
       </c>
-      <c r="F159" t="s">
-        <v>1178</v>
-      </c>
       <c r="G159" t="s">
         <v>1179</v>
       </c>
@@ -30536,10 +29868,6 @@
       <c r="O159" t="s">
         <v>1452</v>
       </c>
-      <c r="P159" t="str">
-        <f t="shared" si="2"/>
-        <v>ROLANDO BARBOSA DE LA CRUZ</v>
-      </c>
       <c r="Q159" t="s">
         <v>329</v>
       </c>
@@ -30613,7 +29941,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="160" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>39</v>
       </c>
@@ -30629,9 +29957,6 @@
       <c r="E160" t="s">
         <v>1177</v>
       </c>
-      <c r="F160" t="s">
-        <v>1178</v>
-      </c>
       <c r="G160" t="s">
         <v>1179</v>
       </c>
@@ -30656,10 +29981,6 @@
       <c r="O160" t="s">
         <v>1459</v>
       </c>
-      <c r="P160" t="str">
-        <f t="shared" si="2"/>
-        <v>DANIA SARAIN FERIA GOMEZ</v>
-      </c>
       <c r="Q160" t="s">
         <v>1460</v>
       </c>
@@ -30733,7 +30054,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="161" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>39</v>
       </c>
@@ -30749,9 +30070,6 @@
       <c r="E161" t="s">
         <v>1177</v>
       </c>
-      <c r="F161" t="s">
-        <v>1178</v>
-      </c>
       <c r="G161" t="s">
         <v>1179</v>
       </c>
@@ -30776,10 +30094,6 @@
       <c r="O161" t="s">
         <v>1466</v>
       </c>
-      <c r="P161" t="str">
-        <f t="shared" si="2"/>
-        <v>ESTEBAN CORONADO CORONA</v>
-      </c>
       <c r="Q161" t="s">
         <v>441</v>
       </c>
@@ -30853,7 +30167,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="162" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>39</v>
       </c>
@@ -30869,9 +30183,6 @@
       <c r="E162" t="s">
         <v>1177</v>
       </c>
-      <c r="F162" t="s">
-        <v>1178</v>
-      </c>
       <c r="G162" t="s">
         <v>1179</v>
       </c>
@@ -30896,10 +30207,6 @@
       <c r="O162" t="s">
         <v>1471</v>
       </c>
-      <c r="P162" t="str">
-        <f t="shared" si="2"/>
-        <v>ABNER MACIAS FLORES</v>
-      </c>
       <c r="Q162" t="s">
         <v>1472</v>
       </c>
@@ -30973,7 +30280,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="163" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>39</v>
       </c>
@@ -30989,9 +30296,6 @@
       <c r="E163" t="s">
         <v>1177</v>
       </c>
-      <c r="F163" t="s">
-        <v>1178</v>
-      </c>
       <c r="G163" t="s">
         <v>1179</v>
       </c>
@@ -31016,10 +30320,6 @@
       <c r="O163" t="s">
         <v>1477</v>
       </c>
-      <c r="P163" t="str">
-        <f t="shared" si="2"/>
-        <v>GREGORIA MAGDALENA ZUÑIGA FUENTES</v>
-      </c>
       <c r="Q163" t="s">
         <v>1478</v>
       </c>
@@ -31093,7 +30393,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="164" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>39</v>
       </c>
@@ -31109,9 +30409,6 @@
       <c r="E164" t="s">
         <v>1177</v>
       </c>
-      <c r="F164" t="s">
-        <v>1178</v>
-      </c>
       <c r="G164" t="s">
         <v>1179</v>
       </c>
@@ -31136,10 +30433,6 @@
       <c r="O164" t="s">
         <v>1485</v>
       </c>
-      <c r="P164" t="str">
-        <f t="shared" si="2"/>
-        <v>JUAN REYES MUÑOZ CHAVEZ</v>
-      </c>
       <c r="Q164" t="s">
         <v>1486</v>
       </c>
@@ -31213,7 +30506,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="165" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>39</v>
       </c>
@@ -31229,9 +30522,6 @@
       <c r="E165" t="s">
         <v>1177</v>
       </c>
-      <c r="F165" t="s">
-        <v>1178</v>
-      </c>
       <c r="G165" t="s">
         <v>1179</v>
       </c>
@@ -31256,10 +30546,6 @@
       <c r="O165" t="s">
         <v>1492</v>
       </c>
-      <c r="P165" t="str">
-        <f t="shared" si="2"/>
-        <v>MARIA ISABEL MARTINEZ MARTINEZ</v>
-      </c>
       <c r="Q165" t="s">
         <v>1493</v>
       </c>
@@ -31333,7 +30619,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="166" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>39</v>
       </c>
@@ -31349,9 +30635,6 @@
       <c r="E166" t="s">
         <v>1177</v>
       </c>
-      <c r="F166" t="s">
-        <v>1178</v>
-      </c>
       <c r="G166" t="s">
         <v>1179</v>
       </c>
@@ -31376,10 +30659,6 @@
       <c r="O166" t="s">
         <v>1498</v>
       </c>
-      <c r="P166" t="str">
-        <f t="shared" si="2"/>
-        <v>LAMBERTO DE LA CRUZ GARCIA</v>
-      </c>
       <c r="Q166" t="s">
         <v>1499</v>
       </c>
@@ -31453,7 +30732,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="167" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>39</v>
       </c>
@@ -31469,9 +30748,6 @@
       <c r="E167" t="s">
         <v>1177</v>
       </c>
-      <c r="F167" t="s">
-        <v>1178</v>
-      </c>
       <c r="G167" t="s">
         <v>1179</v>
       </c>
@@ -31496,10 +30772,6 @@
       <c r="O167" t="s">
         <v>1504</v>
       </c>
-      <c r="P167" t="str">
-        <f t="shared" si="2"/>
-        <v>LUIS ANGEL HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q167" t="s">
         <v>1505</v>
       </c>
@@ -31573,7 +30845,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="168" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>39</v>
       </c>
@@ -31589,9 +30861,6 @@
       <c r="E168" t="s">
         <v>1177</v>
       </c>
-      <c r="F168" t="s">
-        <v>1178</v>
-      </c>
       <c r="G168" t="s">
         <v>1179</v>
       </c>
@@ -31616,10 +30885,6 @@
       <c r="O168" t="s">
         <v>1510</v>
       </c>
-      <c r="P168" t="str">
-        <f t="shared" si="2"/>
-        <v>JORGE EDUARDO HERNANDEZ GUTIERREZ</v>
-      </c>
       <c r="Q168" t="s">
         <v>1511</v>
       </c>
@@ -31693,7 +30958,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="169" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>39</v>
       </c>
@@ -31709,9 +30974,6 @@
       <c r="E169" t="s">
         <v>1177</v>
       </c>
-      <c r="F169" t="s">
-        <v>1178</v>
-      </c>
       <c r="G169" t="s">
         <v>1179</v>
       </c>
@@ -31736,10 +30998,6 @@
       <c r="O169" t="s">
         <v>1516</v>
       </c>
-      <c r="P169" t="str">
-        <f t="shared" si="2"/>
-        <v>CRISTOPHER GIOVANNI OVALLE ESPINOZA</v>
-      </c>
       <c r="Q169" t="s">
         <v>1517</v>
       </c>
@@ -31813,7 +31071,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="170" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>39</v>
       </c>
@@ -31829,9 +31087,6 @@
       <c r="E170" t="s">
         <v>1177</v>
       </c>
-      <c r="F170" t="s">
-        <v>1178</v>
-      </c>
       <c r="G170" t="s">
         <v>1179</v>
       </c>
@@ -31856,10 +31111,6 @@
       <c r="O170" t="s">
         <v>1522</v>
       </c>
-      <c r="P170" t="str">
-        <f t="shared" si="2"/>
-        <v>MARCOS DANIEL JIMENEZ LUNA</v>
-      </c>
       <c r="Q170" t="s">
         <v>1523</v>
       </c>
@@ -31933,7 +31184,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="171" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>39</v>
       </c>
@@ -31949,9 +31200,6 @@
       <c r="E171" t="s">
         <v>1177</v>
       </c>
-      <c r="F171" t="s">
-        <v>1178</v>
-      </c>
       <c r="G171" t="s">
         <v>1179</v>
       </c>
@@ -31976,10 +31224,6 @@
       <c r="O171" t="s">
         <v>1528</v>
       </c>
-      <c r="P171" t="str">
-        <f t="shared" si="2"/>
-        <v>CLAUDIA OJEDA CARCAÑO</v>
-      </c>
       <c r="Q171" t="s">
         <v>1529</v>
       </c>
@@ -32053,7 +31297,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="172" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>39</v>
       </c>
@@ -32069,9 +31313,6 @@
       <c r="E172" t="s">
         <v>1177</v>
       </c>
-      <c r="F172" t="s">
-        <v>1178</v>
-      </c>
       <c r="G172" t="s">
         <v>1179</v>
       </c>
@@ -32096,10 +31337,6 @@
       <c r="O172" t="s">
         <v>1536</v>
       </c>
-      <c r="P172" t="str">
-        <f t="shared" si="2"/>
-        <v>DANA MONSERRATH CARDENAS MURILLO</v>
-      </c>
       <c r="Q172" t="s">
         <v>1537</v>
       </c>
@@ -32173,7 +31410,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="173" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>39</v>
       </c>
@@ -32189,9 +31426,6 @@
       <c r="E173" t="s">
         <v>1177</v>
       </c>
-      <c r="F173" t="s">
-        <v>1178</v>
-      </c>
       <c r="G173" t="s">
         <v>1179</v>
       </c>
@@ -32216,10 +31450,6 @@
       <c r="O173" t="s">
         <v>1543</v>
       </c>
-      <c r="P173" t="str">
-        <f t="shared" si="2"/>
-        <v>DANIEL MARTINEZ HERNANDEZ</v>
-      </c>
       <c r="Q173" t="s">
         <v>68</v>
       </c>
@@ -32293,7 +31523,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="174" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -32309,9 +31539,6 @@
       <c r="E174" t="s">
         <v>1177</v>
       </c>
-      <c r="F174" t="s">
-        <v>1178</v>
-      </c>
       <c r="G174" t="s">
         <v>1179</v>
       </c>
@@ -32336,10 +31563,6 @@
       <c r="O174" t="s">
         <v>1548</v>
       </c>
-      <c r="P174" t="str">
-        <f t="shared" si="2"/>
-        <v>PEDRO XOLOT TOLEN</v>
-      </c>
       <c r="Q174" t="s">
         <v>1343</v>
       </c>
@@ -32413,7 +31636,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="175" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -32429,9 +31652,6 @@
       <c r="E175" t="s">
         <v>1177</v>
       </c>
-      <c r="F175" t="s">
-        <v>1178</v>
-      </c>
       <c r="G175" t="s">
         <v>1179</v>
       </c>
@@ -32456,10 +31676,6 @@
       <c r="O175" t="s">
         <v>1555</v>
       </c>
-      <c r="P175" t="str">
-        <f t="shared" si="2"/>
-        <v>OSVALDO GERONIMO REYNA</v>
-      </c>
       <c r="Q175" t="s">
         <v>1556</v>
       </c>
@@ -32533,7 +31749,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="176" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>39</v>
       </c>
@@ -32549,9 +31765,6 @@
       <c r="E176" t="s">
         <v>1177</v>
       </c>
-      <c r="F176" t="s">
-        <v>1178</v>
-      </c>
       <c r="G176" t="s">
         <v>1179</v>
       </c>
@@ -32576,10 +31789,6 @@
       <c r="O176" t="s">
         <v>1562</v>
       </c>
-      <c r="P176" t="str">
-        <f t="shared" si="2"/>
-        <v>JOCELYN DE JESUS REYNA IBARRA</v>
-      </c>
       <c r="Q176" t="s">
         <v>1563</v>
       </c>
@@ -32653,7 +31862,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="177" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -32669,9 +31878,6 @@
       <c r="E177" t="s">
         <v>1177</v>
       </c>
-      <c r="F177" t="s">
-        <v>1178</v>
-      </c>
       <c r="G177" t="s">
         <v>1179</v>
       </c>
@@ -32696,10 +31902,6 @@
       <c r="O177" t="s">
         <v>1569</v>
       </c>
-      <c r="P177" t="str">
-        <f t="shared" si="2"/>
-        <v>PROCESA MARQUEZ FELIX</v>
-      </c>
       <c r="Q177" t="s">
         <v>1570</v>
       </c>
@@ -32773,7 +31975,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="178" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>39</v>
       </c>
@@ -32789,9 +31991,6 @@
       <c r="E178" t="s">
         <v>1177</v>
       </c>
-      <c r="F178" t="s">
-        <v>1178</v>
-      </c>
       <c r="G178" t="s">
         <v>1179</v>
       </c>
@@ -32816,10 +32015,6 @@
       <c r="O178" t="s">
         <v>1576</v>
       </c>
-      <c r="P178" t="str">
-        <f t="shared" si="2"/>
-        <v>VALDEMAR DEL ANGEL GOMEZ</v>
-      </c>
       <c r="Q178" t="s">
         <v>1577</v>
       </c>
@@ -32893,7 +32088,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="179" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>39</v>
       </c>
@@ -32909,9 +32104,6 @@
       <c r="E179" t="s">
         <v>1177</v>
       </c>
-      <c r="F179" t="s">
-        <v>1178</v>
-      </c>
       <c r="G179" t="s">
         <v>1179</v>
       </c>
@@ -32936,10 +32128,6 @@
       <c r="O179" t="s">
         <v>1582</v>
       </c>
-      <c r="P179" t="str">
-        <f t="shared" si="2"/>
-        <v>ROMUALDO MARTINEZ SANTIAGO</v>
-      </c>
       <c r="Q179" t="s">
         <v>51</v>
       </c>
@@ -33013,7 +32201,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="180" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>39</v>
       </c>
@@ -33029,9 +32217,6 @@
       <c r="E180" t="s">
         <v>1177</v>
       </c>
-      <c r="F180" t="s">
-        <v>1178</v>
-      </c>
       <c r="G180" t="s">
         <v>1179</v>
       </c>
@@ -33056,10 +32241,6 @@
       <c r="O180" t="s">
         <v>1587</v>
       </c>
-      <c r="P180" t="str">
-        <f t="shared" si="2"/>
-        <v>JOSE ISRRAEL RAMIREZ GARCIA</v>
-      </c>
       <c r="Q180" t="s">
         <v>1588</v>
       </c>
@@ -33133,7 +32314,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="181" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>39</v>
       </c>
@@ -33149,9 +32330,6 @@
       <c r="E181" t="s">
         <v>1177</v>
       </c>
-      <c r="F181" t="s">
-        <v>1178</v>
-      </c>
       <c r="G181" t="s">
         <v>1179</v>
       </c>
@@ -33176,10 +32354,6 @@
       <c r="O181" t="s">
         <v>1593</v>
       </c>
-      <c r="P181" t="str">
-        <f t="shared" si="2"/>
-        <v>JENIFER HUERTA HERNANDEZ</v>
-      </c>
       <c r="Q181" t="s">
         <v>1594</v>
       </c>
@@ -33253,7 +32427,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="182" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>39</v>
       </c>
@@ -33269,9 +32443,6 @@
       <c r="E182" t="s">
         <v>1177</v>
       </c>
-      <c r="F182" t="s">
-        <v>1178</v>
-      </c>
       <c r="G182" t="s">
         <v>1179</v>
       </c>
@@ -33296,10 +32467,6 @@
       <c r="O182" t="s">
         <v>1600</v>
       </c>
-      <c r="P182" t="str">
-        <f t="shared" si="2"/>
-        <v>MARIA GUADALUPE GOMEZ PEREZ</v>
-      </c>
       <c r="Q182" t="s">
         <v>283</v>
       </c>
@@ -33373,7 +32540,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="183" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>39</v>
       </c>
@@ -33389,9 +32556,6 @@
       <c r="E183" t="s">
         <v>1177</v>
       </c>
-      <c r="F183" t="s">
-        <v>1178</v>
-      </c>
       <c r="G183" t="s">
         <v>1179</v>
       </c>
@@ -33416,10 +32580,6 @@
       <c r="O183" t="s">
         <v>1605</v>
       </c>
-      <c r="P183" t="str">
-        <f t="shared" si="2"/>
-        <v>ELIZABETH DEL CARMEN PEREZ AGUILAR</v>
-      </c>
       <c r="Q183" t="s">
         <v>1606</v>
       </c>
@@ -33493,7 +32653,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="184" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>39</v>
       </c>
@@ -33509,9 +32669,6 @@
       <c r="E184" t="s">
         <v>1177</v>
       </c>
-      <c r="F184" t="s">
-        <v>1178</v>
-      </c>
       <c r="G184" t="s">
         <v>1179</v>
       </c>
@@ -33536,10 +32693,6 @@
       <c r="O184" t="s">
         <v>1611</v>
       </c>
-      <c r="P184" t="str">
-        <f t="shared" si="2"/>
-        <v>NICOLAS QUISTIAN JACOBO</v>
-      </c>
       <c r="Q184" t="s">
         <v>1612</v>
       </c>
@@ -33613,7 +32766,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="185" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>39</v>
       </c>
@@ -33629,9 +32782,6 @@
       <c r="E185" t="s">
         <v>1177</v>
       </c>
-      <c r="F185" t="s">
-        <v>1178</v>
-      </c>
       <c r="G185" t="s">
         <v>1179</v>
       </c>
@@ -33656,10 +32806,6 @@
       <c r="O185" t="s">
         <v>1619</v>
       </c>
-      <c r="P185" t="str">
-        <f t="shared" si="2"/>
-        <v>EURIDICE GUADALUPE HERNANDEZ CAMPOS</v>
-      </c>
       <c r="Q185" t="s">
         <v>1620</v>
       </c>
@@ -33733,7 +32879,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="186" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>39</v>
       </c>
@@ -33749,9 +32895,6 @@
       <c r="E186" t="s">
         <v>1177</v>
       </c>
-      <c r="F186" t="s">
-        <v>1178</v>
-      </c>
       <c r="G186" t="s">
         <v>1179</v>
       </c>
@@ -33776,10 +32919,6 @@
       <c r="O186" t="s">
         <v>1625</v>
       </c>
-      <c r="P186" t="str">
-        <f t="shared" si="2"/>
-        <v>DAMIAN ANTONIO SILVERIO</v>
-      </c>
       <c r="Q186" t="s">
         <v>1626</v>
       </c>
@@ -33853,7 +32992,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="187" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>39</v>
       </c>
@@ -33869,9 +33008,6 @@
       <c r="E187" t="s">
         <v>1177</v>
       </c>
-      <c r="F187" t="s">
-        <v>1178</v>
-      </c>
       <c r="G187" t="s">
         <v>1179</v>
       </c>
@@ -33896,10 +33032,6 @@
       <c r="O187" t="s">
         <v>1632</v>
       </c>
-      <c r="P187" t="str">
-        <f t="shared" si="2"/>
-        <v>MARLEN DEL CARMEN MACHUCHO CARBALLO</v>
-      </c>
       <c r="Q187" t="s">
         <v>1633</v>
       </c>
@@ -33973,7 +33105,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="188" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>39</v>
       </c>
@@ -33989,9 +33121,6 @@
       <c r="E188" t="s">
         <v>1177</v>
       </c>
-      <c r="F188" t="s">
-        <v>1178</v>
-      </c>
       <c r="G188" t="s">
         <v>1179</v>
       </c>
@@ -34016,10 +33145,6 @@
       <c r="O188" t="s">
         <v>1640</v>
       </c>
-      <c r="P188" t="str">
-        <f t="shared" si="2"/>
-        <v>JESUS BARTOLO BERMUDES MEDINA</v>
-      </c>
       <c r="Q188" t="s">
         <v>1641</v>
       </c>
@@ -34093,7 +33218,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="189" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>39</v>
       </c>
@@ -34109,9 +33234,6 @@
       <c r="E189" t="s">
         <v>1177</v>
       </c>
-      <c r="F189" t="s">
-        <v>1178</v>
-      </c>
       <c r="G189" t="s">
         <v>1179</v>
       </c>
@@ -34136,10 +33258,6 @@
       <c r="O189" t="s">
         <v>1648</v>
       </c>
-      <c r="P189" t="str">
-        <f t="shared" si="2"/>
-        <v>MARIA ALEJANDRA GUERRERO CEPEDA</v>
-      </c>
       <c r="Q189" t="s">
         <v>1649</v>
       </c>
@@ -34213,7 +33331,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="190" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>39</v>
       </c>
@@ -34229,9 +33347,6 @@
       <c r="E190" t="s">
         <v>1177</v>
       </c>
-      <c r="F190" t="s">
-        <v>1178</v>
-      </c>
       <c r="G190" t="s">
         <v>1179</v>
       </c>
@@ -34256,10 +33371,6 @@
       <c r="O190" t="s">
         <v>1656</v>
       </c>
-      <c r="P190" t="str">
-        <f t="shared" si="2"/>
-        <v>ANAYELI MARQUEZ TELLEZ</v>
-      </c>
       <c r="Q190" t="s">
         <v>1657</v>
       </c>
@@ -34333,7 +33444,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="191" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>39</v>
       </c>
@@ -34349,9 +33460,6 @@
       <c r="E191" t="s">
         <v>1177</v>
       </c>
-      <c r="F191" t="s">
-        <v>1178</v>
-      </c>
       <c r="G191" t="s">
         <v>1179</v>
       </c>
@@ -34376,10 +33484,6 @@
       <c r="O191" t="s">
         <v>1662</v>
       </c>
-      <c r="P191" t="str">
-        <f t="shared" si="2"/>
-        <v>OLIVA PEREZ SANCHEZ</v>
-      </c>
       <c r="Q191" t="s">
         <v>1663</v>
       </c>
@@ -34453,7 +33557,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="192" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>39</v>
       </c>
@@ -34469,9 +33573,6 @@
       <c r="E192" t="s">
         <v>1177</v>
       </c>
-      <c r="F192" t="s">
-        <v>1178</v>
-      </c>
       <c r="G192" t="s">
         <v>1179</v>
       </c>
@@ -34496,10 +33597,6 @@
       <c r="O192" t="s">
         <v>1668</v>
       </c>
-      <c r="P192" t="str">
-        <f t="shared" si="2"/>
-        <v>ALMA DELIA LUNA SANCHEZ</v>
-      </c>
       <c r="Q192" t="s">
         <v>1038</v>
       </c>
@@ -34573,7 +33670,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="193" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>39</v>
       </c>
@@ -34589,9 +33686,6 @@
       <c r="E193" t="s">
         <v>1177</v>
       </c>
-      <c r="F193" t="s">
-        <v>1178</v>
-      </c>
       <c r="G193" t="s">
         <v>1179</v>
       </c>
@@ -34616,10 +33710,6 @@
       <c r="O193" t="s">
         <v>1673</v>
       </c>
-      <c r="P193" t="str">
-        <f t="shared" si="2"/>
-        <v>JESUS MANUEL ESPINOSA TREVIÑO</v>
-      </c>
       <c r="Q193" t="s">
         <v>729</v>
       </c>
@@ -34693,7 +33783,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="194" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>39</v>
       </c>
@@ -34709,9 +33799,6 @@
       <c r="E194" t="s">
         <v>1177</v>
       </c>
-      <c r="F194" t="s">
-        <v>1178</v>
-      </c>
       <c r="G194" t="s">
         <v>1179</v>
       </c>
@@ -34736,10 +33823,6 @@
       <c r="O194" t="s">
         <v>1678</v>
       </c>
-      <c r="P194" t="str">
-        <f t="shared" si="2"/>
-        <v>MONTSERRAT RUIZ ALFARO</v>
-      </c>
       <c r="Q194" t="s">
         <v>1679</v>
       </c>
@@ -34813,7 +33896,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="195" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>39</v>
       </c>
@@ -34829,9 +33912,6 @@
       <c r="E195" t="s">
         <v>1177</v>
       </c>
-      <c r="F195" t="s">
-        <v>1178</v>
-      </c>
       <c r="G195" t="s">
         <v>1179</v>
       </c>
@@ -34856,10 +33936,6 @@
       <c r="O195" t="s">
         <v>1684</v>
       </c>
-      <c r="P195" t="str">
-        <f t="shared" si="2"/>
-        <v>HORACIO DE LOS REYES LUNA</v>
-      </c>
       <c r="Q195" t="s">
         <v>1685</v>
       </c>
@@ -34933,7 +34009,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="196" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>39</v>
       </c>
@@ -34949,9 +34025,6 @@
       <c r="E196" t="s">
         <v>1177</v>
       </c>
-      <c r="F196" t="s">
-        <v>1178</v>
-      </c>
       <c r="G196" t="s">
         <v>1179</v>
       </c>
@@ -34976,10 +34049,6 @@
       <c r="O196" t="s">
         <v>1691</v>
       </c>
-      <c r="P196" t="str">
-        <f t="shared" si="2"/>
-        <v>MARIA DEL CARMEN DE LA CRUZ ARIAS</v>
-      </c>
       <c r="Q196" t="s">
         <v>223</v>
       </c>
@@ -35053,7 +34122,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="197" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>39</v>
       </c>
@@ -35069,9 +34138,6 @@
       <c r="E197" t="s">
         <v>1177</v>
       </c>
-      <c r="F197" t="s">
-        <v>1178</v>
-      </c>
       <c r="G197" t="s">
         <v>1179</v>
       </c>
@@ -35096,10 +34162,6 @@
       <c r="O197" t="s">
         <v>1697</v>
       </c>
-      <c r="P197" t="str">
-        <f t="shared" si="2"/>
-        <v>MARIA DEL ROSARIO BERMUDEZ MEDINA</v>
-      </c>
       <c r="Q197" t="s">
         <v>528</v>
       </c>
@@ -35173,7 +34235,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="198" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>39</v>
       </c>
@@ -35189,9 +34251,6 @@
       <c r="E198" t="s">
         <v>1177</v>
       </c>
-      <c r="F198" t="s">
-        <v>1178</v>
-      </c>
       <c r="G198" t="s">
         <v>1179</v>
       </c>
@@ -35216,10 +34275,6 @@
       <c r="O198" t="s">
         <v>1703</v>
       </c>
-      <c r="P198" t="str">
-        <f t="shared" si="2"/>
-        <v>ENRIQUETA RODRIGUEZ MARTINEZ</v>
-      </c>
       <c r="Q198" t="s">
         <v>1704</v>
       </c>
@@ -35293,7 +34348,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="199" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>39</v>
       </c>
@@ -35309,9 +34364,6 @@
       <c r="E199" t="s">
         <v>1177</v>
       </c>
-      <c r="F199" t="s">
-        <v>1178</v>
-      </c>
       <c r="G199" t="s">
         <v>1179</v>
       </c>
@@ -35336,10 +34388,6 @@
       <c r="O199" t="s">
         <v>1709</v>
       </c>
-      <c r="P199" t="str">
-        <f t="shared" si="2"/>
-        <v>JULIO CESAR BETANZOS HERNANDEZ</v>
-      </c>
       <c r="Q199" t="s">
         <v>259</v>
       </c>
@@ -35413,7 +34461,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="200" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>39</v>
       </c>
@@ -35429,9 +34477,6 @@
       <c r="E200" t="s">
         <v>1177</v>
       </c>
-      <c r="F200" t="s">
-        <v>1178</v>
-      </c>
       <c r="G200" t="s">
         <v>1179</v>
       </c>
@@ -35456,10 +34501,6 @@
       <c r="O200" t="s">
         <v>1715</v>
       </c>
-      <c r="P200" t="str">
-        <f t="shared" si="2"/>
-        <v>NICOLAS VAZQUEZ MARTINEZ</v>
-      </c>
       <c r="Q200" t="s">
         <v>1612</v>
       </c>
@@ -35533,7 +34574,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="201" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>39</v>
       </c>
@@ -35549,9 +34590,6 @@
       <c r="E201" t="s">
         <v>1177</v>
       </c>
-      <c r="F201" t="s">
-        <v>1178</v>
-      </c>
       <c r="G201" t="s">
         <v>1179</v>
       </c>
@@ -35576,10 +34614,6 @@
       <c r="O201" t="s">
         <v>1720</v>
       </c>
-      <c r="P201" t="str">
-        <f t="shared" si="2"/>
-        <v>JOAQUIN ISAI ROMERO MONREAL</v>
-      </c>
       <c r="Q201" t="s">
         <v>1721</v>
       </c>
@@ -35653,7 +34687,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="202" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>39</v>
       </c>
@@ -35669,9 +34703,6 @@
       <c r="E202" t="s">
         <v>1177</v>
       </c>
-      <c r="F202" t="s">
-        <v>1178</v>
-      </c>
       <c r="G202" t="s">
         <v>1179</v>
       </c>
@@ -35696,10 +34727,6 @@
       <c r="O202" t="s">
         <v>1727</v>
       </c>
-      <c r="P202" t="str">
-        <f t="shared" si="2"/>
-        <v>LUIS GERARDO DE LA CRUZ CORDOVA</v>
-      </c>
       <c r="Q202" t="s">
         <v>1728</v>
       </c>
@@ -35773,7 +34800,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="203" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>39</v>
       </c>
@@ -35789,9 +34816,6 @@
       <c r="E203" t="s">
         <v>1177</v>
       </c>
-      <c r="F203" t="s">
-        <v>1178</v>
-      </c>
       <c r="G203" t="s">
         <v>1179</v>
       </c>
@@ -35816,10 +34840,6 @@
       <c r="O203" t="s">
         <v>1733</v>
       </c>
-      <c r="P203" t="str">
-        <f t="shared" si="2"/>
-        <v>DULCE GABRIEL CRISTOBAL</v>
-      </c>
       <c r="Q203" t="s">
         <v>1734</v>
       </c>
@@ -35893,7 +34913,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="204" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>39</v>
       </c>
@@ -35909,9 +34929,6 @@
       <c r="E204" t="s">
         <v>1177</v>
       </c>
-      <c r="F204" t="s">
-        <v>1178</v>
-      </c>
       <c r="G204" t="s">
         <v>1179</v>
       </c>
@@ -35936,10 +34953,6 @@
       <c r="O204" t="s">
         <v>1739</v>
       </c>
-      <c r="P204" t="str">
-        <f t="shared" si="2"/>
-        <v>LUIS EDUARDO PEREZ CRUZ</v>
-      </c>
       <c r="Q204" t="s">
         <v>1740</v>
       </c>
@@ -36013,7 +35026,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="205" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>39</v>
       </c>
@@ -36029,9 +35042,6 @@
       <c r="E205" t="s">
         <v>1177</v>
       </c>
-      <c r="F205" t="s">
-        <v>1178</v>
-      </c>
       <c r="G205" t="s">
         <v>1179</v>
       </c>
@@ -36056,10 +35066,6 @@
       <c r="O205" t="s">
         <v>1745</v>
       </c>
-      <c r="P205" t="str">
-        <f t="shared" si="2"/>
-        <v>ALFREDO MATEOS DE LA CRUZ</v>
-      </c>
       <c r="Q205" t="s">
         <v>199</v>
       </c>
@@ -36133,7 +35139,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="206" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>39</v>
       </c>
@@ -36149,9 +35155,6 @@
       <c r="E206" t="s">
         <v>1177</v>
       </c>
-      <c r="F206" t="s">
-        <v>1178</v>
-      </c>
       <c r="G206" t="s">
         <v>1179</v>
       </c>
@@ -36176,10 +35179,6 @@
       <c r="O206" t="s">
         <v>1751</v>
       </c>
-      <c r="P206" t="str">
-        <f t="shared" si="2"/>
-        <v>FELIX VEGA HERNANDEZ</v>
-      </c>
       <c r="Q206" t="s">
         <v>1571</v>
       </c>
@@ -36253,7 +35252,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="207" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>39</v>
       </c>
@@ -36269,9 +35268,6 @@
       <c r="E207" t="s">
         <v>1177</v>
       </c>
-      <c r="F207" t="s">
-        <v>1178</v>
-      </c>
       <c r="G207" t="s">
         <v>1179</v>
       </c>
@@ -36296,10 +35292,6 @@
       <c r="O207" t="s">
         <v>1756</v>
       </c>
-      <c r="P207" t="str">
-        <f t="shared" si="2"/>
-        <v>MARTHA PEREGRINO CARDENAS</v>
-      </c>
       <c r="Q207" t="s">
         <v>1757</v>
       </c>
@@ -36373,7 +35365,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="208" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>39</v>
       </c>
@@ -36389,9 +35381,6 @@
       <c r="E208" t="s">
         <v>1177</v>
       </c>
-      <c r="F208" t="s">
-        <v>1178</v>
-      </c>
       <c r="G208" t="s">
         <v>1179</v>
       </c>
@@ -36416,10 +35405,6 @@
       <c r="O208" t="s">
         <v>1763</v>
       </c>
-      <c r="P208" t="str">
-        <f t="shared" si="2"/>
-        <v>MIRIAM CAZARES MARTINEZ</v>
-      </c>
       <c r="Q208" t="s">
         <v>1764</v>
       </c>
@@ -36493,7 +35478,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="209" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>39</v>
       </c>
@@ -36509,9 +35494,6 @@
       <c r="E209" t="s">
         <v>1177</v>
       </c>
-      <c r="F209" t="s">
-        <v>1178</v>
-      </c>
       <c r="G209" t="s">
         <v>1179</v>
       </c>
@@ -36536,10 +35518,6 @@
       <c r="O209" t="s">
         <v>1770</v>
       </c>
-      <c r="P209" t="str">
-        <f t="shared" si="2"/>
-        <v>ABEL SAGRERO GAMBOA</v>
-      </c>
       <c r="Q209" t="s">
         <v>1771</v>
       </c>
@@ -36613,7 +35591,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="210" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>39</v>
       </c>
@@ -36629,9 +35607,6 @@
       <c r="E210" t="s">
         <v>1177</v>
       </c>
-      <c r="F210" t="s">
-        <v>1178</v>
-      </c>
       <c r="G210" t="s">
         <v>1179</v>
       </c>
@@ -36656,10 +35631,6 @@
       <c r="O210" t="s">
         <v>1778</v>
       </c>
-      <c r="P210" t="str">
-        <f t="shared" si="2"/>
-        <v>SURI YAMILE SORIA MARQUEZ</v>
-      </c>
       <c r="Q210" t="s">
         <v>1779</v>
       </c>
@@ -36733,7 +35704,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="211" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>39</v>
       </c>
@@ -36749,9 +35720,6 @@
       <c r="E211" t="s">
         <v>1177</v>
       </c>
-      <c r="F211" t="s">
-        <v>1178</v>
-      </c>
       <c r="G211" t="s">
         <v>1179</v>
       </c>
@@ -36776,10 +35744,6 @@
       <c r="O211" t="s">
         <v>1785</v>
       </c>
-      <c r="P211" t="str">
-        <f t="shared" si="2"/>
-        <v>ANA LAURA RUIZ SUAREZ</v>
-      </c>
       <c r="Q211" t="s">
         <v>1786</v>
       </c>
@@ -36853,7 +35817,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="212" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>39</v>
       </c>
@@ -36869,9 +35833,6 @@
       <c r="E212" t="s">
         <v>1177</v>
       </c>
-      <c r="F212" t="s">
-        <v>1178</v>
-      </c>
       <c r="G212" t="s">
         <v>1179</v>
       </c>
@@ -36896,10 +35857,6 @@
       <c r="O212" t="s">
         <v>1791</v>
       </c>
-      <c r="P212" t="str">
-        <f t="shared" si="2"/>
-        <v>JOSE ALBERTO ESTRADA HERNANDEZ</v>
-      </c>
       <c r="Q212" t="s">
         <v>1792</v>
       </c>
@@ -36973,7 +35930,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="213" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>39</v>
       </c>
@@ -36989,9 +35946,6 @@
       <c r="E213" t="s">
         <v>1177</v>
       </c>
-      <c r="F213" t="s">
-        <v>1178</v>
-      </c>
       <c r="G213" t="s">
         <v>1179</v>
       </c>
@@ -37016,10 +35970,6 @@
       <c r="O213" t="s">
         <v>1797</v>
       </c>
-      <c r="P213" t="str">
-        <f t="shared" si="2"/>
-        <v>AZALEA BERENISSE MENDOZA PEREZ</v>
-      </c>
       <c r="Q213" t="s">
         <v>1798</v>
       </c>
@@ -37093,7 +36043,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="214" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>39</v>
       </c>
@@ -37109,9 +36059,6 @@
       <c r="E214" t="s">
         <v>1177</v>
       </c>
-      <c r="F214" t="s">
-        <v>1178</v>
-      </c>
       <c r="G214" t="s">
         <v>1179</v>
       </c>
@@ -37136,10 +36083,6 @@
       <c r="O214" t="s">
         <v>1803</v>
       </c>
-      <c r="P214" t="str">
-        <f t="shared" si="2"/>
-        <v>JENNY DE LA CRUZ DE LA CRUZ</v>
-      </c>
       <c r="Q214" t="s">
         <v>1804</v>
       </c>
@@ -37213,7 +36156,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="215" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>39</v>
       </c>
@@ -37229,9 +36172,6 @@
       <c r="E215" t="s">
         <v>1177</v>
       </c>
-      <c r="F215" t="s">
-        <v>1178</v>
-      </c>
       <c r="G215" t="s">
         <v>1179</v>
       </c>
@@ -37256,10 +36196,6 @@
       <c r="O215" t="s">
         <v>1809</v>
       </c>
-      <c r="P215" t="str">
-        <f t="shared" si="2"/>
-        <v>MARIA LIDIA JIMENEZ GOMEZ</v>
-      </c>
       <c r="Q215" t="s">
         <v>1810</v>
       </c>
@@ -37333,7 +36269,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="216" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>39</v>
       </c>
@@ -37349,9 +36285,6 @@
       <c r="E216" t="s">
         <v>1177</v>
       </c>
-      <c r="F216" t="s">
-        <v>1178</v>
-      </c>
       <c r="G216" t="s">
         <v>1179</v>
       </c>
@@ -37376,10 +36309,6 @@
       <c r="O216" t="s">
         <v>1815</v>
       </c>
-      <c r="P216" t="str">
-        <f t="shared" si="2"/>
-        <v>GAEL MORALES RODRIGUEZ</v>
-      </c>
       <c r="Q216" t="s">
         <v>1816</v>
       </c>
@@ -37453,7 +36382,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="217" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>39</v>
       </c>
@@ -37469,9 +36398,6 @@
       <c r="E217" t="s">
         <v>1177</v>
       </c>
-      <c r="F217" t="s">
-        <v>1178</v>
-      </c>
       <c r="G217" t="s">
         <v>1179</v>
       </c>
@@ -37496,10 +36422,6 @@
       <c r="O217" t="s">
         <v>1821</v>
       </c>
-      <c r="P217" t="str">
-        <f t="shared" si="2"/>
-        <v>SANDRA BERENICE NICOLAS BUSTOS</v>
-      </c>
       <c r="Q217" t="s">
         <v>1822</v>
       </c>
@@ -37573,7 +36495,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="218" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>39</v>
       </c>
@@ -37589,9 +36511,6 @@
       <c r="E218" t="s">
         <v>1177</v>
       </c>
-      <c r="F218" t="s">
-        <v>1178</v>
-      </c>
       <c r="G218" t="s">
         <v>1179</v>
       </c>
@@ -37616,10 +36535,6 @@
       <c r="O218" t="s">
         <v>1827</v>
       </c>
-      <c r="P218" t="str">
-        <f t="shared" si="2"/>
-        <v>MIRIAM BERSABE PEREZ CRUZ</v>
-      </c>
       <c r="Q218" t="s">
         <v>1828</v>
       </c>
@@ -37693,7 +36608,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="219" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>39</v>
       </c>
@@ -37709,9 +36624,6 @@
       <c r="E219" t="s">
         <v>1177</v>
       </c>
-      <c r="F219" t="s">
-        <v>1178</v>
-      </c>
       <c r="G219" t="s">
         <v>1179</v>
       </c>
@@ -37736,10 +36648,6 @@
       <c r="O219" t="s">
         <v>1833</v>
       </c>
-      <c r="P219" t="str">
-        <f t="shared" si="2"/>
-        <v>HEBERTO GONZALEZ RAMIREZ</v>
-      </c>
       <c r="Q219" t="s">
         <v>1834</v>
       </c>
@@ -37813,7 +36721,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="220" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>39</v>
       </c>
@@ -37829,9 +36737,6 @@
       <c r="E220" t="s">
         <v>1177</v>
       </c>
-      <c r="F220" t="s">
-        <v>1178</v>
-      </c>
       <c r="G220" t="s">
         <v>1179</v>
       </c>
@@ -37856,10 +36761,6 @@
       <c r="O220" t="s">
         <v>1839</v>
       </c>
-      <c r="P220" t="str">
-        <f t="shared" si="2"/>
-        <v>LEYDI DIANA LEON BRITO</v>
-      </c>
       <c r="Q220" t="s">
         <v>1840</v>
       </c>
@@ -37933,7 +36834,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="221" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>39</v>
       </c>
@@ -37949,9 +36850,6 @@
       <c r="E221" t="s">
         <v>1177</v>
       </c>
-      <c r="F221" t="s">
-        <v>1178</v>
-      </c>
       <c r="G221" t="s">
         <v>1179</v>
       </c>
@@ -37976,10 +36874,6 @@
       <c r="O221" t="s">
         <v>1847</v>
       </c>
-      <c r="P221" t="str">
-        <f t="shared" si="2"/>
-        <v>CAMILA ARACELY MENDOZA CRISTERNA</v>
-      </c>
       <c r="Q221" t="s">
         <v>1848</v>
       </c>
@@ -38053,7 +36947,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="222" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>39</v>
       </c>
@@ -38069,9 +36963,6 @@
       <c r="E222" t="s">
         <v>1177</v>
       </c>
-      <c r="F222" t="s">
-        <v>1178</v>
-      </c>
       <c r="G222" t="s">
         <v>1179</v>
       </c>
@@ -38096,10 +36987,6 @@
       <c r="O222" t="s">
         <v>1854</v>
       </c>
-      <c r="P222" t="str">
-        <f t="shared" ref="P222:P278" si="3">_xlfn.CONCAT(Q222," ",R222," ",S222)</f>
-        <v>JOSE LORENZO RAMIREZ GOMEZ</v>
-      </c>
       <c r="Q222" t="s">
         <v>1855</v>
       </c>
@@ -38173,7 +37060,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="223" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>39</v>
       </c>
@@ -38189,9 +37076,6 @@
       <c r="E223" t="s">
         <v>1177</v>
       </c>
-      <c r="F223" t="s">
-        <v>1178</v>
-      </c>
       <c r="G223" t="s">
         <v>1179</v>
       </c>
@@ -38216,10 +37100,6 @@
       <c r="O223" t="s">
         <v>1860</v>
       </c>
-      <c r="P223" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">FRANCISCO MANUEL SOSA </v>
-      </c>
       <c r="Q223" t="s">
         <v>1861</v>
       </c>
@@ -38290,7 +37170,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="224" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>39</v>
       </c>
@@ -38306,9 +37186,6 @@
       <c r="E224" t="s">
         <v>1177</v>
       </c>
-      <c r="F224" t="s">
-        <v>1178</v>
-      </c>
       <c r="G224" t="s">
         <v>1179</v>
       </c>
@@ -38333,10 +37210,6 @@
       <c r="O224" t="s">
         <v>1867</v>
       </c>
-      <c r="P224" t="str">
-        <f t="shared" si="3"/>
-        <v>PERLA GUTIERREZ HERNANDEZ</v>
-      </c>
       <c r="Q224" t="s">
         <v>1868</v>
       </c>
@@ -38410,7 +37283,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="225" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>39</v>
       </c>
@@ -38426,9 +37299,6 @@
       <c r="E225" t="s">
         <v>1177</v>
       </c>
-      <c r="F225" t="s">
-        <v>1178</v>
-      </c>
       <c r="G225" t="s">
         <v>1179</v>
       </c>
@@ -38453,10 +37323,6 @@
       <c r="O225" t="s">
         <v>1873</v>
       </c>
-      <c r="P225" t="str">
-        <f t="shared" si="3"/>
-        <v>ESMERALDA RODRIGUEZ MARTINEZ</v>
-      </c>
       <c r="Q225" t="s">
         <v>522</v>
       </c>
@@ -38530,7 +37396,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="226" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>39</v>
       </c>
@@ -38546,9 +37412,6 @@
       <c r="E226" t="s">
         <v>1177</v>
       </c>
-      <c r="F226" t="s">
-        <v>1178</v>
-      </c>
       <c r="G226" t="s">
         <v>1179</v>
       </c>
@@ -38573,10 +37436,6 @@
       <c r="O226" t="s">
         <v>1878</v>
       </c>
-      <c r="P226" t="str">
-        <f t="shared" si="3"/>
-        <v>SANDRA BALDERAS RIVERA</v>
-      </c>
       <c r="Q226" t="s">
         <v>1879</v>
       </c>
@@ -38650,7 +37509,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="227" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>39</v>
       </c>
@@ -38666,9 +37525,6 @@
       <c r="E227" t="s">
         <v>1177</v>
       </c>
-      <c r="F227" t="s">
-        <v>1178</v>
-      </c>
       <c r="G227" t="s">
         <v>1179</v>
       </c>
@@ -38693,10 +37549,6 @@
       <c r="O227" t="s">
         <v>1885</v>
       </c>
-      <c r="P227" t="str">
-        <f t="shared" si="3"/>
-        <v>YANETH MIGUEL GUTIERREZ</v>
-      </c>
       <c r="Q227" t="s">
         <v>1886</v>
       </c>
@@ -38770,7 +37622,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="228" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>39</v>
       </c>
@@ -38786,9 +37638,6 @@
       <c r="E228" t="s">
         <v>1177</v>
       </c>
-      <c r="F228" t="s">
-        <v>1178</v>
-      </c>
       <c r="G228" t="s">
         <v>1179</v>
       </c>
@@ -38813,10 +37662,6 @@
       <c r="O228" t="s">
         <v>1891</v>
       </c>
-      <c r="P228" t="str">
-        <f t="shared" si="3"/>
-        <v>RUBI SUSANA PERALTA CASTILLO</v>
-      </c>
       <c r="Q228" t="s">
         <v>1892</v>
       </c>
@@ -38890,7 +37735,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="229" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>39</v>
       </c>
@@ -38906,9 +37751,6 @@
       <c r="E229" t="s">
         <v>1177</v>
       </c>
-      <c r="F229" t="s">
-        <v>1178</v>
-      </c>
       <c r="G229" t="s">
         <v>1179</v>
       </c>
@@ -38933,10 +37775,6 @@
       <c r="O229" t="s">
         <v>1899</v>
       </c>
-      <c r="P229" t="str">
-        <f t="shared" si="3"/>
-        <v>JOCELYN REYES PADUANO</v>
-      </c>
       <c r="Q229" t="s">
         <v>1900</v>
       </c>
@@ -39010,7 +37848,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="230" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>39</v>
       </c>
@@ -39026,9 +37864,6 @@
       <c r="E230" t="s">
         <v>1177</v>
       </c>
-      <c r="F230" t="s">
-        <v>1178</v>
-      </c>
       <c r="G230" t="s">
         <v>1179</v>
       </c>
@@ -39053,10 +37888,6 @@
       <c r="O230" t="s">
         <v>1906</v>
       </c>
-      <c r="P230" t="str">
-        <f t="shared" si="3"/>
-        <v>MARCO ANTONIO CHAIRE CAMARA</v>
-      </c>
       <c r="Q230" t="s">
         <v>864</v>
       </c>
@@ -39130,7 +37961,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="231" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>39</v>
       </c>
@@ -39146,9 +37977,6 @@
       <c r="E231" t="s">
         <v>1177</v>
       </c>
-      <c r="F231" t="s">
-        <v>1178</v>
-      </c>
       <c r="G231" t="s">
         <v>1179</v>
       </c>
@@ -39173,10 +38001,6 @@
       <c r="O231" t="s">
         <v>1913</v>
       </c>
-      <c r="P231" t="str">
-        <f t="shared" si="3"/>
-        <v>NELVIA PEREZ DIAZ</v>
-      </c>
       <c r="Q231" t="s">
         <v>1914</v>
       </c>
@@ -39250,7 +38074,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="232" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>39</v>
       </c>
@@ -39266,9 +38090,6 @@
       <c r="E232" t="s">
         <v>1177</v>
       </c>
-      <c r="F232" t="s">
-        <v>1178</v>
-      </c>
       <c r="G232" t="s">
         <v>1179</v>
       </c>
@@ -39293,10 +38114,6 @@
       <c r="O232" t="s">
         <v>1919</v>
       </c>
-      <c r="P232" t="str">
-        <f t="shared" si="3"/>
-        <v>NIZA YARELY VILLEGAS CHIHUAHUA</v>
-      </c>
       <c r="Q232" t="s">
         <v>1920</v>
       </c>
@@ -39370,7 +38187,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="233" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>39</v>
       </c>
@@ -39386,9 +38203,6 @@
       <c r="E233" t="s">
         <v>1177</v>
       </c>
-      <c r="F233" t="s">
-        <v>1178</v>
-      </c>
       <c r="G233" t="s">
         <v>1179</v>
       </c>
@@ -39413,10 +38227,6 @@
       <c r="O233" t="s">
         <v>1927</v>
       </c>
-      <c r="P233" t="str">
-        <f t="shared" si="3"/>
-        <v>EMETERIO MARTINEZ ESTEBAN</v>
-      </c>
       <c r="Q233" t="s">
         <v>1928</v>
       </c>
@@ -39490,7 +38300,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="234" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>39</v>
       </c>
@@ -39506,9 +38316,6 @@
       <c r="E234" t="s">
         <v>1177</v>
       </c>
-      <c r="F234" t="s">
-        <v>1178</v>
-      </c>
       <c r="G234" t="s">
         <v>1179</v>
       </c>
@@ -39533,10 +38340,6 @@
       <c r="O234" t="s">
         <v>1933</v>
       </c>
-      <c r="P234" t="str">
-        <f t="shared" si="3"/>
-        <v>LUIS ANTONIO LOPEZ CABRERA</v>
-      </c>
       <c r="Q234" t="s">
         <v>1934</v>
       </c>
@@ -39610,7 +38413,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="235" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>39</v>
       </c>
@@ -39626,9 +38429,6 @@
       <c r="E235" t="s">
         <v>1177</v>
       </c>
-      <c r="F235" t="s">
-        <v>1178</v>
-      </c>
       <c r="G235" t="s">
         <v>1179</v>
       </c>
@@ -39653,10 +38453,6 @@
       <c r="O235" t="s">
         <v>1940</v>
       </c>
-      <c r="P235" t="str">
-        <f t="shared" si="3"/>
-        <v>ELIZABETH MIGUEL CRUZ</v>
-      </c>
       <c r="Q235" t="s">
         <v>771</v>
       </c>
@@ -39730,7 +38526,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="236" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>39</v>
       </c>
@@ -39746,9 +38542,6 @@
       <c r="E236" t="s">
         <v>1177</v>
       </c>
-      <c r="F236" t="s">
-        <v>1178</v>
-      </c>
       <c r="G236" t="s">
         <v>1179</v>
       </c>
@@ -39773,10 +38566,6 @@
       <c r="O236" t="s">
         <v>1945</v>
       </c>
-      <c r="P236" t="str">
-        <f t="shared" si="3"/>
-        <v>LEYDI ARACELI BERNAL CANUTO</v>
-      </c>
       <c r="Q236" t="s">
         <v>1946</v>
       </c>
@@ -39850,7 +38639,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="237" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>39</v>
       </c>
@@ -39866,9 +38655,6 @@
       <c r="E237" t="s">
         <v>1177</v>
       </c>
-      <c r="F237" t="s">
-        <v>1178</v>
-      </c>
       <c r="G237" t="s">
         <v>1179</v>
       </c>
@@ -39893,10 +38679,6 @@
       <c r="O237" t="s">
         <v>1953</v>
       </c>
-      <c r="P237" t="str">
-        <f t="shared" si="3"/>
-        <v>CECILIA LARA HERNANDEZ</v>
-      </c>
       <c r="Q237" t="s">
         <v>1954</v>
       </c>
@@ -39970,7 +38752,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="238" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>39</v>
       </c>
@@ -39986,9 +38768,6 @@
       <c r="E238" t="s">
         <v>1177</v>
       </c>
-      <c r="F238" t="s">
-        <v>1178</v>
-      </c>
       <c r="G238" t="s">
         <v>1179</v>
       </c>
@@ -40013,10 +38792,6 @@
       <c r="O238" t="s">
         <v>1959</v>
       </c>
-      <c r="P238" t="str">
-        <f t="shared" si="3"/>
-        <v>ADILENE YESENIA PIÑON CALDERON</v>
-      </c>
       <c r="Q238" t="s">
         <v>1960</v>
       </c>
@@ -40090,7 +38865,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="239" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>39</v>
       </c>
@@ -40133,10 +38908,6 @@
       <c r="O239" t="s">
         <v>3159</v>
       </c>
-      <c r="P239" t="str">
-        <f t="shared" si="3"/>
-        <v>AZUCENA HERNANDEZ RODRIGUEZ</v>
-      </c>
       <c r="Q239" t="s">
         <v>3160</v>
       </c>
@@ -40210,7 +38981,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="240" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>39</v>
       </c>
@@ -40253,10 +39024,6 @@
       <c r="O240" t="s">
         <v>2434</v>
       </c>
-      <c r="P240" t="str">
-        <f t="shared" si="3"/>
-        <v>PERLA EDITH TOVAR ANGELES</v>
-      </c>
       <c r="Q240" t="s">
         <v>2435</v>
       </c>
@@ -40330,7 +39097,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="241" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>39</v>
       </c>
@@ -40346,9 +39113,6 @@
       <c r="E241" t="s">
         <v>2431</v>
       </c>
-      <c r="F241" t="s">
-        <v>2432</v>
-      </c>
       <c r="G241" t="s">
         <v>2433</v>
       </c>
@@ -40373,10 +39137,6 @@
       <c r="O241" t="s">
         <v>2441</v>
       </c>
-      <c r="P241" t="str">
-        <f t="shared" si="3"/>
-        <v>BRAYAN CARDONA SOLIS</v>
-      </c>
       <c r="Q241" t="s">
         <v>2442</v>
       </c>
@@ -40450,7 +39210,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="242" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>39</v>
       </c>
@@ -40466,9 +39226,6 @@
       <c r="E242" t="s">
         <v>2431</v>
       </c>
-      <c r="F242" t="s">
-        <v>2432</v>
-      </c>
       <c r="G242" t="s">
         <v>2433</v>
       </c>
@@ -40493,10 +39250,6 @@
       <c r="O242" t="s">
         <v>2448</v>
       </c>
-      <c r="P242" t="str">
-        <f t="shared" si="3"/>
-        <v>FABIAN ARIAS BOLON</v>
-      </c>
       <c r="Q242" t="s">
         <v>2449</v>
       </c>
@@ -40570,7 +39323,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="243" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>39</v>
       </c>
@@ -40586,9 +39339,6 @@
       <c r="E243" t="s">
         <v>2431</v>
       </c>
-      <c r="F243" t="s">
-        <v>2432</v>
-      </c>
       <c r="G243" t="s">
         <v>2433</v>
       </c>
@@ -40613,10 +39363,6 @@
       <c r="O243" t="s">
         <v>2455</v>
       </c>
-      <c r="P243" t="str">
-        <f t="shared" si="3"/>
-        <v>MIGUEL ANGEL HERNANDEZ TREJO</v>
-      </c>
       <c r="Q243" t="s">
         <v>2456</v>
       </c>
@@ -40690,7 +39436,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="244" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>39</v>
       </c>
@@ -40706,9 +39452,6 @@
       <c r="E244" t="s">
         <v>2431</v>
       </c>
-      <c r="F244" t="s">
-        <v>2432</v>
-      </c>
       <c r="G244" t="s">
         <v>2433</v>
       </c>
@@ -40733,10 +39476,6 @@
       <c r="O244" t="s">
         <v>2462</v>
       </c>
-      <c r="P244" t="str">
-        <f t="shared" si="3"/>
-        <v>GENOVEVA SANCHEZ RIVERA</v>
-      </c>
       <c r="Q244" t="s">
         <v>2463</v>
       </c>
@@ -40810,7 +39549,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="245" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>39</v>
       </c>
@@ -40826,9 +39565,6 @@
       <c r="E245" t="s">
         <v>2431</v>
       </c>
-      <c r="F245" t="s">
-        <v>2432</v>
-      </c>
       <c r="G245" t="s">
         <v>2433</v>
       </c>
@@ -40853,10 +39589,6 @@
       <c r="O245" t="s">
         <v>2468</v>
       </c>
-      <c r="P245" t="str">
-        <f t="shared" si="3"/>
-        <v>JUAN LUIS RUIZ VELAZQUEZ</v>
-      </c>
       <c r="Q245" t="s">
         <v>2469</v>
       </c>
@@ -40927,7 +39659,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="246" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>39</v>
       </c>
@@ -40943,9 +39675,6 @@
       <c r="E246" t="s">
         <v>2431</v>
       </c>
-      <c r="F246" t="s">
-        <v>2432</v>
-      </c>
       <c r="G246" t="s">
         <v>2433</v>
       </c>
@@ -40970,10 +39699,6 @@
       <c r="O246" t="s">
         <v>2473</v>
       </c>
-      <c r="P246" t="str">
-        <f t="shared" si="3"/>
-        <v>FRANCISCO RICARDO FERNANDEZ PALMAREZ</v>
-      </c>
       <c r="Q246" t="s">
         <v>2474</v>
       </c>
@@ -41047,7 +39772,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="247" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>39</v>
       </c>
@@ -41063,9 +39788,6 @@
       <c r="E247" t="s">
         <v>2431</v>
       </c>
-      <c r="F247" t="s">
-        <v>2432</v>
-      </c>
       <c r="G247" t="s">
         <v>2433</v>
       </c>
@@ -41090,10 +39812,6 @@
       <c r="O247" t="s">
         <v>2480</v>
       </c>
-      <c r="P247" t="str">
-        <f t="shared" si="3"/>
-        <v>MARIO ARTURO PERALES ARVIZU</v>
-      </c>
       <c r="Q247" t="s">
         <v>2481</v>
       </c>
@@ -41167,7 +39885,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="248" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>39</v>
       </c>
@@ -41183,9 +39901,6 @@
       <c r="E248" t="s">
         <v>2431</v>
       </c>
-      <c r="F248" t="s">
-        <v>2432</v>
-      </c>
       <c r="G248" t="s">
         <v>2433</v>
       </c>
@@ -41210,10 +39925,6 @@
       <c r="O248" t="s">
         <v>2488</v>
       </c>
-      <c r="P248" t="str">
-        <f t="shared" si="3"/>
-        <v>JONAS CANDELARIO VARGAS</v>
-      </c>
       <c r="Q248" t="s">
         <v>2489</v>
       </c>
@@ -41287,7 +39998,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="249" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>39</v>
       </c>
@@ -41303,9 +40014,6 @@
       <c r="E249" t="s">
         <v>2431</v>
       </c>
-      <c r="F249" t="s">
-        <v>2432</v>
-      </c>
       <c r="G249" t="s">
         <v>2433</v>
       </c>
@@ -41330,10 +40038,6 @@
       <c r="O249" t="s">
         <v>2496</v>
       </c>
-      <c r="P249" t="str">
-        <f t="shared" si="3"/>
-        <v>VOGAR ZAHID NABARRETE HERNANDEZ</v>
-      </c>
       <c r="Q249" t="s">
         <v>2497</v>
       </c>
@@ -41407,7 +40111,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="250" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>39</v>
       </c>
@@ -41423,9 +40127,6 @@
       <c r="E250" t="s">
         <v>2431</v>
       </c>
-      <c r="F250" t="s">
-        <v>2432</v>
-      </c>
       <c r="G250" t="s">
         <v>2433</v>
       </c>
@@ -41450,10 +40151,6 @@
       <c r="O250" t="s">
         <v>2503</v>
       </c>
-      <c r="P250" t="str">
-        <f t="shared" si="3"/>
-        <v>ISAIN CANDELARIO VARGAS</v>
-      </c>
       <c r="Q250" t="s">
         <v>2504</v>
       </c>
@@ -41527,7 +40224,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="251" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>39</v>
       </c>
@@ -41543,9 +40240,6 @@
       <c r="E251" t="s">
         <v>2431</v>
       </c>
-      <c r="F251" t="s">
-        <v>2432</v>
-      </c>
       <c r="G251" t="s">
         <v>2433</v>
       </c>
@@ -41570,10 +40264,6 @@
       <c r="O251" t="s">
         <v>2509</v>
       </c>
-      <c r="P251" t="str">
-        <f t="shared" si="3"/>
-        <v>CARLOS ORTIZ CARREON</v>
-      </c>
       <c r="Q251" t="s">
         <v>1108</v>
       </c>
@@ -41647,7 +40337,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="252" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>39</v>
       </c>
@@ -41663,9 +40353,6 @@
       <c r="E252" t="s">
         <v>2431</v>
       </c>
-      <c r="F252" t="s">
-        <v>2432</v>
-      </c>
       <c r="G252" t="s">
         <v>2433</v>
       </c>
@@ -41690,10 +40377,6 @@
       <c r="O252" t="s">
         <v>2516</v>
       </c>
-      <c r="P252" t="str">
-        <f t="shared" si="3"/>
-        <v>SIXTO ALBERTO CRUZ GUTIERREZ</v>
-      </c>
       <c r="Q252" t="s">
         <v>2517</v>
       </c>
@@ -41767,7 +40450,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="253" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>39</v>
       </c>
@@ -41783,9 +40466,6 @@
       <c r="E253" t="s">
         <v>2431</v>
       </c>
-      <c r="F253" t="s">
-        <v>2432</v>
-      </c>
       <c r="G253" t="s">
         <v>2433</v>
       </c>
@@ -41810,10 +40490,6 @@
       <c r="O253" t="s">
         <v>2522</v>
       </c>
-      <c r="P253" t="str">
-        <f t="shared" si="3"/>
-        <v>JULIO CESAR AVITUA JUAREZ</v>
-      </c>
       <c r="Q253" t="s">
         <v>259</v>
       </c>
@@ -41887,7 +40563,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="254" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>39</v>
       </c>
@@ -41903,9 +40579,6 @@
       <c r="E254" t="s">
         <v>2431</v>
       </c>
-      <c r="F254" t="s">
-        <v>2432</v>
-      </c>
       <c r="G254" t="s">
         <v>2433</v>
       </c>
@@ -41930,10 +40603,6 @@
       <c r="O254" t="s">
         <v>2528</v>
       </c>
-      <c r="P254" t="str">
-        <f t="shared" si="3"/>
-        <v>IVAN MORALES NICOLAS</v>
-      </c>
       <c r="Q254" t="s">
         <v>2529</v>
       </c>
@@ -42007,7 +40676,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="255" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>39</v>
       </c>
@@ -42023,9 +40692,6 @@
       <c r="E255" t="s">
         <v>2431</v>
       </c>
-      <c r="F255" t="s">
-        <v>2432</v>
-      </c>
       <c r="G255" t="s">
         <v>2433</v>
       </c>
@@ -42050,10 +40716,6 @@
       <c r="O255" t="s">
         <v>2534</v>
       </c>
-      <c r="P255" t="str">
-        <f t="shared" si="3"/>
-        <v>SAMANTHA DENISSE NAVA VALADEZ</v>
-      </c>
       <c r="Q255" t="s">
         <v>2535</v>
       </c>
@@ -42127,7 +40789,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="256" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>39</v>
       </c>
@@ -42143,9 +40805,6 @@
       <c r="E256" t="s">
         <v>2431</v>
       </c>
-      <c r="F256" t="s">
-        <v>2432</v>
-      </c>
       <c r="G256" t="s">
         <v>2433</v>
       </c>
@@ -42170,10 +40829,6 @@
       <c r="O256" t="s">
         <v>2542</v>
       </c>
-      <c r="P256" t="str">
-        <f t="shared" si="3"/>
-        <v>DIANA LAURA SANJUAN MARTINEZ</v>
-      </c>
       <c r="Q256" t="s">
         <v>2543</v>
       </c>
@@ -42247,7 +40902,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="257" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>39</v>
       </c>
@@ -42263,9 +40918,6 @@
       <c r="E257" t="s">
         <v>2431</v>
       </c>
-      <c r="F257" t="s">
-        <v>2432</v>
-      </c>
       <c r="G257" t="s">
         <v>2433</v>
       </c>
@@ -42290,10 +40942,6 @@
       <c r="O257" t="s">
         <v>2549</v>
       </c>
-      <c r="P257" t="str">
-        <f t="shared" si="3"/>
-        <v>MARIA DEL CARMEN MAURICIO PLATA</v>
-      </c>
       <c r="Q257" t="s">
         <v>223</v>
       </c>
@@ -42367,7 +41015,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="258" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>39</v>
       </c>
@@ -42383,9 +41031,6 @@
       <c r="E258" t="s">
         <v>2431</v>
       </c>
-      <c r="F258" t="s">
-        <v>2432</v>
-      </c>
       <c r="G258" t="s">
         <v>2433</v>
       </c>
@@ -42410,10 +41055,6 @@
       <c r="O258" t="s">
         <v>2555</v>
       </c>
-      <c r="P258" t="str">
-        <f t="shared" si="3"/>
-        <v>LAURA RUIZ MANJARREZ</v>
-      </c>
       <c r="Q258" t="s">
         <v>238</v>
       </c>
@@ -42487,7 +41128,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="259" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>39</v>
       </c>
@@ -42503,9 +41144,6 @@
       <c r="E259" t="s">
         <v>2431</v>
       </c>
-      <c r="F259" t="s">
-        <v>2432</v>
-      </c>
       <c r="G259" t="s">
         <v>2433</v>
       </c>
@@ -42530,10 +41168,6 @@
       <c r="O259" t="s">
         <v>2561</v>
       </c>
-      <c r="P259" t="str">
-        <f t="shared" si="3"/>
-        <v>WILLIAMS HERNANDEZ AGUILAR</v>
-      </c>
       <c r="Q259" t="s">
         <v>2562</v>
       </c>
@@ -42607,7 +41241,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="260" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>39</v>
       </c>
@@ -42623,9 +41257,6 @@
       <c r="E260" t="s">
         <v>2431</v>
       </c>
-      <c r="F260" t="s">
-        <v>2432</v>
-      </c>
       <c r="G260" t="s">
         <v>2433</v>
       </c>
@@ -42650,10 +41281,6 @@
       <c r="O260" t="s">
         <v>2567</v>
       </c>
-      <c r="P260" t="str">
-        <f t="shared" si="3"/>
-        <v>PEDRO HERNANDEZ SANTIAGO</v>
-      </c>
       <c r="Q260" t="s">
         <v>1343</v>
       </c>
@@ -42727,7 +41354,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="261" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>39</v>
       </c>
@@ -42743,9 +41370,6 @@
       <c r="E261" t="s">
         <v>2431</v>
       </c>
-      <c r="F261" t="s">
-        <v>2432</v>
-      </c>
       <c r="G261" t="s">
         <v>2433</v>
       </c>
@@ -42770,10 +41394,6 @@
       <c r="O261" t="s">
         <v>2572</v>
       </c>
-      <c r="P261" t="str">
-        <f t="shared" si="3"/>
-        <v>JUAN FRANCISCO DE LA TORRE CRUZ</v>
-      </c>
       <c r="Q261" t="s">
         <v>2573</v>
       </c>
@@ -42847,7 +41467,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="262" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>39</v>
       </c>
@@ -42863,9 +41483,6 @@
       <c r="E262" t="s">
         <v>2431</v>
       </c>
-      <c r="F262" t="s">
-        <v>2432</v>
-      </c>
       <c r="G262" t="s">
         <v>2433</v>
       </c>
@@ -42890,10 +41507,6 @@
       <c r="O262" t="s">
         <v>2579</v>
       </c>
-      <c r="P262" t="str">
-        <f t="shared" si="3"/>
-        <v>RITA MONSERRAT SANCHEZ CAMACHO</v>
-      </c>
       <c r="Q262" t="s">
         <v>2580</v>
       </c>
@@ -42967,7 +41580,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="263" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>39</v>
       </c>
@@ -42983,9 +41596,6 @@
       <c r="E263" t="s">
         <v>2431</v>
       </c>
-      <c r="F263" t="s">
-        <v>2432</v>
-      </c>
       <c r="G263" t="s">
         <v>2433</v>
       </c>
@@ -43010,10 +41620,6 @@
       <c r="O263" t="s">
         <v>2586</v>
       </c>
-      <c r="P263" t="str">
-        <f t="shared" si="3"/>
-        <v>DAVID SEGURA CASTILLO</v>
-      </c>
       <c r="Q263" t="s">
         <v>96</v>
       </c>
@@ -43087,7 +41693,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="264" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>39</v>
       </c>
@@ -43103,9 +41709,6 @@
       <c r="E264" t="s">
         <v>2431</v>
       </c>
-      <c r="F264" t="s">
-        <v>2432</v>
-      </c>
       <c r="G264" t="s">
         <v>2433</v>
       </c>
@@ -43130,10 +41733,6 @@
       <c r="O264" t="s">
         <v>2592</v>
       </c>
-      <c r="P264" t="str">
-        <f t="shared" si="3"/>
-        <v>JOSE NICOLAS FLORES MARTINEZ</v>
-      </c>
       <c r="Q264" t="s">
         <v>2593</v>
       </c>
@@ -43207,7 +41806,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="265" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>39</v>
       </c>
@@ -43223,9 +41822,6 @@
       <c r="E265" t="s">
         <v>2431</v>
       </c>
-      <c r="F265" t="s">
-        <v>2432</v>
-      </c>
       <c r="G265" t="s">
         <v>2433</v>
       </c>
@@ -43250,10 +41846,6 @@
       <c r="O265" t="s">
         <v>2598</v>
       </c>
-      <c r="P265" t="str">
-        <f t="shared" si="3"/>
-        <v>CLAUDIA RUBI NALLELY ARREDONDO VIGIL</v>
-      </c>
       <c r="Q265" t="s">
         <v>2599</v>
       </c>
@@ -43327,7 +41919,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="266" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>39</v>
       </c>
@@ -43343,9 +41935,6 @@
       <c r="E266" t="s">
         <v>2431</v>
       </c>
-      <c r="F266" t="s">
-        <v>2432</v>
-      </c>
       <c r="G266" t="s">
         <v>2433</v>
       </c>
@@ -43370,10 +41959,6 @@
       <c r="O266" t="s">
         <v>2606</v>
       </c>
-      <c r="P266" t="str">
-        <f t="shared" si="3"/>
-        <v>YEIMI YULIANA SANTOS DEL ANGEL</v>
-      </c>
       <c r="Q266" t="s">
         <v>2607</v>
       </c>
@@ -43447,7 +42032,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="267" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>39</v>
       </c>
@@ -43463,9 +42048,6 @@
       <c r="E267" t="s">
         <v>2431</v>
       </c>
-      <c r="F267" t="s">
-        <v>2432</v>
-      </c>
       <c r="G267" t="s">
         <v>2433</v>
       </c>
@@ -43490,10 +42072,6 @@
       <c r="O267" t="s">
         <v>2612</v>
       </c>
-      <c r="P267" t="str">
-        <f t="shared" si="3"/>
-        <v>KAREM HERNANDEZ MARTINEZ</v>
-      </c>
       <c r="Q267" t="s">
         <v>2613</v>
       </c>
@@ -43567,7 +42145,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="268" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>39</v>
       </c>
@@ -43583,9 +42161,6 @@
       <c r="E268" t="s">
         <v>2431</v>
       </c>
-      <c r="F268" t="s">
-        <v>2432</v>
-      </c>
       <c r="G268" t="s">
         <v>2433</v>
       </c>
@@ -43610,10 +42185,6 @@
       <c r="O268" t="s">
         <v>2618</v>
       </c>
-      <c r="P268" t="str">
-        <f t="shared" si="3"/>
-        <v>YANERI HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q268" t="s">
         <v>2619</v>
       </c>
@@ -43687,7 +42258,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="269" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>39</v>
       </c>
@@ -43703,9 +42274,6 @@
       <c r="E269" t="s">
         <v>2431</v>
       </c>
-      <c r="F269" t="s">
-        <v>2432</v>
-      </c>
       <c r="G269" t="s">
         <v>2433</v>
       </c>
@@ -43730,10 +42298,6 @@
       <c r="O269" t="s">
         <v>2624</v>
       </c>
-      <c r="P269" t="str">
-        <f t="shared" si="3"/>
-        <v>FERNANDA HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q269" t="s">
         <v>2625</v>
       </c>
@@ -43807,7 +42371,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="270" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>39</v>
       </c>
@@ -43823,9 +42387,6 @@
       <c r="E270" t="s">
         <v>2431</v>
       </c>
-      <c r="F270" t="s">
-        <v>2432</v>
-      </c>
       <c r="G270" t="s">
         <v>2433</v>
       </c>
@@ -43850,10 +42411,6 @@
       <c r="O270" t="s">
         <v>2630</v>
       </c>
-      <c r="P270" t="str">
-        <f t="shared" si="3"/>
-        <v>MARCOS TRINIDAD SANTOS</v>
-      </c>
       <c r="Q270" t="s">
         <v>2631</v>
       </c>
@@ -43927,7 +42484,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="271" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>39</v>
       </c>
@@ -43943,9 +42500,6 @@
       <c r="E271" t="s">
         <v>2431</v>
       </c>
-      <c r="F271" t="s">
-        <v>2432</v>
-      </c>
       <c r="G271" t="s">
         <v>2433</v>
       </c>
@@ -43969,10 +42523,6 @@
       </c>
       <c r="O271" t="s">
         <v>2637</v>
-      </c>
-      <c r="P271" t="str">
-        <f t="shared" si="3"/>
-        <v>JOSE CRUZ COLORADO ROMERO</v>
       </c>
       <c r="Q271" t="s">
         <v>2638</v>
@@ -44091,7 +42641,7 @@
         <v>121</v>
       </c>
       <c r="P272" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="P272:P278" si="1">_xlfn.CONCAT(Q272," ",R272," ",S272)</f>
         <v>J. GUADALUPE MARTINEZ SALAZAR</v>
       </c>
       <c r="Q272" t="s">
@@ -44211,7 +42761,7 @@
         <v>131</v>
       </c>
       <c r="P273" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>OLGA LIDIA JIMENEZ PORRAS</v>
       </c>
       <c r="Q273" t="s">
@@ -44331,7 +42881,7 @@
         <v>139</v>
       </c>
       <c r="P274" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>ROSA ICELA CANTU CANTU</v>
       </c>
       <c r="Q274" t="s">
@@ -44451,7 +43001,7 @@
         <v>146</v>
       </c>
       <c r="P275" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>ELIAS IGNACIO DEL ANGEL</v>
       </c>
       <c r="Q275" t="s">
@@ -44571,7 +43121,7 @@
         <v>154</v>
       </c>
       <c r="P276" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>MA. DEL CARMEN RODRIGUEZ SUSTAITA</v>
       </c>
       <c r="Q276" t="s">
@@ -44691,7 +43241,7 @@
         <v>162</v>
       </c>
       <c r="P277" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>PEDRO DANIEL PALOMO GONZALEZ</v>
       </c>
       <c r="Q277" t="s">
@@ -44811,7 +43361,7 @@
         <v>169</v>
       </c>
       <c r="P278" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>ROSA HILDA VAZQUEZ ROCILLO</v>
       </c>
       <c r="Q278" t="s">
@@ -49571,7 +48121,7 @@
         <v>177</v>
       </c>
       <c r="P319" t="str">
-        <f t="shared" ref="P319:P321" si="4">_xlfn.CONCAT(Q319," ",R319," ",S319)</f>
+        <f t="shared" ref="P319:P321" si="2">_xlfn.CONCAT(Q319," ",R319," ",S319)</f>
         <v>MARCELINO SANTIZ GOMEZ</v>
       </c>
       <c r="Q319" t="s">
@@ -49691,7 +48241,7 @@
         <v>185</v>
       </c>
       <c r="P320" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>ROMEO PEREZ PEREZ</v>
       </c>
       <c r="Q320" t="s">
@@ -49811,7 +48361,7 @@
         <v>192</v>
       </c>
       <c r="P321" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>NORMA BELEN RODRIGUEZ GARCIA</v>
       </c>
       <c r="Q321" t="s">
@@ -50627,7 +49177,7 @@
         <v>198</v>
       </c>
       <c r="P328" t="str">
-        <f t="shared" ref="P328:P329" si="5">_xlfn.CONCAT(Q328," ",R328," ",S328)</f>
+        <f t="shared" ref="P328:P329" si="3">_xlfn.CONCAT(Q328," ",R328," ",S328)</f>
         <v>ALFREDO CASTRO JIMENEZ</v>
       </c>
       <c r="Q328" t="s">
@@ -50747,7 +49297,7 @@
         <v>205</v>
       </c>
       <c r="P329" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>ADRIAN RIVERA REYES</v>
       </c>
       <c r="Q329" t="s">
@@ -50983,7 +49533,7 @@
         <v>214</v>
       </c>
       <c r="P331" t="str">
-        <f t="shared" ref="P331:P337" si="6">_xlfn.CONCAT(Q331," ",R331," ",S331)</f>
+        <f t="shared" ref="P331:P337" si="4">_xlfn.CONCAT(Q331," ",R331," ",S331)</f>
         <v>ALEJANDRO LURIA LAZARO</v>
       </c>
       <c r="Q331" t="s">
@@ -51103,7 +49653,7 @@
         <v>222</v>
       </c>
       <c r="P332" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>MARIA DEL CARMEN GARCIA MONFIL</v>
       </c>
       <c r="Q332" t="s">
@@ -51223,7 +49773,7 @@
         <v>230</v>
       </c>
       <c r="P333" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>JALOSLAW DE JESUS GUTIERREZ CAMACHO</v>
       </c>
       <c r="Q333" t="s">
@@ -51343,7 +49893,7 @@
         <v>237</v>
       </c>
       <c r="P334" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>LAURA MARTINEZ RODRIGUEZ</v>
       </c>
       <c r="Q334" t="s">
@@ -51463,7 +50013,7 @@
         <v>243</v>
       </c>
       <c r="P335" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>BETZY JANETH PONCIANO LOPEZ</v>
       </c>
       <c r="Q335" t="s">
@@ -51583,7 +50133,7 @@
         <v>251</v>
       </c>
       <c r="P336" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>RODRIGO SANTIAGO RAMOS</v>
       </c>
       <c r="Q336" t="s">
@@ -51703,7 +50253,7 @@
         <v>258</v>
       </c>
       <c r="P337" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>JULIO CESAR ZAMORA VENEGAS</v>
       </c>
       <c r="Q337" t="s">
@@ -52055,7 +50605,7 @@
         <v>266</v>
       </c>
       <c r="P340" t="str">
-        <f t="shared" ref="P340:P378" si="7">_xlfn.CONCAT(Q340," ",R340," ",S340)</f>
+        <f t="shared" ref="P340:P378" si="5">_xlfn.CONCAT(Q340," ",R340," ",S340)</f>
         <v>ROSALIO REYNA RANGEL</v>
       </c>
       <c r="Q340" t="s">
@@ -52175,7 +50725,7 @@
         <v>274</v>
       </c>
       <c r="P341" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>JORGE CID FERRER</v>
       </c>
       <c r="Q341" t="s">
@@ -52295,7 +50845,7 @@
         <v>282</v>
       </c>
       <c r="P342" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>MARIA GUADALUPE PEDRAZA RODRIGUEZ</v>
       </c>
       <c r="Q342" t="s">
@@ -52415,7 +50965,7 @@
         <v>290</v>
       </c>
       <c r="P343" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>EMILIO GARCIA CRUZ</v>
       </c>
       <c r="Q343" t="s">
@@ -52535,7 +51085,7 @@
         <v>297</v>
       </c>
       <c r="P344" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>RICARDO LOPEZ TORRES</v>
       </c>
       <c r="Q344" t="s">
@@ -52655,7 +51205,7 @@
         <v>305</v>
       </c>
       <c r="P345" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>GERSON RAMIREZ GUILLEN</v>
       </c>
       <c r="Q345" t="s">
@@ -52775,7 +51325,7 @@
         <v>313</v>
       </c>
       <c r="P346" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>GABRIEL GONZALEZ CAMPOS</v>
       </c>
       <c r="Q346" t="s">
@@ -52895,7 +51445,7 @@
         <v>320</v>
       </c>
       <c r="P347" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>PAULA GUZMAN VELASCO</v>
       </c>
       <c r="Q347" t="s">
@@ -53015,7 +51565,7 @@
         <v>328</v>
       </c>
       <c r="P348" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>ROLANDO LUNA MARTINEZ</v>
       </c>
       <c r="Q348" t="s">
@@ -53135,7 +51685,7 @@
         <v>335</v>
       </c>
       <c r="P349" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>JUAN SANTILLAN SANTILLAN</v>
       </c>
       <c r="Q349" t="s">
@@ -53255,7 +51805,7 @@
         <v>343</v>
       </c>
       <c r="P350" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>MARIA ELVIA GONZALEZ AQUINO</v>
       </c>
       <c r="Q350" t="s">
@@ -53375,7 +51925,7 @@
         <v>350</v>
       </c>
       <c r="P351" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>JOSE ARMANDO FLORES MARTINEZ</v>
       </c>
       <c r="Q351" t="s">
@@ -53495,7 +52045,7 @@
         <v>357</v>
       </c>
       <c r="P352" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>AGUSTIN HERNANDEZ ANTONIO</v>
       </c>
       <c r="Q352" t="s">
@@ -53615,7 +52165,7 @@
         <v>365</v>
       </c>
       <c r="P353" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>JORGE ALBERTO DE LUNA PALOMINO</v>
       </c>
       <c r="Q353" t="s">
@@ -53735,7 +52285,7 @@
         <v>373</v>
       </c>
       <c r="P354" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>MIREYA MONTIEL LOPEZ</v>
       </c>
       <c r="Q354" t="s">
@@ -53855,7 +52405,7 @@
         <v>380</v>
       </c>
       <c r="P355" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>DOMINGO HERNANDEZ ZAVALA</v>
       </c>
       <c r="Q355" t="s">
@@ -53975,7 +52525,7 @@
         <v>388</v>
       </c>
       <c r="P356" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>NATALIE GIOVANNA CORONA RODRIGUEZ</v>
       </c>
       <c r="Q356" t="s">
@@ -54095,7 +52645,7 @@
         <v>395</v>
       </c>
       <c r="P357" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>NALLELY YANETH REYES SANCHEZ</v>
       </c>
       <c r="Q357" t="s">
@@ -54215,7 +52765,7 @@
         <v>403</v>
       </c>
       <c r="P358" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>JOSE LUIS HERNANDEZ HERNANDEZ</v>
       </c>
       <c r="Q358" t="s">
@@ -54335,7 +52885,7 @@
         <v>409</v>
       </c>
       <c r="P359" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>CESAR URIEL MARTINEZ RODRIGUEZ</v>
       </c>
       <c r="Q359" t="s">
@@ -54455,7 +53005,7 @@
         <v>415</v>
       </c>
       <c r="P360" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>MARCELO MATEO LICONA</v>
       </c>
       <c r="Q360" t="s">
@@ -54575,7 +53125,7 @@
         <v>424</v>
       </c>
       <c r="P361" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>NURIA YARELY DIAZ RODRIGUEZ</v>
       </c>
       <c r="Q361" t="s">
@@ -54695,7 +53245,7 @@
         <v>431</v>
       </c>
       <c r="P362" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>BRAULIO DE JESUS FIGUEROA CHIGUIL</v>
       </c>
       <c r="Q362" t="s">
@@ -54815,7 +53365,7 @@
         <v>439</v>
       </c>
       <c r="P363" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>JESUS HERNANDEZ ESTEBAN</v>
       </c>
       <c r="Q363" t="s">
@@ -54935,7 +53485,7 @@
         <v>446</v>
       </c>
       <c r="P364" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>NERY ROMERO CANCINO</v>
       </c>
       <c r="Q364" t="s">
@@ -55055,7 +53605,7 @@
         <v>455</v>
       </c>
       <c r="P365" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>ANDY JESUS ARCE VELAZQUEZ</v>
       </c>
       <c r="Q365" t="s">
@@ -55175,7 +53725,7 @@
         <v>463</v>
       </c>
       <c r="P366" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>DAVID JAVIER MARQUEZ</v>
       </c>
       <c r="Q366" t="s">
@@ -55295,7 +53845,7 @@
         <v>470</v>
       </c>
       <c r="P367" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>JORGE PEREZ MARTINEZ</v>
       </c>
       <c r="Q367" t="s">
@@ -55415,7 +53965,7 @@
         <v>475</v>
       </c>
       <c r="P368" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>ROMAN HERNANDEZ MONTAÑO</v>
       </c>
       <c r="Q368" t="s">
@@ -55535,7 +54085,7 @@
         <v>482</v>
       </c>
       <c r="P369" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>SAMARIA GUADALUPE MORALES VAZQUEZ</v>
       </c>
       <c r="Q369" t="s">
@@ -55611,7 +54161,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="370" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>39</v>
       </c>
@@ -55654,10 +54204,6 @@
       <c r="O370" t="s">
         <v>488</v>
       </c>
-      <c r="P370" t="str">
-        <f t="shared" si="7"/>
-        <v>JORGE XAVIER CRUZ GUTIERREZ</v>
-      </c>
       <c r="Q370" t="s">
         <v>489</v>
       </c>
@@ -55731,7 +54277,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="371" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>39</v>
       </c>
@@ -55747,9 +54293,6 @@
       <c r="E371" t="s">
         <v>118</v>
       </c>
-      <c r="F371" t="s">
-        <v>119</v>
-      </c>
       <c r="G371" t="s">
         <v>120</v>
       </c>
@@ -55774,10 +54317,6 @@
       <c r="O371" t="s">
         <v>494</v>
       </c>
-      <c r="P371" t="str">
-        <f t="shared" si="7"/>
-        <v>MAURILIO MARTINEZ MARTINEZ</v>
-      </c>
       <c r="Q371" t="s">
         <v>495</v>
       </c>
@@ -55851,7 +54390,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="372" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>39</v>
       </c>
@@ -55867,9 +54406,6 @@
       <c r="E372" t="s">
         <v>118</v>
       </c>
-      <c r="F372" t="s">
-        <v>119</v>
-      </c>
       <c r="G372" t="s">
         <v>120</v>
       </c>
@@ -55894,10 +54430,6 @@
       <c r="O372" t="s">
         <v>500</v>
       </c>
-      <c r="P372" t="str">
-        <f t="shared" si="7"/>
-        <v>JAZMIN MENDO RAMIREZ</v>
-      </c>
       <c r="Q372" t="s">
         <v>501</v>
       </c>
@@ -55971,7 +54503,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="373" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>39</v>
       </c>
@@ -55987,9 +54519,6 @@
       <c r="E373" t="s">
         <v>118</v>
       </c>
-      <c r="F373" t="s">
-        <v>119</v>
-      </c>
       <c r="G373" t="s">
         <v>120</v>
       </c>
@@ -56014,10 +54543,6 @@
       <c r="O373" t="s">
         <v>507</v>
       </c>
-      <c r="P373" t="str">
-        <f t="shared" si="7"/>
-        <v>LUZ ANGELICA HERNANDEZ VILLASANA</v>
-      </c>
       <c r="Q373" t="s">
         <v>508</v>
       </c>
@@ -56091,7 +54616,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="374" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>39</v>
       </c>
@@ -56107,9 +54632,6 @@
       <c r="E374" t="s">
         <v>118</v>
       </c>
-      <c r="F374" t="s">
-        <v>119</v>
-      </c>
       <c r="G374" t="s">
         <v>120</v>
       </c>
@@ -56134,10 +54656,6 @@
       <c r="O374" t="s">
         <v>514</v>
       </c>
-      <c r="P374" t="str">
-        <f t="shared" si="7"/>
-        <v>EZEQUIEL PABLO RAMOS</v>
-      </c>
       <c r="Q374" t="s">
         <v>515</v>
       </c>
@@ -56211,7 +54729,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="375" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>39</v>
       </c>
@@ -56227,9 +54745,6 @@
       <c r="E375" t="s">
         <v>118</v>
       </c>
-      <c r="F375" t="s">
-        <v>119</v>
-      </c>
       <c r="G375" t="s">
         <v>120</v>
       </c>
@@ -56254,10 +54769,6 @@
       <c r="O375" t="s">
         <v>521</v>
       </c>
-      <c r="P375" t="str">
-        <f t="shared" si="7"/>
-        <v>ESMERALDA ROMERO CANCINO</v>
-      </c>
       <c r="Q375" t="s">
         <v>522</v>
       </c>
@@ -56331,7 +54842,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="376" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>39</v>
       </c>
@@ -56347,9 +54858,6 @@
       <c r="E376" t="s">
         <v>118</v>
       </c>
-      <c r="F376" t="s">
-        <v>119</v>
-      </c>
       <c r="G376" t="s">
         <v>120</v>
       </c>
@@ -56374,10 +54882,6 @@
       <c r="O376" t="s">
         <v>527</v>
       </c>
-      <c r="P376" t="str">
-        <f t="shared" si="7"/>
-        <v>MARIA DEL ROSARIO ANGEL VICENTE</v>
-      </c>
       <c r="Q376" t="s">
         <v>528</v>
       </c>
@@ -56451,7 +54955,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="377" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>39</v>
       </c>
@@ -56467,9 +54971,6 @@
       <c r="E377" t="s">
         <v>118</v>
       </c>
-      <c r="F377" t="s">
-        <v>119</v>
-      </c>
       <c r="G377" t="s">
         <v>120</v>
       </c>
@@ -56494,10 +54995,6 @@
       <c r="O377" t="s">
         <v>535</v>
       </c>
-      <c r="P377" t="str">
-        <f t="shared" si="7"/>
-        <v>JESUS HERNANDEZ MELCHOR</v>
-      </c>
       <c r="Q377" t="s">
         <v>440</v>
       </c>
@@ -56571,7 +55068,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="378" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>39</v>
       </c>
@@ -56587,9 +55084,6 @@
       <c r="E378" t="s">
         <v>118</v>
       </c>
-      <c r="F378" t="s">
-        <v>119</v>
-      </c>
       <c r="G378" t="s">
         <v>120</v>
       </c>
@@ -56613,10 +55107,6 @@
       </c>
       <c r="O378" t="s">
         <v>541</v>
-      </c>
-      <c r="P378" t="str">
-        <f t="shared" si="7"/>
-        <v>WILBERT RAMIREZ ANTONIO</v>
       </c>
       <c r="Q378" t="s">
         <v>542</v>
@@ -58083,7 +56573,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="391" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>39</v>
       </c>
@@ -58099,9 +56589,6 @@
       <c r="E391" t="s">
         <v>118</v>
       </c>
-      <c r="F391" t="s">
-        <v>119</v>
-      </c>
       <c r="G391" t="s">
         <v>120</v>
       </c>
@@ -58126,10 +56613,6 @@
       <c r="O391" t="s">
         <v>547</v>
       </c>
-      <c r="P391" t="str">
-        <f t="shared" ref="P391:P402" si="8">_xlfn.CONCAT(Q391," ",R391," ",S391)</f>
-        <v>MANUEL HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q391" t="s">
         <v>548</v>
       </c>
@@ -58203,7 +56686,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="392" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>39</v>
       </c>
@@ -58219,9 +56702,6 @@
       <c r="E392" t="s">
         <v>118</v>
       </c>
-      <c r="F392" t="s">
-        <v>119</v>
-      </c>
       <c r="G392" t="s">
         <v>120</v>
       </c>
@@ -58246,10 +56726,6 @@
       <c r="O392" t="s">
         <v>553</v>
       </c>
-      <c r="P392" t="str">
-        <f t="shared" si="8"/>
-        <v>ENEDINO CORTES MARTINEZ</v>
-      </c>
       <c r="Q392" t="s">
         <v>554</v>
       </c>
@@ -58323,7 +56799,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="393" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>39</v>
       </c>
@@ -58339,9 +56815,6 @@
       <c r="E393" t="s">
         <v>118</v>
       </c>
-      <c r="F393" t="s">
-        <v>119</v>
-      </c>
       <c r="G393" t="s">
         <v>120</v>
       </c>
@@ -58366,10 +56839,6 @@
       <c r="O393" t="s">
         <v>559</v>
       </c>
-      <c r="P393" t="str">
-        <f t="shared" si="8"/>
-        <v>AURELIO ORGEN HERNANDEZ</v>
-      </c>
       <c r="Q393" t="s">
         <v>560</v>
       </c>
@@ -58443,7 +56912,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="394" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>39</v>
       </c>
@@ -58459,9 +56928,6 @@
       <c r="E394" t="s">
         <v>118</v>
       </c>
-      <c r="F394" t="s">
-        <v>119</v>
-      </c>
       <c r="G394" t="s">
         <v>120</v>
       </c>
@@ -58486,10 +56952,6 @@
       <c r="O394" t="s">
         <v>566</v>
       </c>
-      <c r="P394" t="str">
-        <f t="shared" si="8"/>
-        <v>ANA MARIA GALLARDO LABASTIDA</v>
-      </c>
       <c r="Q394" t="s">
         <v>567</v>
       </c>
@@ -58563,7 +57025,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="395" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>39</v>
       </c>
@@ -58579,9 +57041,6 @@
       <c r="E395" t="s">
         <v>118</v>
       </c>
-      <c r="F395" t="s">
-        <v>119</v>
-      </c>
       <c r="G395" t="s">
         <v>120</v>
       </c>
@@ -58606,10 +57065,6 @@
       <c r="O395" t="s">
         <v>574</v>
       </c>
-      <c r="P395" t="str">
-        <f t="shared" si="8"/>
-        <v>EDIEL ONAN HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q395" t="s">
         <v>575</v>
       </c>
@@ -58683,7 +57138,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="396" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>39</v>
       </c>
@@ -58699,9 +57154,6 @@
       <c r="E396" t="s">
         <v>118</v>
       </c>
-      <c r="F396" t="s">
-        <v>119</v>
-      </c>
       <c r="G396" t="s">
         <v>120</v>
       </c>
@@ -58726,10 +57178,6 @@
       <c r="O396" t="s">
         <v>580</v>
       </c>
-      <c r="P396" t="str">
-        <f t="shared" si="8"/>
-        <v>LUIS FELIPE GUZMAN VALDES</v>
-      </c>
       <c r="Q396" t="s">
         <v>581</v>
       </c>
@@ -58803,7 +57251,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="397" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>39</v>
       </c>
@@ -58819,9 +57267,6 @@
       <c r="E397" t="s">
         <v>118</v>
       </c>
-      <c r="F397" t="s">
-        <v>119</v>
-      </c>
       <c r="G397" t="s">
         <v>120</v>
       </c>
@@ -58846,10 +57291,6 @@
       <c r="O397" t="s">
         <v>587</v>
       </c>
-      <c r="P397" t="str">
-        <f t="shared" si="8"/>
-        <v>DEVANY JARETZI HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q397" t="s">
         <v>588</v>
       </c>
@@ -58923,7 +57364,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="398" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>39</v>
       </c>
@@ -58939,9 +57380,6 @@
       <c r="E398" t="s">
         <v>118</v>
       </c>
-      <c r="F398" t="s">
-        <v>119</v>
-      </c>
       <c r="G398" t="s">
         <v>120</v>
       </c>
@@ -58966,10 +57404,6 @@
       <c r="O398" t="s">
         <v>593</v>
       </c>
-      <c r="P398" t="str">
-        <f t="shared" si="8"/>
-        <v>INGRID YIZELL ROSADO PEREZ</v>
-      </c>
       <c r="Q398" t="s">
         <v>594</v>
       </c>
@@ -59043,7 +57477,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="399" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>39</v>
       </c>
@@ -59059,9 +57493,6 @@
       <c r="E399" t="s">
         <v>118</v>
       </c>
-      <c r="F399" t="s">
-        <v>119</v>
-      </c>
       <c r="G399" t="s">
         <v>120</v>
       </c>
@@ -59086,10 +57517,6 @@
       <c r="O399" t="s">
         <v>601</v>
       </c>
-      <c r="P399" t="str">
-        <f t="shared" si="8"/>
-        <v>FLOR ANDREA ALVARADO CORDOVA</v>
-      </c>
       <c r="Q399" t="s">
         <v>602</v>
       </c>
@@ -59163,7 +57590,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="400" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>39</v>
       </c>
@@ -59179,9 +57606,6 @@
       <c r="E400" t="s">
         <v>118</v>
       </c>
-      <c r="F400" t="s">
-        <v>119</v>
-      </c>
       <c r="G400" t="s">
         <v>120</v>
       </c>
@@ -59206,10 +57630,6 @@
       <c r="O400" t="s">
         <v>609</v>
       </c>
-      <c r="P400" t="str">
-        <f t="shared" si="8"/>
-        <v>ANA MARIA GONZALEZ OBREGON</v>
-      </c>
       <c r="Q400" t="s">
         <v>567</v>
       </c>
@@ -59283,7 +57703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="401" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>39</v>
       </c>
@@ -59299,9 +57719,6 @@
       <c r="E401" t="s">
         <v>118</v>
       </c>
-      <c r="F401" t="s">
-        <v>119</v>
-      </c>
       <c r="G401" t="s">
         <v>120</v>
       </c>
@@ -59326,10 +57743,6 @@
       <c r="O401" t="s">
         <v>615</v>
       </c>
-      <c r="P401" t="str">
-        <f t="shared" si="8"/>
-        <v>HORTENCIA LOPEZ RAMOS</v>
-      </c>
       <c r="Q401" t="s">
         <v>616</v>
       </c>
@@ -59403,7 +57816,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="402" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>39</v>
       </c>
@@ -59419,9 +57832,6 @@
       <c r="E402" t="s">
         <v>118</v>
       </c>
-      <c r="F402" t="s">
-        <v>119</v>
-      </c>
       <c r="G402" t="s">
         <v>120</v>
       </c>
@@ -59445,10 +57855,6 @@
       </c>
       <c r="O402" t="s">
         <v>621</v>
-      </c>
-      <c r="P402" t="str">
-        <f t="shared" si="8"/>
-        <v>EMMILY JAZMIN RUIZ MORENO</v>
       </c>
       <c r="Q402" t="s">
         <v>622</v>
@@ -60567,7 +58973,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="412" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>39</v>
       </c>
@@ -60583,9 +58989,6 @@
       <c r="E412" t="s">
         <v>118</v>
       </c>
-      <c r="F412" t="s">
-        <v>119</v>
-      </c>
       <c r="G412" t="s">
         <v>120</v>
       </c>
@@ -60610,10 +59013,6 @@
       <c r="O412" t="s">
         <v>629</v>
       </c>
-      <c r="P412" t="str">
-        <f t="shared" ref="P412:P431" si="9">_xlfn.CONCAT(Q412," ",R412," ",S412)</f>
-        <v>LAURA SANCHEZ BUSTOS</v>
-      </c>
       <c r="Q412" t="s">
         <v>238</v>
       </c>
@@ -60687,7 +59086,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="413" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>39</v>
       </c>
@@ -60703,9 +59102,6 @@
       <c r="E413" t="s">
         <v>118</v>
       </c>
-      <c r="F413" t="s">
-        <v>119</v>
-      </c>
       <c r="G413" t="s">
         <v>120</v>
       </c>
@@ -60730,10 +59126,6 @@
       <c r="O413" t="s">
         <v>635</v>
       </c>
-      <c r="P413" t="str">
-        <f t="shared" si="9"/>
-        <v>CESAR DANIEL TREVIÑO PEÑA</v>
-      </c>
       <c r="Q413" t="s">
         <v>636</v>
       </c>
@@ -60807,7 +59199,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="414" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>39</v>
       </c>
@@ -60823,9 +59215,6 @@
       <c r="E414" t="s">
         <v>118</v>
       </c>
-      <c r="F414" t="s">
-        <v>119</v>
-      </c>
       <c r="G414" t="s">
         <v>120</v>
       </c>
@@ -60850,10 +59239,6 @@
       <c r="O414" t="s">
         <v>643</v>
       </c>
-      <c r="P414" t="str">
-        <f t="shared" si="9"/>
-        <v>JESUS MONTERO BERNARDO</v>
-      </c>
       <c r="Q414" t="s">
         <v>440</v>
       </c>
@@ -60927,7 +59312,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="415" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>39</v>
       </c>
@@ -60943,9 +59328,6 @@
       <c r="E415" t="s">
         <v>118</v>
       </c>
-      <c r="F415" t="s">
-        <v>119</v>
-      </c>
       <c r="G415" t="s">
         <v>120</v>
       </c>
@@ -60970,10 +59352,6 @@
       <c r="O415" t="s">
         <v>650</v>
       </c>
-      <c r="P415" t="str">
-        <f t="shared" si="9"/>
-        <v>SAMUEL OLAN ESTRADA</v>
-      </c>
       <c r="Q415" t="s">
         <v>651</v>
       </c>
@@ -61047,7 +59425,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="416" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>39</v>
       </c>
@@ -61063,9 +59441,6 @@
       <c r="E416" t="s">
         <v>118</v>
       </c>
-      <c r="F416" t="s">
-        <v>119</v>
-      </c>
       <c r="G416" t="s">
         <v>120</v>
       </c>
@@ -61090,10 +59465,6 @@
       <c r="O416" t="s">
         <v>658</v>
       </c>
-      <c r="P416" t="str">
-        <f t="shared" si="9"/>
-        <v>NOEMI ANTONIA ESPINOZA TORRES</v>
-      </c>
       <c r="Q416" t="s">
         <v>659</v>
       </c>
@@ -61167,7 +59538,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="417" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>39</v>
       </c>
@@ -61183,9 +59554,6 @@
       <c r="E417" t="s">
         <v>118</v>
       </c>
-      <c r="F417" t="s">
-        <v>119</v>
-      </c>
       <c r="G417" t="s">
         <v>120</v>
       </c>
@@ -61210,10 +59578,6 @@
       <c r="O417" t="s">
         <v>665</v>
       </c>
-      <c r="P417" t="str">
-        <f t="shared" si="9"/>
-        <v>MIRALDELLY ASENCIO ALVARADO</v>
-      </c>
       <c r="Q417" t="s">
         <v>666</v>
       </c>
@@ -61287,7 +59651,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="418" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>39</v>
       </c>
@@ -61303,9 +59667,6 @@
       <c r="E418" t="s">
         <v>118</v>
       </c>
-      <c r="F418" t="s">
-        <v>119</v>
-      </c>
       <c r="G418" t="s">
         <v>120</v>
       </c>
@@ -61330,10 +59691,6 @@
       <c r="O418" t="s">
         <v>672</v>
       </c>
-      <c r="P418" t="str">
-        <f t="shared" si="9"/>
-        <v>CHRISTIAN CERDA ESPINOZA</v>
-      </c>
       <c r="Q418" t="s">
         <v>673</v>
       </c>
@@ -61407,7 +59764,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="419" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>39</v>
       </c>
@@ -61423,9 +59780,6 @@
       <c r="E419" t="s">
         <v>118</v>
       </c>
-      <c r="F419" t="s">
-        <v>119</v>
-      </c>
       <c r="G419" t="s">
         <v>120</v>
       </c>
@@ -61450,10 +59804,6 @@
       <c r="O419" t="s">
         <v>679</v>
       </c>
-      <c r="P419" t="str">
-        <f t="shared" si="9"/>
-        <v>ROBERTO SOLIS SOTO</v>
-      </c>
       <c r="Q419" t="s">
         <v>680</v>
       </c>
@@ -61527,7 +59877,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="420" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>39</v>
       </c>
@@ -61543,9 +59893,6 @@
       <c r="E420" t="s">
         <v>118</v>
       </c>
-      <c r="F420" t="s">
-        <v>119</v>
-      </c>
       <c r="G420" t="s">
         <v>120</v>
       </c>
@@ -61570,10 +59917,6 @@
       <c r="O420" t="s">
         <v>687</v>
       </c>
-      <c r="P420" t="str">
-        <f t="shared" si="9"/>
-        <v>JAIME ROBLES HERNANDEZ</v>
-      </c>
       <c r="Q420" t="s">
         <v>688</v>
       </c>
@@ -61647,7 +59990,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="421" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>39</v>
       </c>
@@ -61663,9 +60006,6 @@
       <c r="E421" t="s">
         <v>118</v>
       </c>
-      <c r="F421" t="s">
-        <v>119</v>
-      </c>
       <c r="G421" t="s">
         <v>120</v>
       </c>
@@ -61690,10 +60030,6 @@
       <c r="O421" t="s">
         <v>694</v>
       </c>
-      <c r="P421" t="str">
-        <f t="shared" si="9"/>
-        <v>CESAR VENEGAS BLANCO</v>
-      </c>
       <c r="Q421" t="s">
         <v>695</v>
       </c>
@@ -61767,7 +60103,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="422" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>39</v>
       </c>
@@ -61783,9 +60119,6 @@
       <c r="E422" t="s">
         <v>118</v>
       </c>
-      <c r="F422" t="s">
-        <v>119</v>
-      </c>
       <c r="G422" t="s">
         <v>120</v>
       </c>
@@ -61810,10 +60143,6 @@
       <c r="O422" t="s">
         <v>701</v>
       </c>
-      <c r="P422" t="str">
-        <f t="shared" si="9"/>
-        <v>JANET PEREZ JUAREZ</v>
-      </c>
       <c r="Q422" t="s">
         <v>702</v>
       </c>
@@ -61887,7 +60216,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="423" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>39</v>
       </c>
@@ -61903,9 +60232,6 @@
       <c r="E423" t="s">
         <v>118</v>
       </c>
-      <c r="F423" t="s">
-        <v>119</v>
-      </c>
       <c r="G423" t="s">
         <v>120</v>
       </c>
@@ -61930,10 +60256,6 @@
       <c r="O423" t="s">
         <v>708</v>
       </c>
-      <c r="P423" t="str">
-        <f t="shared" si="9"/>
-        <v>DAVID PEREZ SANCHEZ</v>
-      </c>
       <c r="Q423" t="s">
         <v>96</v>
       </c>
@@ -62007,7 +60329,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="424" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>39</v>
       </c>
@@ -62023,9 +60345,6 @@
       <c r="E424" t="s">
         <v>118</v>
       </c>
-      <c r="F424" t="s">
-        <v>119</v>
-      </c>
       <c r="G424" t="s">
         <v>120</v>
       </c>
@@ -62050,10 +60369,6 @@
       <c r="O424" t="s">
         <v>713</v>
       </c>
-      <c r="P424" t="str">
-        <f t="shared" si="9"/>
-        <v>LEONARDO AMADOR CRUZ</v>
-      </c>
       <c r="Q424" t="s">
         <v>714</v>
       </c>
@@ -62127,7 +60442,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="425" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>39</v>
       </c>
@@ -62143,9 +60458,6 @@
       <c r="E425" t="s">
         <v>118</v>
       </c>
-      <c r="F425" t="s">
-        <v>119</v>
-      </c>
       <c r="G425" t="s">
         <v>120</v>
       </c>
@@ -62170,10 +60482,6 @@
       <c r="O425" t="s">
         <v>720</v>
       </c>
-      <c r="P425" t="str">
-        <f t="shared" si="9"/>
-        <v>GONZALO ALONSO PIÑA RAMIREZ</v>
-      </c>
       <c r="Q425" t="s">
         <v>721</v>
       </c>
@@ -62247,7 +60555,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="426" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>39</v>
       </c>
@@ -62263,9 +60571,6 @@
       <c r="E426" t="s">
         <v>118</v>
       </c>
-      <c r="F426" t="s">
-        <v>119</v>
-      </c>
       <c r="G426" t="s">
         <v>120</v>
       </c>
@@ -62290,10 +60595,6 @@
       <c r="O426" t="s">
         <v>728</v>
       </c>
-      <c r="P426" t="str">
-        <f t="shared" si="9"/>
-        <v>JESUS MANUEL VILLA CARDEL</v>
-      </c>
       <c r="Q426" t="s">
         <v>729</v>
       </c>
@@ -62367,7 +60668,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="427" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>39</v>
       </c>
@@ -62383,9 +60684,6 @@
       <c r="E427" t="s">
         <v>118</v>
       </c>
-      <c r="F427" t="s">
-        <v>119</v>
-      </c>
       <c r="G427" t="s">
         <v>120</v>
       </c>
@@ -62410,10 +60708,6 @@
       <c r="O427" t="s">
         <v>736</v>
       </c>
-      <c r="P427" t="str">
-        <f t="shared" si="9"/>
-        <v>XOCHITL LIZETH CRUZ BONILLA</v>
-      </c>
       <c r="Q427" t="s">
         <v>737</v>
       </c>
@@ -62487,7 +60781,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="428" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>39</v>
       </c>
@@ -62503,9 +60797,6 @@
       <c r="E428" t="s">
         <v>118</v>
       </c>
-      <c r="F428" t="s">
-        <v>119</v>
-      </c>
       <c r="G428" t="s">
         <v>120</v>
       </c>
@@ -62530,10 +60821,6 @@
       <c r="O428" t="s">
         <v>743</v>
       </c>
-      <c r="P428" t="str">
-        <f t="shared" si="9"/>
-        <v>CATALINA ESMERALDA RIVERA CARMONA</v>
-      </c>
       <c r="Q428" t="s">
         <v>744</v>
       </c>
@@ -62607,7 +60894,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="429" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>39</v>
       </c>
@@ -62623,9 +60910,6 @@
       <c r="E429" t="s">
         <v>118</v>
       </c>
-      <c r="F429" t="s">
-        <v>119</v>
-      </c>
       <c r="G429" t="s">
         <v>120</v>
       </c>
@@ -62650,10 +60934,6 @@
       <c r="O429" t="s">
         <v>750</v>
       </c>
-      <c r="P429" t="str">
-        <f t="shared" si="9"/>
-        <v>JOSE ROMAN HERNANDEZ GARCIA</v>
-      </c>
       <c r="Q429" t="s">
         <v>751</v>
       </c>
@@ -62727,7 +61007,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="430" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>39</v>
       </c>
@@ -62743,9 +61023,6 @@
       <c r="E430" t="s">
         <v>118</v>
       </c>
-      <c r="F430" t="s">
-        <v>119</v>
-      </c>
       <c r="G430" t="s">
         <v>120</v>
       </c>
@@ -62770,10 +61047,6 @@
       <c r="O430" t="s">
         <v>757</v>
       </c>
-      <c r="P430" t="str">
-        <f t="shared" si="9"/>
-        <v>SINDI GUADALUPE RODRIGUEZ LUCIO</v>
-      </c>
       <c r="Q430" t="s">
         <v>758</v>
       </c>
@@ -62847,7 +61120,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="431" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>39</v>
       </c>
@@ -62863,9 +61136,6 @@
       <c r="E431" t="s">
         <v>118</v>
       </c>
-      <c r="F431" t="s">
-        <v>119</v>
-      </c>
       <c r="G431" t="s">
         <v>120</v>
       </c>
@@ -62889,10 +61159,6 @@
       </c>
       <c r="O431" t="s">
         <v>764</v>
-      </c>
-      <c r="P431" t="str">
-        <f t="shared" si="9"/>
-        <v>AMALIA POLETH GARCIA GOMEZ</v>
       </c>
       <c r="Q431" t="s">
         <v>765</v>
@@ -63895,7 +62161,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="440" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>39</v>
       </c>
@@ -63911,9 +62177,6 @@
       <c r="E440" t="s">
         <v>118</v>
       </c>
-      <c r="F440" t="s">
-        <v>119</v>
-      </c>
       <c r="G440" t="s">
         <v>120</v>
       </c>
@@ -63938,10 +62201,6 @@
       <c r="O440" t="s">
         <v>770</v>
       </c>
-      <c r="P440" t="str">
-        <f t="shared" ref="P440:P450" si="10">_xlfn.CONCAT(Q440," ",R440," ",S440)</f>
-        <v>ELIZABETH GUZMAN JIMENEZ</v>
-      </c>
       <c r="Q440" t="s">
         <v>771</v>
       </c>
@@ -64015,7 +62274,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="441" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>39</v>
       </c>
@@ -64031,9 +62290,6 @@
       <c r="E441" t="s">
         <v>118</v>
       </c>
-      <c r="F441" t="s">
-        <v>119</v>
-      </c>
       <c r="G441" t="s">
         <v>120</v>
       </c>
@@ -64058,10 +62314,6 @@
       <c r="O441" t="s">
         <v>776</v>
       </c>
-      <c r="P441" t="str">
-        <f t="shared" si="10"/>
-        <v>MARIA ZULEMA MENDOZA RENTERIA</v>
-      </c>
       <c r="Q441" t="s">
         <v>777</v>
       </c>
@@ -64135,7 +62387,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="442" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>39</v>
       </c>
@@ -64151,9 +62403,6 @@
       <c r="E442" t="s">
         <v>118</v>
       </c>
-      <c r="F442" t="s">
-        <v>119</v>
-      </c>
       <c r="G442" t="s">
         <v>120</v>
       </c>
@@ -64178,10 +62427,6 @@
       <c r="O442" t="s">
         <v>784</v>
       </c>
-      <c r="P442" t="str">
-        <f t="shared" si="10"/>
-        <v>VICTOR MANUEL ALVARADO ROSTRO</v>
-      </c>
       <c r="Q442" t="s">
         <v>785</v>
       </c>
@@ -64255,7 +62500,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="443" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>39</v>
       </c>
@@ -64271,9 +62516,6 @@
       <c r="E443" t="s">
         <v>118</v>
       </c>
-      <c r="F443" t="s">
-        <v>119</v>
-      </c>
       <c r="G443" t="s">
         <v>120</v>
       </c>
@@ -64298,10 +62540,6 @@
       <c r="O443" t="s">
         <v>791</v>
       </c>
-      <c r="P443" t="str">
-        <f t="shared" si="10"/>
-        <v>JOSE ANGEL CRUZ BONILLA</v>
-      </c>
       <c r="Q443" t="s">
         <v>792</v>
       </c>
@@ -64375,7 +62613,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="444" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>39</v>
       </c>
@@ -64391,9 +62629,6 @@
       <c r="E444" t="s">
         <v>118</v>
       </c>
-      <c r="F444" t="s">
-        <v>119</v>
-      </c>
       <c r="G444" t="s">
         <v>120</v>
       </c>
@@ -64418,10 +62653,6 @@
       <c r="O444" t="s">
         <v>797</v>
       </c>
-      <c r="P444" t="str">
-        <f t="shared" si="10"/>
-        <v>JUAN PABLO LEYVA GARCIA</v>
-      </c>
       <c r="Q444" t="s">
         <v>798</v>
       </c>
@@ -64495,7 +62726,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="445" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>39</v>
       </c>
@@ -64511,9 +62742,6 @@
       <c r="E445" t="s">
         <v>118</v>
       </c>
-      <c r="F445" t="s">
-        <v>119</v>
-      </c>
       <c r="G445" t="s">
         <v>120</v>
       </c>
@@ -64538,10 +62766,6 @@
       <c r="O445" t="s">
         <v>804</v>
       </c>
-      <c r="P445" t="str">
-        <f t="shared" si="10"/>
-        <v>JUAN CARLOS CRUZ MORENO</v>
-      </c>
       <c r="Q445" t="s">
         <v>805</v>
       </c>
@@ -64615,7 +62839,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="446" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>39</v>
       </c>
@@ -64631,9 +62855,6 @@
       <c r="E446" t="s">
         <v>118</v>
       </c>
-      <c r="F446" t="s">
-        <v>119</v>
-      </c>
       <c r="G446" t="s">
         <v>120</v>
       </c>
@@ -64658,10 +62879,6 @@
       <c r="O446" t="s">
         <v>810</v>
       </c>
-      <c r="P446" t="str">
-        <f t="shared" si="10"/>
-        <v>SEBASTIAN GUTIERREZ ALFARO</v>
-      </c>
       <c r="Q446" t="s">
         <v>811</v>
       </c>
@@ -64735,7 +62952,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="447" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>39</v>
       </c>
@@ -64751,9 +62968,6 @@
       <c r="E447" t="s">
         <v>118</v>
       </c>
-      <c r="F447" t="s">
-        <v>119</v>
-      </c>
       <c r="G447" t="s">
         <v>120</v>
       </c>
@@ -64778,10 +62992,6 @@
       <c r="O447" t="s">
         <v>817</v>
       </c>
-      <c r="P447" t="str">
-        <f t="shared" si="10"/>
-        <v>SELENE ELIZABETH JIMENEZ ABAD</v>
-      </c>
       <c r="Q447" t="s">
         <v>818</v>
       </c>
@@ -64855,7 +63065,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="448" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>39</v>
       </c>
@@ -64871,9 +63081,6 @@
       <c r="E448" t="s">
         <v>118</v>
       </c>
-      <c r="F448" t="s">
-        <v>119</v>
-      </c>
       <c r="G448" t="s">
         <v>120</v>
       </c>
@@ -64898,10 +63105,6 @@
       <c r="O448" t="s">
         <v>824</v>
       </c>
-      <c r="P448" t="str">
-        <f t="shared" si="10"/>
-        <v>OSCAR CRUZ MORAN</v>
-      </c>
       <c r="Q448" t="s">
         <v>825</v>
       </c>
@@ -64975,7 +63178,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="449" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>39</v>
       </c>
@@ -64991,9 +63194,6 @@
       <c r="E449" t="s">
         <v>118</v>
       </c>
-      <c r="F449" t="s">
-        <v>119</v>
-      </c>
       <c r="G449" t="s">
         <v>120</v>
       </c>
@@ -65018,10 +63218,6 @@
       <c r="O449" t="s">
         <v>832</v>
       </c>
-      <c r="P449" t="str">
-        <f t="shared" si="10"/>
-        <v>JULIO CESAR GUTIERREZ PEREZ</v>
-      </c>
       <c r="Q449" t="s">
         <v>259</v>
       </c>
@@ -65095,7 +63291,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="450" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>39</v>
       </c>
@@ -65111,9 +63307,6 @@
       <c r="E450" t="s">
         <v>118</v>
       </c>
-      <c r="F450" t="s">
-        <v>119</v>
-      </c>
       <c r="G450" t="s">
         <v>120</v>
       </c>
@@ -65137,10 +63330,6 @@
       </c>
       <c r="O450" t="s">
         <v>837</v>
-      </c>
-      <c r="P450" t="str">
-        <f t="shared" si="10"/>
-        <v>ROSALBA GARCIA MANUEL</v>
       </c>
       <c r="Q450" t="s">
         <v>838</v>
@@ -65447,7 +63636,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="453" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>39</v>
       </c>
@@ -65463,9 +63652,6 @@
       <c r="E453" t="s">
         <v>118</v>
       </c>
-      <c r="F453" t="s">
-        <v>119</v>
-      </c>
       <c r="G453" t="s">
         <v>120</v>
       </c>
@@ -65490,10 +63676,6 @@
       <c r="O453" t="s">
         <v>843</v>
       </c>
-      <c r="P453" t="str">
-        <f t="shared" ref="P453:P474" si="11">_xlfn.CONCAT(Q453," ",R453," ",S453)</f>
-        <v>JOSE YUREM LOPEZ MOLINA</v>
-      </c>
       <c r="Q453" t="s">
         <v>844</v>
       </c>
@@ -65567,7 +63749,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="454" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>39</v>
       </c>
@@ -65583,9 +63765,6 @@
       <c r="E454" t="s">
         <v>118</v>
       </c>
-      <c r="F454" t="s">
-        <v>119</v>
-      </c>
       <c r="G454" t="s">
         <v>120</v>
       </c>
@@ -65610,10 +63789,6 @@
       <c r="O454" t="s">
         <v>850</v>
       </c>
-      <c r="P454" t="str">
-        <f t="shared" si="11"/>
-        <v>JESUS RIOS POSADA</v>
-      </c>
       <c r="Q454" t="s">
         <v>440</v>
       </c>
@@ -65687,7 +63862,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="455" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>39</v>
       </c>
@@ -65703,9 +63878,6 @@
       <c r="E455" t="s">
         <v>118</v>
       </c>
-      <c r="F455" t="s">
-        <v>119</v>
-      </c>
       <c r="G455" t="s">
         <v>120</v>
       </c>
@@ -65730,10 +63902,6 @@
       <c r="O455" t="s">
         <v>857</v>
       </c>
-      <c r="P455" t="str">
-        <f t="shared" si="11"/>
-        <v>JOSE ENRIQUE MARTINEZ GONZALEZ</v>
-      </c>
       <c r="Q455" t="s">
         <v>858</v>
       </c>
@@ -65807,7 +63975,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="456" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>39</v>
       </c>
@@ -65823,9 +63991,6 @@
       <c r="E456" t="s">
         <v>118</v>
       </c>
-      <c r="F456" t="s">
-        <v>119</v>
-      </c>
       <c r="G456" t="s">
         <v>120</v>
       </c>
@@ -65850,10 +64015,6 @@
       <c r="O456" t="s">
         <v>863</v>
       </c>
-      <c r="P456" t="str">
-        <f t="shared" si="11"/>
-        <v>MARCO ANTONIO HERNANDEZ MARAÑON</v>
-      </c>
       <c r="Q456" t="s">
         <v>864</v>
       </c>
@@ -65927,7 +64088,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="457" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>39</v>
       </c>
@@ -65943,9 +64104,6 @@
       <c r="E457" t="s">
         <v>118</v>
       </c>
-      <c r="F457" t="s">
-        <v>119</v>
-      </c>
       <c r="G457" t="s">
         <v>120</v>
       </c>
@@ -65970,10 +64128,6 @@
       <c r="O457" t="s">
         <v>870</v>
       </c>
-      <c r="P457" t="str">
-        <f t="shared" si="11"/>
-        <v>ADRIAN ALEJANDRO CERDA ESPINOZA</v>
-      </c>
       <c r="Q457" t="s">
         <v>871</v>
       </c>
@@ -66047,7 +64201,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="458" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>39</v>
       </c>
@@ -66063,9 +64217,6 @@
       <c r="E458" t="s">
         <v>118</v>
       </c>
-      <c r="F458" t="s">
-        <v>119</v>
-      </c>
       <c r="G458" t="s">
         <v>120</v>
       </c>
@@ -66090,10 +64241,6 @@
       <c r="O458" t="s">
         <v>876</v>
       </c>
-      <c r="P458" t="str">
-        <f t="shared" si="11"/>
-        <v>MARIA ELENA HERNANDEZ HERNANDEZ</v>
-      </c>
       <c r="Q458" t="s">
         <v>877</v>
       </c>
@@ -66167,7 +64314,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="459" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>39</v>
       </c>
@@ -66183,9 +64330,6 @@
       <c r="E459" t="s">
         <v>118</v>
       </c>
-      <c r="F459" t="s">
-        <v>119</v>
-      </c>
       <c r="G459" t="s">
         <v>120</v>
       </c>
@@ -66210,10 +64354,6 @@
       <c r="O459" t="s">
         <v>882</v>
       </c>
-      <c r="P459" t="str">
-        <f t="shared" si="11"/>
-        <v>ROBERTO APARICIO OSORIO</v>
-      </c>
       <c r="Q459" t="s">
         <v>680</v>
       </c>
@@ -66287,7 +64427,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="460" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>39</v>
       </c>
@@ -66330,10 +64470,6 @@
       <c r="O460" t="s">
         <v>108</v>
       </c>
-      <c r="P460" t="str">
-        <f t="shared" si="11"/>
-        <v>RAUL CORTES GARCIA</v>
-      </c>
       <c r="Q460" t="s">
         <v>109</v>
       </c>
@@ -66407,7 +64543,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="461" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>39</v>
       </c>
@@ -66450,10 +64586,6 @@
       <c r="O461" t="s">
         <v>3188</v>
       </c>
-      <c r="P461" t="str">
-        <f t="shared" si="11"/>
-        <v>JUAN MANUEL TENIENTE CARREON</v>
-      </c>
       <c r="Q461" t="s">
         <v>2323</v>
       </c>
@@ -66524,7 +64656,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="462" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>39</v>
       </c>
@@ -66540,9 +64672,6 @@
       <c r="E462" t="s">
         <v>3185</v>
       </c>
-      <c r="F462" t="s">
-        <v>3186</v>
-      </c>
       <c r="G462" t="s">
         <v>3187</v>
       </c>
@@ -66567,10 +64696,6 @@
       <c r="O462" t="s">
         <v>3193</v>
       </c>
-      <c r="P462" t="str">
-        <f t="shared" si="11"/>
-        <v>FRANCISCO JAVIER ESTRADA SALAZAR</v>
-      </c>
       <c r="Q462" t="s">
         <v>2645</v>
       </c>
@@ -66641,7 +64766,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="463" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>39</v>
       </c>
@@ -66657,9 +64782,6 @@
       <c r="E463" t="s">
         <v>3185</v>
       </c>
-      <c r="F463" t="s">
-        <v>3186</v>
-      </c>
       <c r="G463" t="s">
         <v>3187</v>
       </c>
@@ -66684,10 +64806,6 @@
       <c r="O463" t="s">
         <v>3197</v>
       </c>
-      <c r="P463" t="str">
-        <f t="shared" si="11"/>
-        <v>HORACIO RIOS MENDOZA</v>
-      </c>
       <c r="Q463" t="s">
         <v>1685</v>
       </c>
@@ -66758,7 +64876,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="464" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>39</v>
       </c>
@@ -66774,9 +64892,6 @@
       <c r="E464" t="s">
         <v>3185</v>
       </c>
-      <c r="F464" t="s">
-        <v>3186</v>
-      </c>
       <c r="G464" t="s">
         <v>3187</v>
       </c>
@@ -66801,10 +64916,6 @@
       <c r="O464" t="s">
         <v>3201</v>
       </c>
-      <c r="P464" t="str">
-        <f t="shared" si="11"/>
-        <v>ERICK DANIEL GUERRERO HERRERA</v>
-      </c>
       <c r="Q464" t="s">
         <v>3202</v>
       </c>
@@ -66875,7 +64986,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="465" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>39</v>
       </c>
@@ -66891,9 +65002,6 @@
       <c r="E465" t="s">
         <v>3185</v>
       </c>
-      <c r="F465" t="s">
-        <v>3186</v>
-      </c>
       <c r="G465" t="s">
         <v>3187</v>
       </c>
@@ -66918,10 +65026,6 @@
       <c r="O465" t="s">
         <v>3206</v>
       </c>
-      <c r="P465" t="str">
-        <f t="shared" si="11"/>
-        <v>JOSE FIDENCIO CAMPOS MARTINEZ</v>
-      </c>
       <c r="Q465" t="s">
         <v>3207</v>
       </c>
@@ -66995,7 +65099,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="466" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>39</v>
       </c>
@@ -67011,9 +65115,6 @@
       <c r="E466" t="s">
         <v>3185</v>
       </c>
-      <c r="F466" t="s">
-        <v>3186</v>
-      </c>
       <c r="G466" t="s">
         <v>3187</v>
       </c>
@@ -67038,10 +65139,6 @@
       <c r="O466" t="s">
         <v>3212</v>
       </c>
-      <c r="P466" t="str">
-        <f t="shared" si="11"/>
-        <v>LUCIANO PEREZ HERNANDEZ</v>
-      </c>
       <c r="Q466" t="s">
         <v>3213</v>
       </c>
@@ -67115,7 +65212,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="467" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>39</v>
       </c>
@@ -67131,9 +65228,6 @@
       <c r="E467" t="s">
         <v>3185</v>
       </c>
-      <c r="F467" t="s">
-        <v>3186</v>
-      </c>
       <c r="G467" t="s">
         <v>3187</v>
       </c>
@@ -67158,10 +65252,6 @@
       <c r="O467" t="s">
         <v>3218</v>
       </c>
-      <c r="P467" t="str">
-        <f t="shared" si="11"/>
-        <v>GABRIELA GONZALEZ PENAGOS</v>
-      </c>
       <c r="Q467" t="s">
         <v>3219</v>
       </c>
@@ -67235,7 +65325,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="468" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>39</v>
       </c>
@@ -67251,9 +65341,6 @@
       <c r="E468" t="s">
         <v>3185</v>
       </c>
-      <c r="F468" t="s">
-        <v>3186</v>
-      </c>
       <c r="G468" t="s">
         <v>3187</v>
       </c>
@@ -67278,10 +65365,6 @@
       <c r="O468" t="s">
         <v>3225</v>
       </c>
-      <c r="P468" t="str">
-        <f t="shared" si="11"/>
-        <v>CARLOS ROSAS CASTILLO</v>
-      </c>
       <c r="Q468" t="s">
         <v>1108</v>
       </c>
@@ -67355,7 +65438,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="469" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>39</v>
       </c>
@@ -67371,9 +65454,6 @@
       <c r="E469" t="s">
         <v>3185</v>
       </c>
-      <c r="F469" t="s">
-        <v>3186</v>
-      </c>
       <c r="G469" t="s">
         <v>3187</v>
       </c>
@@ -67398,10 +65478,6 @@
       <c r="O469" t="s">
         <v>3230</v>
       </c>
-      <c r="P469" t="str">
-        <f t="shared" si="11"/>
-        <v>KARLA MARIA CASTAÑEDA CRUZ</v>
-      </c>
       <c r="Q469" t="s">
         <v>3231</v>
       </c>
@@ -67475,7 +65551,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="470" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>39</v>
       </c>
@@ -67491,9 +65567,6 @@
       <c r="E470" t="s">
         <v>3185</v>
       </c>
-      <c r="F470" t="s">
-        <v>3186</v>
-      </c>
       <c r="G470" t="s">
         <v>3187</v>
       </c>
@@ -67518,10 +65591,6 @@
       <c r="O470" t="s">
         <v>3236</v>
       </c>
-      <c r="P470" t="str">
-        <f t="shared" si="11"/>
-        <v>LIZETH ANTONIO CHAVEZ</v>
-      </c>
       <c r="Q470" t="s">
         <v>3237</v>
       </c>
@@ -67595,7 +65664,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="471" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>39</v>
       </c>
@@ -67611,9 +65680,6 @@
       <c r="E471" t="s">
         <v>3185</v>
       </c>
-      <c r="F471" t="s">
-        <v>3186</v>
-      </c>
       <c r="G471" t="s">
         <v>3187</v>
       </c>
@@ -67638,10 +65704,6 @@
       <c r="O471" t="s">
         <v>3242</v>
       </c>
-      <c r="P471" t="str">
-        <f t="shared" si="11"/>
-        <v>JESUS ABEL GARZA MARQUEZ</v>
-      </c>
       <c r="Q471" t="s">
         <v>3243</v>
       </c>
@@ -67715,7 +65777,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="472" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>39</v>
       </c>
@@ -67731,9 +65793,6 @@
       <c r="E472" t="s">
         <v>3185</v>
       </c>
-      <c r="F472" t="s">
-        <v>3186</v>
-      </c>
       <c r="G472" t="s">
         <v>3187</v>
       </c>
@@ -67758,10 +65817,6 @@
       <c r="O472" t="s">
         <v>3248</v>
       </c>
-      <c r="P472" t="str">
-        <f t="shared" si="11"/>
-        <v>FRANCISCA NOHEMI CORTEZ BAUTISTA</v>
-      </c>
       <c r="Q472" t="s">
         <v>3014</v>
       </c>
@@ -67835,7 +65890,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="473" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>39</v>
       </c>
@@ -67851,9 +65906,6 @@
       <c r="E473" t="s">
         <v>3185</v>
       </c>
-      <c r="F473" t="s">
-        <v>3186</v>
-      </c>
       <c r="G473" t="s">
         <v>3187</v>
       </c>
@@ -67878,10 +65930,6 @@
       <c r="O473" t="s">
         <v>3254</v>
       </c>
-      <c r="P473" t="str">
-        <f t="shared" si="11"/>
-        <v>BELEN YESAMIN MARTINEZ SANTIAGO</v>
-      </c>
       <c r="Q473" t="s">
         <v>3255</v>
       </c>
@@ -67955,7 +66003,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="474" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>39</v>
       </c>
@@ -67971,9 +66019,6 @@
       <c r="E474" t="s">
         <v>3185</v>
       </c>
-      <c r="F474" t="s">
-        <v>3186</v>
-      </c>
       <c r="G474" t="s">
         <v>3187</v>
       </c>
@@ -67997,10 +66042,6 @@
       </c>
       <c r="O474" t="s">
         <v>3260</v>
-      </c>
-      <c r="P474" t="str">
-        <f t="shared" si="11"/>
-        <v>ARGELIO MARISCAL MARTINEZ</v>
       </c>
       <c r="Q474" t="s">
         <v>3261</v>
@@ -68307,7 +66348,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="477" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>39</v>
       </c>
@@ -68323,9 +66364,6 @@
       <c r="E477" t="s">
         <v>3281</v>
       </c>
-      <c r="F477" t="s">
-        <v>3186</v>
-      </c>
       <c r="G477" t="s">
         <v>3282</v>
       </c>
@@ -68350,10 +66388,6 @@
       <c r="O477" t="s">
         <v>3283</v>
       </c>
-      <c r="P477" t="str">
-        <f t="shared" ref="P477:P490" si="12">_xlfn.CONCAT(Q477," ",R477," ",S477)</f>
-        <v>PEDRO RIVERA RAMOS</v>
-      </c>
       <c r="Q477" t="s">
         <v>1343</v>
       </c>
@@ -68427,7 +66461,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="478" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>39</v>
       </c>
@@ -68443,9 +66477,6 @@
       <c r="E478" t="s">
         <v>3281</v>
       </c>
-      <c r="F478" t="s">
-        <v>3186</v>
-      </c>
       <c r="G478" t="s">
         <v>3282</v>
       </c>
@@ -68470,10 +66501,6 @@
       <c r="O478" t="s">
         <v>3288</v>
       </c>
-      <c r="P478" t="str">
-        <f t="shared" si="12"/>
-        <v>CLAUDIA ROMERO HERNANDEZ</v>
-      </c>
       <c r="Q478" t="s">
         <v>1529</v>
       </c>
@@ -68547,7 +66574,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="479" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>39</v>
       </c>
@@ -68563,9 +66590,6 @@
       <c r="E479" t="s">
         <v>3281</v>
       </c>
-      <c r="F479" t="s">
-        <v>3186</v>
-      </c>
       <c r="G479" t="s">
         <v>3282</v>
       </c>
@@ -68590,10 +66614,6 @@
       <c r="O479" t="s">
         <v>3293</v>
       </c>
-      <c r="P479" t="str">
-        <f t="shared" si="12"/>
-        <v>OCTAVIO ANTONIO LOPEZ GONZALEZ</v>
-      </c>
       <c r="Q479" t="s">
         <v>3294</v>
       </c>
@@ -68667,7 +66687,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="480" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>39</v>
       </c>
@@ -68683,9 +66703,6 @@
       <c r="E480" t="s">
         <v>3281</v>
       </c>
-      <c r="F480" t="s">
-        <v>3186</v>
-      </c>
       <c r="G480" t="s">
         <v>3282</v>
       </c>
@@ -68710,10 +66727,6 @@
       <c r="O480" t="s">
         <v>3299</v>
       </c>
-      <c r="P480" t="str">
-        <f t="shared" si="12"/>
-        <v>HECTOR JAZIEL CRUZ HERNANDEZ</v>
-      </c>
       <c r="Q480" t="s">
         <v>3300</v>
       </c>
@@ -68787,7 +66800,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="481" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>39</v>
       </c>
@@ -68803,9 +66816,6 @@
       <c r="E481" t="s">
         <v>3281</v>
       </c>
-      <c r="F481" t="s">
-        <v>3186</v>
-      </c>
       <c r="G481" t="s">
         <v>3282</v>
       </c>
@@ -68830,10 +66840,6 @@
       <c r="O481" t="s">
         <v>3305</v>
       </c>
-      <c r="P481" t="str">
-        <f t="shared" si="12"/>
-        <v>SANTOS MATEO MARTINEZ MARTINEZ</v>
-      </c>
       <c r="Q481" t="s">
         <v>3306</v>
       </c>
@@ -68907,7 +66913,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="482" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>39</v>
       </c>
@@ -68923,9 +66929,6 @@
       <c r="E482" t="s">
         <v>3281</v>
       </c>
-      <c r="F482" t="s">
-        <v>3186</v>
-      </c>
       <c r="G482" t="s">
         <v>3282</v>
       </c>
@@ -68950,10 +66953,6 @@
       <c r="O482" t="s">
         <v>3311</v>
       </c>
-      <c r="P482" t="str">
-        <f t="shared" si="12"/>
-        <v>ENYA ROCIO ARELLANO HERNANDEZ</v>
-      </c>
       <c r="Q482" t="s">
         <v>3312</v>
       </c>
@@ -69027,7 +67026,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="483" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>39</v>
       </c>
@@ -69043,9 +67042,6 @@
       <c r="E483" t="s">
         <v>3281</v>
       </c>
-      <c r="F483" t="s">
-        <v>3186</v>
-      </c>
       <c r="G483" t="s">
         <v>3282</v>
       </c>
@@ -69070,10 +67066,6 @@
       <c r="O483" t="s">
         <v>3317</v>
       </c>
-      <c r="P483" t="str">
-        <f t="shared" si="12"/>
-        <v>YESENIA PIO DOMINGUEZ</v>
-      </c>
       <c r="Q483" t="s">
         <v>3318</v>
       </c>
@@ -69147,7 +67139,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="484" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>39</v>
       </c>
@@ -69163,9 +67155,6 @@
       <c r="E484" t="s">
         <v>3281</v>
       </c>
-      <c r="F484" t="s">
-        <v>3186</v>
-      </c>
       <c r="G484" t="s">
         <v>3282</v>
       </c>
@@ -69190,10 +67179,6 @@
       <c r="O484" t="s">
         <v>3324</v>
       </c>
-      <c r="P484" t="str">
-        <f t="shared" si="12"/>
-        <v>DIANA LUCERO CRUZ LARA</v>
-      </c>
       <c r="Q484" t="s">
         <v>3325</v>
       </c>
@@ -69267,7 +67252,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="485" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>39</v>
       </c>
@@ -69283,9 +67268,6 @@
       <c r="E485" t="s">
         <v>3281</v>
       </c>
-      <c r="F485" t="s">
-        <v>3186</v>
-      </c>
       <c r="G485" t="s">
         <v>3282</v>
       </c>
@@ -69310,10 +67292,6 @@
       <c r="O485" t="s">
         <v>3330</v>
       </c>
-      <c r="P485" t="str">
-        <f t="shared" si="12"/>
-        <v>TANIA ALEJANDRA RIVAS GONZALEZ</v>
-      </c>
       <c r="Q485" t="s">
         <v>3331</v>
       </c>
@@ -69387,7 +67365,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="486" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>39</v>
       </c>
@@ -69403,9 +67381,6 @@
       <c r="E486" t="s">
         <v>3281</v>
       </c>
-      <c r="F486" t="s">
-        <v>3186</v>
-      </c>
       <c r="G486" t="s">
         <v>3282</v>
       </c>
@@ -69430,10 +67405,6 @@
       <c r="O486" t="s">
         <v>3337</v>
       </c>
-      <c r="P486" t="str">
-        <f t="shared" si="12"/>
-        <v>JORGE MAR GUTIERREZ</v>
-      </c>
       <c r="Q486" t="s">
         <v>275</v>
       </c>
@@ -69507,7 +67478,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="487" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>39</v>
       </c>
@@ -69523,9 +67494,6 @@
       <c r="E487" t="s">
         <v>3281</v>
       </c>
-      <c r="F487" t="s">
-        <v>3186</v>
-      </c>
       <c r="G487" t="s">
         <v>3282</v>
       </c>
@@ -69550,10 +67518,6 @@
       <c r="O487" t="s">
         <v>3343</v>
       </c>
-      <c r="P487" t="str">
-        <f t="shared" si="12"/>
-        <v>BLANCA NELLY BECERRA GUTIERREZ</v>
-      </c>
       <c r="Q487" t="s">
         <v>3344</v>
       </c>
@@ -69627,7 +67591,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="488" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>39</v>
       </c>
@@ -69643,9 +67607,6 @@
       <c r="E488" t="s">
         <v>3281</v>
       </c>
-      <c r="F488" t="s">
-        <v>3186</v>
-      </c>
       <c r="G488" t="s">
         <v>3282</v>
       </c>
@@ -69670,10 +67631,6 @@
       <c r="O488" t="s">
         <v>3349</v>
       </c>
-      <c r="P488" t="str">
-        <f t="shared" si="12"/>
-        <v>ANGEL FRANCISCO SANTIAGO FUENTES</v>
-      </c>
       <c r="Q488" t="s">
         <v>3350</v>
       </c>
@@ -69747,7 +67704,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="489" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>39</v>
       </c>
@@ -69763,9 +67720,6 @@
       <c r="E489" t="s">
         <v>3281</v>
       </c>
-      <c r="F489" t="s">
-        <v>3186</v>
-      </c>
       <c r="G489" t="s">
         <v>3282</v>
       </c>
@@ -69790,10 +67744,6 @@
       <c r="O489" t="s">
         <v>3355</v>
       </c>
-      <c r="P489" t="str">
-        <f t="shared" si="12"/>
-        <v>VICTOR MANUEL VEGA VEGA</v>
-      </c>
       <c r="Q489" t="s">
         <v>785</v>
       </c>
@@ -69867,7 +67817,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="490" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>39</v>
       </c>
@@ -69883,9 +67833,6 @@
       <c r="E490" t="s">
         <v>3281</v>
       </c>
-      <c r="F490" t="s">
-        <v>3186</v>
-      </c>
       <c r="G490" t="s">
         <v>3282</v>
       </c>
@@ -69909,10 +67856,6 @@
       </c>
       <c r="O490" t="s">
         <v>3360</v>
-      </c>
-      <c r="P490" t="str">
-        <f t="shared" si="12"/>
-        <v>MARIA DE JESUS ALVARADO DIAZ</v>
       </c>
       <c r="Q490" t="s">
         <v>1282</v>
@@ -71959,7 +69902,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="508" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>39</v>
       </c>
@@ -71975,9 +69918,6 @@
       <c r="E508" t="s">
         <v>3477</v>
       </c>
-      <c r="F508" t="s">
-        <v>3186</v>
-      </c>
       <c r="G508" t="s">
         <v>3478</v>
       </c>
@@ -72002,10 +69942,6 @@
       <c r="O508" t="s">
         <v>3479</v>
       </c>
-      <c r="P508" t="str">
-        <f t="shared" ref="P508:P517" si="13">_xlfn.CONCAT(Q508," ",R508," ",S508)</f>
-        <v>MANUELA JUAREZ VILLEGAS</v>
-      </c>
       <c r="Q508" t="s">
         <v>3480</v>
       </c>
@@ -72079,7 +70015,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="509" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>39</v>
       </c>
@@ -72095,9 +70031,6 @@
       <c r="E509" t="s">
         <v>3477</v>
       </c>
-      <c r="F509" t="s">
-        <v>3186</v>
-      </c>
       <c r="G509" t="s">
         <v>3478</v>
       </c>
@@ -72122,10 +70055,6 @@
       <c r="O509" t="s">
         <v>3485</v>
       </c>
-      <c r="P509" t="str">
-        <f t="shared" si="13"/>
-        <v>MARIA YOLANDA MARTINEZ GONZALEZ</v>
-      </c>
       <c r="Q509" t="s">
         <v>3486</v>
       </c>
@@ -72199,7 +70128,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="510" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>39</v>
       </c>
@@ -72215,9 +70144,6 @@
       <c r="E510" t="s">
         <v>3477</v>
       </c>
-      <c r="F510" t="s">
-        <v>3186</v>
-      </c>
       <c r="G510" t="s">
         <v>3478</v>
       </c>
@@ -72242,10 +70168,6 @@
       <c r="O510" t="s">
         <v>3491</v>
       </c>
-      <c r="P510" t="str">
-        <f t="shared" si="13"/>
-        <v>EMMANUEL NARVAEZ MORALES</v>
-      </c>
       <c r="Q510" t="s">
         <v>2005</v>
       </c>
@@ -72319,7 +70241,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="511" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>39</v>
       </c>
@@ -72335,9 +70257,6 @@
       <c r="E511" t="s">
         <v>3477</v>
       </c>
-      <c r="F511" t="s">
-        <v>3186</v>
-      </c>
       <c r="G511" t="s">
         <v>3478</v>
       </c>
@@ -72362,10 +70281,6 @@
       <c r="O511" t="s">
         <v>3496</v>
       </c>
-      <c r="P511" t="str">
-        <f t="shared" si="13"/>
-        <v>RAFAELA MORALES PEREZ</v>
-      </c>
       <c r="Q511" t="s">
         <v>3497</v>
       </c>
@@ -72439,7 +70354,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="512" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>39</v>
       </c>
@@ -72455,9 +70370,6 @@
       <c r="E512" t="s">
         <v>3477</v>
       </c>
-      <c r="F512" t="s">
-        <v>3186</v>
-      </c>
       <c r="G512" t="s">
         <v>3478</v>
       </c>
@@ -72482,10 +70394,6 @@
       <c r="O512" t="s">
         <v>3502</v>
       </c>
-      <c r="P512" t="str">
-        <f t="shared" si="13"/>
-        <v>MARIA SAUCEDA MARTINEZ</v>
-      </c>
       <c r="Q512" t="s">
         <v>3503</v>
       </c>
@@ -72559,7 +70467,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="513" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>39</v>
       </c>
@@ -72575,9 +70483,6 @@
       <c r="E513" t="s">
         <v>3477</v>
       </c>
-      <c r="F513" t="s">
-        <v>3186</v>
-      </c>
       <c r="G513" t="s">
         <v>3478</v>
       </c>
@@ -72602,10 +70507,6 @@
       <c r="O513" t="s">
         <v>3509</v>
       </c>
-      <c r="P513" t="str">
-        <f t="shared" si="13"/>
-        <v>DORA ELIA SANCHEZ ESPARZA</v>
-      </c>
       <c r="Q513" t="s">
         <v>3510</v>
       </c>
@@ -72679,7 +70580,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="514" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>39</v>
       </c>
@@ -72695,9 +70596,6 @@
       <c r="E514" t="s">
         <v>3477</v>
       </c>
-      <c r="F514" t="s">
-        <v>3186</v>
-      </c>
       <c r="G514" t="s">
         <v>3478</v>
       </c>
@@ -72722,10 +70620,6 @@
       <c r="O514" t="s">
         <v>3516</v>
       </c>
-      <c r="P514" t="str">
-        <f t="shared" si="13"/>
-        <v>MARIA FERNANDA DE LA CRUZ BOCANEGRA</v>
-      </c>
       <c r="Q514" t="s">
         <v>2258</v>
       </c>
@@ -72799,7 +70693,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="515" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>39</v>
       </c>
@@ -72815,9 +70709,6 @@
       <c r="E515" t="s">
         <v>3477</v>
       </c>
-      <c r="F515" t="s">
-        <v>3186</v>
-      </c>
       <c r="G515" t="s">
         <v>3478</v>
       </c>
@@ -72842,10 +70733,6 @@
       <c r="O515" t="s">
         <v>3521</v>
       </c>
-      <c r="P515" t="str">
-        <f t="shared" si="13"/>
-        <v>MARCO ANTONIO MARTINEZ SOLANO</v>
-      </c>
       <c r="Q515" t="s">
         <v>864</v>
       </c>
@@ -72919,7 +70806,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="516" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>39</v>
       </c>
@@ -72935,9 +70822,6 @@
       <c r="E516" t="s">
         <v>3477</v>
       </c>
-      <c r="F516" t="s">
-        <v>3186</v>
-      </c>
       <c r="G516" t="s">
         <v>3478</v>
       </c>
@@ -72962,10 +70846,6 @@
       <c r="O516" t="s">
         <v>3526</v>
       </c>
-      <c r="P516" t="str">
-        <f t="shared" si="13"/>
-        <v>EDGAR ARMANDO LOZANO GONZALEZ</v>
-      </c>
       <c r="Q516" t="s">
         <v>3527</v>
       </c>
@@ -73039,7 +70919,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="517" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>39</v>
       </c>
@@ -73055,9 +70935,6 @@
       <c r="E517" t="s">
         <v>3477</v>
       </c>
-      <c r="F517" t="s">
-        <v>3186</v>
-      </c>
       <c r="G517" t="s">
         <v>3478</v>
       </c>
@@ -73081,10 +70958,6 @@
       </c>
       <c r="O517" t="s">
         <v>3533</v>
-      </c>
-      <c r="P517" t="str">
-        <f t="shared" si="13"/>
-        <v>JENNIFER MORALES MENDOZA</v>
       </c>
       <c r="Q517" t="s">
         <v>3534</v>
@@ -73507,7 +71380,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="521" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>39</v>
       </c>
@@ -73550,10 +71423,6 @@
       <c r="O521" t="s">
         <v>3562</v>
       </c>
-      <c r="P521" t="str">
-        <f t="shared" ref="P521:P522" si="14">_xlfn.CONCAT(Q521," ",R521," ",S521)</f>
-        <v>MARCOS BARRON CALIXTO</v>
-      </c>
       <c r="Q521" t="s">
         <v>2631</v>
       </c>
@@ -73627,7 +71496,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="522" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>39</v>
       </c>
@@ -73643,9 +71512,6 @@
       <c r="E522" t="s">
         <v>3559</v>
       </c>
-      <c r="F522" t="s">
-        <v>3560</v>
-      </c>
       <c r="G522" t="s">
         <v>3561</v>
       </c>
@@ -73669,10 +71535,6 @@
       </c>
       <c r="O522" t="s">
         <v>3569</v>
-      </c>
-      <c r="P522" t="str">
-        <f t="shared" si="14"/>
-        <v>EDUARDO REYES HERNANDEZ</v>
       </c>
       <c r="Q522" t="s">
         <v>3570</v>
@@ -75255,8 +73117,30 @@
         <v>2864</v>
       </c>
     </row>
+    <row r="536" spans="1:40" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="537" spans="1:40" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="538" spans="1:40" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:AN538" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters blank="1">
+        <filter val="ESAB MEXICO S.A DE C.V"/>
+        <filter val="FLEX FORCE SAN NICOLAS"/>
+        <filter val="FULTRA SOLUCIONES"/>
+        <filter val="GREYHOUND LINES MEXICO S. DE R"/>
+        <filter val="HERSMEX S. DE R.L. DE C.V."/>
+        <filter val="INCAPACIDADES SAN NICOLAS"/>
+        <filter val="JC RESIDENTIAL AND LIGHT COMME"/>
+        <filter val="KLOECKNER SPECIALTY METALS DE"/>
+        <filter val="LEGO OPERACIONES DE MEXICO SA"/>
+        <filter val="MOBILE SAN NICOLAS"/>
+        <filter val="MONTOI S.A DE C.V"/>
+        <filter val="NAVISTAR MEXICO S. DE R.L. DE"/>
+        <filter val="QUIMICA E INGENIEROS CONSULTOR"/>
+        <filter val="SERVICIOS COMERCIALES AMAZON M"/>
+        <filter val="SIKA MEXICANA S.A DE C.V"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="12">
       <filters blank="1">
         <dateGroupItem year="2026" month="1" dateTimeGrouping="month"/>
@@ -75283,11 +73167,17 @@
         <dateGroupItem year="2004" dateTimeGrouping="year"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="15">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AN522">
       <sortCondition ref="F1:F538"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
